--- a/workspaces/nasdaq_hourly_24hrs/rsi/rsi_10.xlsx
+++ b/workspaces/nasdaq_hourly_24hrs/rsi/rsi_10.xlsx
@@ -618,2133 +618,2133 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ 12.72</t>
+          <t>X ≈ 12.88</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>20.41148072265104</v>
+        <v>19.21184363064075</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>18.83908882104335</v>
+        <v>18.87736371542996</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>3.985375179490148</v>
+        <v>7.223904604751546</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-2.096265960183388</v>
+        <v>1.401545011481936</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-7.834867656682697</v>
+        <v>-9.14038800380019</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-2.275108047133322</v>
+        <v>-2.416843970925314</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-5.733295542584941</v>
+        <v>-5.736270352163494</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-8.70200651891227</v>
+        <v>-8.566707134564183</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-19.42551055174821</v>
+        <v>-16.18565636702877</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-9.436602384874092</v>
+        <v>-6.746908605410418</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-6.474031954755624</v>
+        <v>-3.921884154612236</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-1.368150674314684</v>
+        <v>0.9089134889268067</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>2.898080722049968</v>
+        <v>4.900875871590735</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.01630645885903448</v>
+        <v>-0.4308256538270783</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-6.063915715894332</v>
+        <v>-6.201336095397579</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>-2.776087328013212</v>
+        <v>-5.6104732140507</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>-2.910733313916708</v>
+        <v>-5.745794182813846</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-0.3186372814689165</v>
+        <v>-3.292754843065488</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>2.595714929656545</v>
+        <v>-0.5179178044571131</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>5.482770215164507</v>
+        <v>4.790575237387785</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>4.941845868782842</v>
+        <v>4.250098841925983</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>4.867542978534651</v>
+        <v>4.175699394616082</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>10.54760426350604</v>
+        <v>9.578138668846876</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>10.47494863284398</v>
+        <v>9.505301941049602</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ 15.61</t>
+          <t>X ≈ 15.77</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-2.797533993443892</v>
+        <v>-1.810255276484241</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-8.656210306032222</v>
+        <v>-7.77497773411028</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-5.414070300396958</v>
+        <v>-9.234628822469652</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>1.236930794309494</v>
+        <v>-0.5777329534108304</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-6.490128585312604</v>
+        <v>-6.550166556086616</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-9.989822852129791</v>
+        <v>-10.11308450115524</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-8.91902508322103</v>
+        <v>-7.949330994345893</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-3.670547939593504</v>
+        <v>-2.595884989231024</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-5.473423071927741</v>
+        <v>-4.433241793991968</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-8.08994778317323</v>
+        <v>-7.083322531274447</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-9.66378327596076</v>
+        <v>-10.57123207513866</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-11.79001730193064</v>
+        <v>-12.73221177386677</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-3.686532417427102</v>
+        <v>-4.453551040856205</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-5.754427207884845</v>
+        <v>-4.675134747327377</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-4.566107810056444</v>
+        <v>-3.450856741146069</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-5.821471528992625</v>
+        <v>-4.741413541319837</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-4.10919463963031</v>
+        <v>-2.993766486707962</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>1.329973682402105</v>
+        <v>2.550516014118699</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-2.151861366556894</v>
+        <v>-1.000960177374864</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-1.965721277100265</v>
+        <v>-2.699182978312407</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-0.6587264469055398</v>
+        <v>-1.356847177856203</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-4.436131386338303</v>
+        <v>-5.204194571352559</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-2.311395172733555</v>
+        <v>-3.045061215706241</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-6.091617933723612</v>
+        <v>-6.895278610474342</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ 18.51</t>
+          <t>X ≈ 18.66</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>1.869043664882476</v>
+        <v>1.179940263708545</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-2.602847416184183</v>
+        <v>-3.364614823337334</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>1.486176481315404</v>
+        <v>0.765797778145803</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.7765595268500576</v>
+        <v>0.03999474296593775</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.4145519362507599</v>
+        <v>0.485386712486104</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-7.685882231806588</v>
+        <v>-7.733866875841784</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-7.075186778432354</v>
+        <v>-7.111851717005308</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-12.8827260286964</v>
+        <v>-13.00156613292972</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-8.697937343014537</v>
+        <v>-8.757778078742589</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-13.619775655603</v>
+        <v>-13.74881823641581</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-16.11735411606193</v>
+        <v>-14.8795956305299</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-16.40053670232863</v>
+        <v>-15.16581477641606</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-16.14296391954854</v>
+        <v>-14.89959711140029</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-17.75304360317414</v>
+        <v>-16.53273247488185</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>-19.80026159063606</v>
+        <v>-20.01491782551064</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-20.5985481071948</v>
+        <v>-20.82402765993054</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-17.96723455677411</v>
+        <v>-18.15382361630544</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-23.623048069323</v>
+        <v>-23.88836332367905</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-20.64118948139269</v>
+        <v>-20.86359749850269</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-20.46089393956202</v>
+        <v>-20.67941075976289</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-18.23472418395545</v>
+        <v>-18.4204530377964</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>-18.31619009237918</v>
+        <v>-17.65971150453752</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>-19.43561523566481</v>
+        <v>-18.79878230694401</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>-15.35087719298183</v>
+        <v>-14.65504475450835</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ 21.41</t>
+          <t>X ≈ 21.55</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-8.035634038584519</v>
+        <v>-6.718123995519186</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-1.017777395844213</v>
+        <v>-1.757133816514681</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-3.709882534415243</v>
+        <v>-2.588662141868916</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>1.700823356149549</v>
+        <v>2.027218296511791</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>3.781886047826021</v>
+        <v>2.858781635657969</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>6.427553034429032</v>
+        <v>5.387778466758895</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>6.868872739353307</v>
+        <v>5.781029764673129</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>7.814796098077053</v>
+        <v>7.844557411170399</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>5.400801327028049</v>
+        <v>4.374140391813746</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>5.841132929849792</v>
+        <v>4.767921112502016</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>6.122132581247314</v>
+        <v>5.045293270647022</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>5.839108552033601</v>
+        <v>4.765745727931439</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.2270786451498594</v>
+        <v>-1.056170514964982</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>3.238952242664332</v>
+        <v>2.239916711524884</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>8.721220321655217</v>
+        <v>8.617111703296381</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-2.987630306695145</v>
+        <v>-2.521252619904857</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-3.123246514778522</v>
+        <v>-3.830873581192463</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-1.257261263943597</v>
+        <v>-2.762610711201475</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-2.767223834781625</v>
+        <v>-4.895163991088538</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-3.81447499675749</v>
+        <v>-5.882374643273927</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-1.891695368651519</v>
+        <v>-4.080250917232654</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>1.733152897898051</v>
+        <v>-0.6292613185455096</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>-1.694132716734543</v>
+        <v>-3.178017069368742</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>3.167641325535499</v>
+        <v>1.451003298515673</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ 24.3</t>
+          <t>X ≈ 24.43</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>5.445614397018254</v>
+        <v>2.187658526833346</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>1.680895401227723</v>
+        <v>-0.4916772821935709</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-2.051910941737304</v>
+        <v>-3.110967044271611</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.1575248867277779</v>
+        <v>-1.485052690826834</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-7.06286906264112</v>
+        <v>-7.679395371172745</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-5.735272648226342</v>
+        <v>-6.320491118004057</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-6.505990351405025</v>
+        <v>-7.098130439684269</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-5.641209505218498</v>
+        <v>-6.705639747447087</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-9.034983928339315</v>
+        <v>-9.009019376824277</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-7.518890982883981</v>
+        <v>-7.43811453460966</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-14.11942505555245</v>
+        <v>-14.20060704547943</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-14.40237919837589</v>
+        <v>-14.48323859293931</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-13.23661384135163</v>
+        <v>-13.26223427959703</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-10.02272856406835</v>
+        <v>-9.967151353437671</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-8.389920400130904</v>
+        <v>-8.279566148645763</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-7.79845501578373</v>
+        <v>-7.688734058042606</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-9.082781310567569</v>
+        <v>-7.825270758851779</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-12.63032395102941</v>
+        <v>-11.45754052713594</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>-13.56214794171815</v>
+        <v>-12.42108779068813</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-9.93633326563981</v>
+        <v>-8.71156671154305</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-10.48243881606267</v>
+        <v>-9.256924058434954</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>-10.56184871725075</v>
+        <v>-9.332759306638202</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>-12.58873799032525</v>
+        <v>-11.41051983337206</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>-12.66888485581745</v>
+        <v>-11.49017317207257</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ 27.2</t>
+          <t>X ≈ 27.32</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-3.207663551642057</v>
+        <v>-3.661623026711979</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-8.783919858190337</v>
+        <v>-7.015650934707054</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-6.060091884849882</v>
+        <v>-5.445363328410117</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-5.733130859575454</v>
+        <v>-5.154930131991115</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-4.016578821226858</v>
+        <v>-4.488817382482843</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.3619197988117477</v>
+        <v>-0.2784708739758344</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-2.52078528036639</v>
+        <v>-2.060670245079599</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.3398605644957371</v>
+        <v>0.6764739360719076</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.3793446618621701</v>
+        <v>0.7173827301919857</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-2.506294087396171</v>
+        <v>-2.072962523754086</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>5.113626847628844</v>
+        <v>5.247053670069121</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.6318398370529579</v>
+        <v>0.939914807080676</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-1.561640910965302</v>
+        <v>-1.197928446644177</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-3.886941997449632</v>
+        <v>-3.435895866643698</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>0.6942324808187976</v>
+        <v>0.939528441561535</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-1.856788235648651</v>
+        <v>-1.487879550398873</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-0.9412776609279092</v>
+        <v>-0.6142944627554954</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-3.151350265080907</v>
+        <v>-2.738765007685252</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-2.930584439063153</v>
+        <v>-2.522035505406436</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-2.107141208814845</v>
+        <v>-2.332585835670955</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-1.603736208205895</v>
+        <v>-1.870544342873686</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>0.4236444594132109</v>
+        <v>0.07347646832248955</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>3.437486487984927</v>
+        <v>2.369829438992134</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>-4.005847953216382</v>
+        <v>-4.169911734164067</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ 30.09</t>
+          <t>X ≈ 30.21</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-2.059679221581291</v>
+        <v>-0.3095363811297602</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>4.231474928342415</v>
+        <v>3.537161816164186</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>1.116397108971576</v>
+        <v>1.256388493744161</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-2.918474695091959</v>
+        <v>-3.641815421883649</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-5.307041093690728</v>
+        <v>-5.653747095419433</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-4.291357392077558</v>
+        <v>-3.792037819644833</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-3.410082615239254</v>
+        <v>-3.730879198197435</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-2.030698736537587</v>
+        <v>-3.173047303857764</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-1.990601915760124</v>
+        <v>-1.812152796920358</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-1.939118723902453</v>
+        <v>-1.745407273047917</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-1.664092154404663</v>
+        <v>-1.473196851698916</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.5472683342566569</v>
+        <v>0.7616293821153164</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>1.079137917961333</v>
+        <v>2.155387680296705</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.02482422693548614</v>
+        <v>0.2588505741527456</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-0.6377775694705008</v>
+        <v>-0.3983528510225298</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>3.288722922397461</v>
+        <v>3.55054979576132</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>2.3226224472863</v>
+        <v>1.739383837396034</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-2.780090958002901</v>
+        <v>-3.401475082822643</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-0.8966668966903129</v>
+        <v>-1.507755743144635</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>0.1262440981554391</v>
+        <v>-0.4818213114550005</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-2.919641539868095</v>
+        <v>-3.545742779165749</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>0.005952393710408899</v>
+        <v>-1.100580337213884</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>0.2806417637774175</v>
+        <v>0.01423050972213957</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>0.2046783625730981</v>
+        <v>-0.06160174350113579</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ 32.98</t>
+          <t>X ≈ 33.1</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>118</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>1.339793048217686</v>
+        <v>1.438381459377425</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>1.000200246599199</v>
+        <v>1.105354737394244</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-8.052472331849103</v>
+        <v>-8.762407347573159</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-2.867151546519821</v>
+        <v>-2.723421128267489</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-2.3980204871919</v>
+        <v>-2.212196211792126</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>3.700262287779054</v>
+        <v>3.035065902780786</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>7.138145165945112</v>
+        <v>6.485466335881341</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>4.326448695007834</v>
+        <v>4.520542614253785</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>8.592309035286789</v>
+        <v>7.937045328432944</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>11.18991569642724</v>
+        <v>10.54641689752977</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>10.62702314367351</v>
+        <v>9.978737873111292</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>7.80885631444022</v>
+        <v>7.170764126015087</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>11.7478680430368</v>
+        <v>10.27771349465613</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>8.987390954434638</v>
+        <v>8.37045846990037</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>10.86359141969557</v>
+        <v>10.25304780690484</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>12.31698118584931</v>
+        <v>11.69612113588063</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>7.101510246084388</v>
+        <v>7.335497292870443</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>6.142405847689474</v>
+        <v>6.38711994935403</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>6.363980846678579</v>
+        <v>6.604825660177518</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>4.86398426236677</v>
+        <v>5.099375782845854</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>5.671141682710648</v>
+        <v>5.405973500566098</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>6.443856206459934</v>
+        <v>6.17758516627584</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>6.720752289420183</v>
+        <v>6.452059878757893</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>8.001288532064613</v>
+        <v>6.376227625534618</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ 35.88</t>
+          <t>X ≈ 35.99</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-4.910870646011396</v>
+        <v>-5.679565424903991</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-1.898655402658626</v>
+        <v>-1.899514816181515</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>4.198738933697356</v>
+        <v>4.075103210853804</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.6957358525032333</v>
+        <v>-0.7493739138081992</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>3.124534142099932</v>
+        <v>3.031228216331691</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>5.820237261399406</v>
+        <v>5.682986555949817</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>1.704238972486117</v>
+        <v>1.624184572368314</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>2.264483720052056</v>
+        <v>2.169599469400339</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>4.819768927164702</v>
+        <v>4.678487464193488</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>4.049807226409968</v>
+        <v>4.733491106937088</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>4.32500675324976</v>
+        <v>5.008232411199572</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>4.88711996858261</v>
+        <v>5.556539847741526</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>6.282816320028438</v>
+        <v>6.909728038762744</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>6.903612974775889</v>
+        <v>7.51644623156001</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>4.568232258404173</v>
+        <v>5.213112398337977</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>2.644822735482315</v>
+        <v>3.334032899931799</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>6.713371079391763</v>
+        <v>7.327566657367001</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>13.33107673892674</v>
+        <v>13.82983255314559</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>14.38753603631235</v>
+        <v>14.87641843033025</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>12.05357142857125</v>
+        <v>12.59033295051046</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>10.6700348851197</v>
+        <v>11.22611637771995</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>9.753743695023296</v>
+        <v>10.32382413531912</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>10.02851886150543</v>
+        <v>9.771852566809244</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>6.591232984421829</v>
+        <v>7.216681470610958</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ 38.77</t>
+          <t>X ≈ 38.88</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>128</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-1.743096795230336</v>
+        <v>-2.487552427024553</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>4.142810755396297</v>
+        <v>4.176433282123767</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-3.524464917358607</v>
+        <v>-4.266835736307975</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.4264720445018213</v>
+        <v>-0.3150929303035923</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.05929280553738892</v>
+        <v>-0.6527914798811096</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>1.805115937957211</v>
+        <v>0.3144438909573921</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>2.585794082301717</v>
+        <v>1.872617529922252</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.7498548189889789</v>
+        <v>0.03831989542345582</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.792459733662767</v>
+        <v>-0.6972819790194009</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>3.131968250567688</v>
+        <v>1.638880024274705</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>1.849957156223766</v>
+        <v>0.358063881043833</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>3.908724164441722</v>
+        <v>3.192164091446891</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>3.56076013523483</v>
+        <v>2.845301530290058</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>2.557959930103117</v>
+        <v>2.623668608806952</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>5.019864383255943</v>
+        <v>5.082148059043071</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>5.620211909504526</v>
+        <v>5.681194063242231</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>5.951816457543202</v>
+        <v>5.54893956193159</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>5.065583041447752</v>
+        <v>4.664526135106826</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>4.500456204379567</v>
+        <v>3.323175581358107</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>3.125</v>
+        <v>1.951190146437398</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>1.800549591002046</v>
+        <v>1.089236212430521</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>1.724594535359437</v>
+        <v>1.013390251021598</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>1.218119701841566</v>
+        <v>0.5066149635038286</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>1.923428362573098</v>
+        <v>1.212032710280376</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ 41.67</t>
+          <t>X ≈ 41.77</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-5.900194836078079</v>
+        <v>-4.800826970262904</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-3.366205283246579</v>
+        <v>-2.244910971954219</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-1.260425327907903</v>
+        <v>0.6094846498516091</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.1713795689326574</v>
+        <v>1.335538422664953</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-1.638809016656346</v>
+        <v>-0.4556656460926263</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-3.899961703251009</v>
+        <v>-1.697267195189568</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-8.57422955072861</v>
+        <v>-7.539673337427196</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-3.837200709261595</v>
+        <v>-2.768307437956693</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-5.949221348495513</v>
+        <v>-4.16806520338281</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-9.600478386596585</v>
+        <v>-8.144478818488011</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-7.892703435735676</v>
+        <v>-6.006669798068813</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-6.740316876600517</v>
+        <v>-5.566895724277941</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-3.560054075562284</v>
+        <v>-2.359738812016353</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-3.066385497998169</v>
+        <v>-3.306552268384024</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>-4.448862601450699</v>
+        <v>-4.691598353373614</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>-1.985133013775673</v>
+        <v>-2.649150002392773</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>-2.11922670792476</v>
+        <v>-2.78478215681082</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-1.504785663588059</v>
+        <v>-2.167952543062889</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>2.308459801501876</v>
+        <v>2.397105409814685</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-1.821043165467628</v>
+        <v>-1.334703126849647</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-0.9253946536021047</v>
+        <v>-0.4279739324965064</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-2.440198630108192</v>
+        <v>-1.953095256224778</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-3.604272384489377</v>
+        <v>-3.127895906061568</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-1.521940342462869</v>
+        <v>-1.029815115806578</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ 44.56</t>
+          <t>X ≈ 44.66</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>2.955467583577551</v>
+        <v>3.367651829743465</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>1.737619210866335</v>
+        <v>1.283801537924255</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.5761658128434917</v>
+        <v>-1.020537840602387</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>6.646144468377997</v>
+        <v>7.007089344833311</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>2.75670399620077</v>
+        <v>3.178097689898628</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>7.349598856481293</v>
+        <v>6.857945974218701</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>2.172592902790917</v>
+        <v>2.594551070846364</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-3.397905235742449</v>
+        <v>-2.927530470586881</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-3.358284459799982</v>
+        <v>-2.886362372836487</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-6.780556902467822</v>
+        <v>-7.152000605013825</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-5.626778097643907</v>
+        <v>-6.005238950063763</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-1.489555938700917</v>
+        <v>-1.914080667571817</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.9221914983256738</v>
+        <v>0.4624693384933138</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-1.952174179117073</v>
+        <v>-1.507714920215065</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>0.04284125251305682</v>
+        <v>0.4610415783084747</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>-2.016965954502531</v>
+        <v>-0.6969890543499702</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>-3.920971153076437</v>
+        <v>-3.460222649832936</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-1.371087312534549</v>
+        <v>-0.9361211600161212</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>-3.809831406239901</v>
+        <v>-3.35221255237812</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>-0.9679203539823007</v>
+        <v>-0.5337877950420591</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>-3.281032267405237</v>
+        <v>-2.830719927920377</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>-1.587075818623063</v>
+        <v>-1.152179924416991</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>-0.4273448999283431</v>
+        <v>-0.0005122294788080239</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>-4.928065000258961</v>
+        <v>-4.462309394982775</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ 47.46</t>
+          <t>X ≈ 47.55</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>143</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1.567555195641802</v>
+        <v>1.600675844940433</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>2.624612292577218</v>
+        <v>3.354675871159948</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>6.766190638249491</v>
+        <v>6.801367649013329</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>6.748066226373695</v>
+        <v>7.480632110522912</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>4.993427218393229</v>
+        <v>5.755497417125888</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.3960339718448722</v>
+        <v>0.3658651053886359</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>3.016387896711272</v>
+        <v>2.385898316172103</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>2.043169024663825</v>
+        <v>1.412206375340375</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.006521066716004498</v>
+        <v>-1.332899099726767</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-5.661094308499059</v>
+        <v>-5.584295103694856</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-10.27618868321342</v>
+        <v>-10.88431898177799</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-6.370946944232827</v>
+        <v>-6.987085350135693</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-6.79977968762838</v>
+        <v>-6.718125092525838</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-6.325181332178396</v>
+        <v>-6.243504335529217</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-7.686597450376979</v>
+        <v>-7.602000181466558</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-6.392236701455055</v>
+        <v>-7.011944759878794</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-5.827029696302958</v>
+        <v>-6.450392737876811</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-5.932013112398714</v>
+        <v>-5.160466454597987</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-7.114491348067986</v>
+        <v>-6.345710282718308</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-5.528846153846153</v>
+        <v>-5.459563773449425</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-7.470647961445508</v>
+        <v>-6.701410640716311</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-9.644505114989897</v>
+        <v>-8.875158700027349</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-9.369729948508244</v>
+        <v>-8.600683987545295</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-6.648468490573435</v>
+        <v>-6.578614142866478</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ 50.35</t>
+          <t>X ≈ 50.45</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.6287832586151296</v>
+        <v>0.4076528872826799</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>4.342972763637519</v>
+        <v>2.831262347861646</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>1.52023626343157</v>
+        <v>0.6683677686814065</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.5361799378764687</v>
+        <v>-2.101910281197377</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.4265556435956697</v>
+        <v>-1.082320925936806</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-2.742836963684816</v>
+        <v>-4.321288210114709</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-4.886701172878716</v>
+        <v>-5.805764786258521</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-5.174750896248952</v>
+        <v>-6.090150049959533</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-5.812262202871175</v>
+        <v>-6.050426816315579</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-1.89350880647001</v>
+        <v>-2.721924043511535</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-6.346710209795376</v>
+        <v>-6.573978125982187</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-9.598702364202666</v>
+        <v>-10.29396391112614</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-11.41018893058337</v>
+        <v>-12.8073180253251</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-9.881221126750205</v>
+        <v>-11.66765028727381</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-11.48550124928077</v>
+        <v>-13.71934701629618</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-10.21476552398372</v>
+        <v>-12.01281872702086</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-5.619129488403225</v>
+        <v>-6.639181868516253</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-7.751139931525067</v>
+        <v>-9.777827404080625</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-5.50798974156622</v>
+        <v>-7.078770326123184</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-7.347972972972968</v>
+        <v>-7.581579688568787</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-5.188470679268228</v>
+        <v>-6.744815511706918</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-6.615777086262341</v>
+        <v>-8.199971817943762</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-7.016677595455583</v>
+        <v>-8.615152277875502</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-6.416943259048679</v>
+        <v>-7.31167418627119</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ 53.25</t>
+          <t>X ≈ 53.33</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>7.556146880025352</v>
+        <v>7.076988002169905</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>4.726202927344744</v>
+        <v>5.516931463698725</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>2.046662667174502</v>
+        <v>2.250316406219966</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-1.160527370794121</v>
+        <v>-0.9101401748642459</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.2762029543246456</v>
+        <v>-0.01927529391919336</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-4.452939847428539</v>
+        <v>-4.11589712848459</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>1.010581671562385</v>
+        <v>1.233814664400271</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.1095265334551812</v>
+        <v>0.3449503466774786</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.4730974788796587</v>
+        <v>-0.2249795740280049</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>4.372106827431189</v>
+        <v>5.122848151130334</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>4.023626585136583</v>
+        <v>4.174226433982064</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>1.870617123535574</v>
+        <v>2.060519849859119</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0.7461381521422297</v>
+        <v>0.9383598131347952</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>1.149781341107868</v>
+        <v>1.330420934133841</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>0.4908501020704392</v>
+        <v>1.285662104655799</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-0.1640898483080449</v>
+        <v>0.6533980025215058</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-0.2981835424569681</v>
+        <v>0.5190852798287651</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>0.8468330414478942</v>
+        <v>1.641238441038119</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-0.1870437956205748</v>
+        <v>0.6301359569317668</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-1.249999999999993</v>
+        <v>-1.637005963161407</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-0.5432004089979543</v>
+        <v>0.2744355989336285</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>1.255844535359572</v>
+        <v>1.425583502555199</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-0.9693802981582849</v>
+        <v>-0.7539295150240974</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-1.670321637426895</v>
+        <v>-1.443258700762705</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ 56.15</t>
+          <t>X ≈ 56.22</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>157</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-3.449681946662473</v>
+        <v>-4.053155400422888</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-3.771964887303227</v>
+        <v>-4.37357493829473</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-4.639590726067148</v>
+        <v>-3.968028000369699</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-7.899534020622035</v>
+        <v>-7.227127866686345</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-9.56509645255673</v>
+        <v>-8.863270057578873</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-3.008259361477762</v>
+        <v>-2.30663207615374</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-7.627568121804387</v>
+        <v>-6.288541863544594</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-6.650197525744929</v>
+        <v>-5.941702654961702</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-7.514727769869168</v>
+        <v>-7.177595574627368</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-2.830648290054633</v>
+        <v>-3.513420457256373</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>4.189192353466119</v>
+        <v>3.752490181473696</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-2.460433465294209</v>
+        <v>-2.899810054153676</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-4.476791784163503</v>
+        <v>-4.289033378642834</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-1.513435219401678</v>
+        <v>-0.9459690830364664</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-0.8984811081203645</v>
+        <v>-1.219811760189735</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-0.9403637336583657</v>
+        <v>-0.6217324169413274</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-0.4375147526479779</v>
+        <v>-0.3679453168656721</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-1.179440843902711</v>
+        <v>-1.746671371005249</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-4.148031056766932</v>
+        <v>-4.078550690717655</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-6.508757961783438</v>
+        <v>-5.802532906227476</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-4.504187670144375</v>
+        <v>-4.434251048715801</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-3.943200050627972</v>
+        <v>-3.236211659806429</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-1.757596858668137</v>
+        <v>-1.050908921846592</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-3.107423548254928</v>
+        <v>-2.400626525388418</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 59.05</t>
+          <t>X ≈ 59.1</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-2.40626959882897</v>
+        <v>-1.691196062321168</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-5.904168951115238</v>
+        <v>-5.919772408264159</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.3847882593737637</v>
+        <v>-0.8669378347608543</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.1665259577463871</v>
+        <v>-0.2819286030677901</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.1977990763140482</v>
+        <v>-0.6167719145726238</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-1.908610675764947</v>
+        <v>-2.377066325526101</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>1.114430628955375</v>
+        <v>0.09652455911761848</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-2.961936900428825</v>
+        <v>-3.425828264059106</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>2.142870303834243</v>
+        <v>1.807015790423463</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-2.428433461365415</v>
+        <v>-2.858977786697743</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.8882514094400236</v>
+        <v>-1.287315716654504</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-4.331902274940319</v>
+        <v>-4.81494640400345</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-1.658925138997013</v>
+        <v>-2.691355224106246</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-2.513193342436423</v>
+        <v>-3.561784749903559</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-3.172124581473724</v>
+        <v>-3.570577398133466</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-1.311241747042224</v>
+        <v>-2.326839826839894</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-0.1795126563809433</v>
+        <v>-0.5127050157653485</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-3.449053034501617</v>
+        <v>-3.214948316989208</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-4.498752656379921</v>
+        <v>-4.947108884116759</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-4.311708860759566</v>
+        <v>-4.760263074148796</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-5.487820662162591</v>
+        <v>-5.952159891465406</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-4.930864325400051</v>
+        <v>-5.378655203523863</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-7.187734728538253</v>
+        <v>-7.701583088444551</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-6.630764675401593</v>
+        <v>-7.128064692317025</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 61.94</t>
+          <t>X ≈ 61.99</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>2.543117965245202</v>
+        <v>2.082495004952598</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>4.415904843478792</v>
+        <v>4.627451195317875</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>4.429632285208449</v>
+        <v>4.611491104495222</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>5.18538718734095</v>
+        <v>5.336368432421473</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>7.750373663237212</v>
+        <v>7.867591279911181</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>1.325091317262256</v>
+        <v>0.8654007291631913</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>4.218815583743897</v>
+        <v>5.119756320099022</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>5.842977470382792</v>
+        <v>6.27428835524384</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>8.0903758883466</v>
+        <v>8.475575278694862</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>10.99301106581256</v>
+        <v>11.29367646385131</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>8.32619386233965</v>
+        <v>8.69309098476932</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>11.72357054709995</v>
+        <v>12.44189747154546</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>6.187314622730376</v>
+        <v>7.002188642099419</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>8.907134282284353</v>
+        <v>9.658807607379444</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>12.6599677491294</v>
+        <v>13.31721107238882</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>8.843263092868433</v>
+        <v>9.595051231741877</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>4.297404692837148</v>
+        <v>5.144587332174481</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>6.398303629682971</v>
+        <v>7.19802000964826</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>6.614426792614857</v>
+        <v>7.413911390572586</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>8.272058823529491</v>
+        <v>9.039606121404006</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>6.993564296884394</v>
+        <v>7.058211032574583</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>3.241138653006416</v>
+        <v>3.385242769007206</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>4.251207937135682</v>
+        <v>3.659717481489345</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>4.175266597867136</v>
+        <v>3.583885228265984</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ 64.84</t>
+          <t>X ≈ 64.88</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.5491214057507321</v>
+        <v>-0.2246980451090508</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-3.384296920395123</v>
+        <v>-3.665064905570603</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-2.948997384481338</v>
+        <v>-2.618611904912221</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-1.787790697674346</v>
+        <v>-1.468211887087953</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-3.403060482698528</v>
+        <v>-2.425120372057442</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1.159104130308251</v>
+        <v>2.109671900996453</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>6.011237998254373</v>
+        <v>5.685549304062768</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>4.482683352735734</v>
+        <v>4.165101834464835</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>2.024199417758368</v>
+        <v>1.722116966690095</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>1.250364006988875</v>
+        <v>0.9492012906536047</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.2747232741042041</v>
+        <v>-0.6400931044514806</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>5.620629370629366</v>
+        <v>4.67121960390169</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>3.246138152142294</v>
+        <v>2.926939524623144</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>4.274781341107868</v>
+        <v>3.94809667302134</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>-0.1341498979294258</v>
+        <v>-0.4367546990933775</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>0.4609101516919551</v>
+        <v>0.7787502352719784</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>2.826816457543032</v>
+        <v>3.129305147983942</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>3.346833041447752</v>
+        <v>3.645582456585117</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>2.937956204379567</v>
+        <v>2.619237812664721</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>5</v>
+        <v>4.669437659899835</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>3.206799591002046</v>
+        <v>3.50577347951144</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>3.130844535359515</v>
+        <v>3.429927518102339</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>1.530619701841637</v>
+        <v>2.46216620573967</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>4.579678362573169</v>
+        <v>5.491924014628204</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ 67.73</t>
+          <t>X ≈ 67.78</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-3.674121405750796</v>
+        <v>-3.640847113431889</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-3.3599462710444</v>
+        <v>-3.317729174939679</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>4.291262355778557</v>
+        <v>3.796883354976693</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>1.629417094533302</v>
+        <v>1.110245125007715</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>9.056355101717131</v>
+        <v>8.011296757723528</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>3.399363870568216</v>
+        <v>2.935105049084058</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>5.873250985267283</v>
+        <v>5.452630049404164</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>2.997293742346052</v>
+        <v>2.542839657282748</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.2079434393844934</v>
+        <v>-0.7051468450130827</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-0.332428200803264</v>
+        <v>-0.8201677842074702</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-1.35677023238916</v>
+        <v>-1.20400287888765</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.337162837162829</v>
+        <v>-0.8248575454934652</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>1.135748541752626</v>
+        <v>0.02566459817673206</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>0.2650410813676913</v>
+        <v>-0.8533090151121101</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>-1.043240807020332</v>
+        <v>-2.169347049534693</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>-1.097531406749603</v>
+        <v>-2.890749601275843</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-1.880975750249249</v>
+        <v>-3.68256147509549</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>1.260794080408935</v>
+        <v>-0.4979284947062226</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>0.8275665939899639</v>
+        <v>-0.2820371137818327</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>3.61201298701306</v>
+        <v>3.194282380396807</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>2.419461928664305</v>
+        <v>1.993841475588596</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>3.642208171723148</v>
+        <v>3.233784987863778</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>1.3195807408026</v>
+        <v>0.8766807529773359</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>-3.301815143920336</v>
+        <v>-3.804414658140672</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X ≈ 70.62</t>
+          <t>X ≈ 70.66</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>3.362915631286157</v>
+        <v>3.712094063038663</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.6759635870618794</v>
+        <v>-0.2991533235464914</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-2.115664051147924</v>
+        <v>-1.737172372577483</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.8742463393625783</v>
+        <v>1.226344196215038</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.2317641864021667</v>
+        <v>0.1552596060207421</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-6.71126624006218</v>
+        <v>-6.275421266705408</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-8.224873112856905</v>
+        <v>-7.782664068242774</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-8.503427758375295</v>
+        <v>-8.060875512995892</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-3.276726508167556</v>
+        <v>-2.87232950755174</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-6.272784141159256</v>
+        <v>-5.85112753652944</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-6.739165614784739</v>
+        <v>-5.577067894367516</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-6.277518777518736</v>
+        <v>-4.385229062521447</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-5.920528514524435</v>
+        <v>-4.037802894083399</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-3.91966310333661</v>
+        <v>-2.05299941758873</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>-6.800816564596182</v>
+        <v>-4.917025068110632</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>-3.983534292752488</v>
+        <v>-2.11675579322646</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>-5.599109468382728</v>
+        <v>-3.721261165497928</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-4.222611402996733</v>
+        <v>-2.355513634024952</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>-4.747228980805573</v>
+        <v>-2.874916370747769</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>-5.300925925926016</v>
+        <v>-4.158658796073986</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>-2.881163371960838</v>
+        <v>-1.760028493451649</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>-2.216377686862792</v>
+        <v>-1.100580337213742</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>-4.163824742602877</v>
+        <v>-3.031987977672735</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-7.943469785575054</v>
+        <v>-6.784290819131385</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X ≈ 73.52</t>
+          <t>X ≈ 73.56</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>127</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.6565872556665298</v>
+        <v>0.6898615479853163</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-1.2533914085841</v>
+        <v>-0.4323168251676037</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-2.693091872670237</v>
+        <v>-1.870335874198595</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-1.832082036257049</v>
+        <v>-1.795888318838145</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-8.496564419706338</v>
+        <v>-8.430891389810661</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-11.45900610591211</v>
+        <v>-11.39353150292588</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-8.294864363950431</v>
+        <v>-7.441070737997421</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-7.786017434665837</v>
+        <v>-6.931880607947264</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-10.10670609405265</v>
+        <v>-9.252598150442054</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-10.88054150482204</v>
+        <v>-10.02551382647845</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-8.243977513297253</v>
+        <v>-8.176651034710225</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-5.373465117559654</v>
+        <v>-6.093195713748869</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-4.135751611637296</v>
+        <v>-4.854153056195486</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-5.144509997474842</v>
+        <v>-5.862633507445224</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>-4.228638086905761</v>
+        <v>-4.945973655419444</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>-5.208381186890719</v>
+        <v>-5.926389883082749</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>-3.767671731433431</v>
+        <v>-4.485503870454011</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-3.872655147528668</v>
+        <v>-3.802942999472002</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>-4.443933559399959</v>
+        <v>-4.374453193350824</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>-3.469488188976378</v>
+        <v>-3.400205808579607</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>-1.650483873564887</v>
+        <v>-1.580547252136192</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>-0.9390373544044337</v>
+        <v>-0.8689916387422301</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>1.69794253648724</v>
+        <v>1.767687798149232</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>2.409402772021828</v>
+        <v>2.479257119729198</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X ≈ 76.41</t>
+          <t>X ≈ 76.44</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-2.135659867289299</v>
+        <v>-1.702862617307886</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-3.240066151164356</v>
+        <v>-4.363220811006634</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-2.372074307558179</v>
+        <v>-3.475658464688742</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-10.00894454382826</v>
+        <v>-10.39016287172839</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-3.451137405775384</v>
+        <v>-3.749209158229135</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.9562804850762916</v>
+        <v>-1.236661576782929</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>1.347776459792712</v>
+        <v>0.3169711346756472</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>2.607683352735734</v>
+        <v>1.589147286821714</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>2.649199417758368</v>
+        <v>2.405828267186017</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>4.952287083912012</v>
+        <v>4.733687784947939</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>5.226646351027348</v>
+        <v>4.232553628660249</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>3.409090909090914</v>
+        <v>3.178610426762681</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>4.592291998296069</v>
+        <v>4.381029755255405</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>5.140165956492488</v>
+        <v>4.935144677258435</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>6.788927025147537</v>
+        <v>6.602582775026796</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>5.845525536307342</v>
+        <v>5.646582100070432</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>4.942201072927645</v>
+        <v>4.737471164643395</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>4.067986887601592</v>
+        <v>3.082242863922978</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>8.130263896687218</v>
+        <v>7.174103237095359</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>7.54807692307692</v>
+        <v>7.360949047063386</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>8.543338052540513</v>
+        <v>8.368790475996541</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>5.390459919974823</v>
+        <v>4.416975522339435</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>7.972927394149259</v>
+        <v>7.792225428619929</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>5.589293747188485</v>
+        <v>5.390811780047819</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X ≈ 79.31</t>
+          <t>X ≈ 79.34</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>114</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-4.55131438820689</v>
+        <v>-5.395233078344248</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>0.3766679918856255</v>
+        <v>1.287533982955111</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-1.940225454656698</v>
+        <v>-1.027678048532067</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-4.408404732762129</v>
+        <v>-3.495018032887096</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-7.405253465154608</v>
+        <v>-6.462387452802787</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-8.095281834603959</v>
+        <v>-7.152614249161552</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-5.359376036833375</v>
+        <v>-4.415791003227383</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-3.006351734983561</v>
+        <v>-2.062423500611985</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-1.210449705048653</v>
+        <v>-1.143743336241094</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>2.401679796462624</v>
+        <v>2.469305900003121</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>3.553232046034104</v>
+        <v>4.497751507077318</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>3.274138142559202</v>
+        <v>4.219002103629322</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>2.149646924072059</v>
+        <v>3.095840036773204</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>0.1739041481254162</v>
+        <v>1.120375195414283</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>-1.362220073367972</v>
+        <v>-0.4149610846224618</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>-0.767160023746591</v>
+        <v>0.1794258373205722</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>-0.02406073543937026</v>
+        <v>0.9227016827992998</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-0.1290441515347069</v>
+        <v>0.8178609789780609</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>0.9642719938532522</v>
+        <v>1.910945342358531</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>-0.6030701754386456</v>
+        <v>-0.5337877950418601</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>2.362501345387962</v>
+        <v>2.432437966816671</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>4.040932254657683</v>
+        <v>4.988170952775981</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>4.31570742113977</v>
+        <v>4.385452682801898</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>5.994152046783633</v>
+        <v>6.064006394490953</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X ≈ 82.21</t>
+          <t>X ≈ 82.22</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>5.876440392002017</v>
+        <v>6.58642561384066</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>1.046882854885709</v>
+        <v>0.5698306336727583</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.7307778964176208</v>
+        <v>0.2681752210054071</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>5.634962111314344</v>
+        <v>5.237039383380854</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>4.146096820672327</v>
+        <v>3.76488527446994</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>2.086070422443186</v>
+        <v>1.679124187840053</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-4.304773237700765</v>
+        <v>-4.774642677868485</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-2.336136871983399</v>
+        <v>-2.780126849894323</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.04742979572478134</v>
+        <v>-0.4659123952523743</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>0.3023302991237671</v>
+        <v>-0.1024644349252597</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.546905939378874</v>
+        <v>-0.9647684291269769</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>4.791977685236112</v>
+        <v>4.438300349243242</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>5.914677477984931</v>
+        <v>5.587865555114398</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>0.07534313886071686</v>
+        <v>-0.3150315031503084</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>1.663602911059279</v>
+        <v>1.299552471996407</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>-1.11212355617328</v>
+        <v>-1.515151515151508</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>-1.246217250322204</v>
+        <v>-1.649068652129081</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-1.351200666417384</v>
+        <v>-1.753909355950164</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>-4.50586402033953</v>
+        <v>-6.083472520480392</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>-0.9480337078651004</v>
+        <v>-1.351172165057811</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>-0.3676386112450771</v>
+        <v>-0.757354696660208</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-1.567189172505735</v>
+        <v>-1.969564294432942</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>-0.1688185004055569</v>
+        <v>-0.5587259455872555</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>4.249622182797857</v>
+        <v>3.910896346643945</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X ≈ 85.1</t>
+          <t>X ≈ 85.12</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>3.642951764980872</v>
+        <v>3.149276343358153</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>0.8687518600926865</v>
+        <v>0.345363742539206</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>11.62417334722606</v>
+        <v>11.25302370585388</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>4.812819058423145</v>
+        <v>4.367230180238316</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>6.886573663642999</v>
+        <v>6.500575510160175</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>15.6103236425034</v>
+        <v>15.32951700489953</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>7.520384339717744</v>
+        <v>7.150160913601802</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>12.11987847468694</v>
+        <v>11.81022107378696</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>13.38090673483154</v>
+        <v>13.08627615693624</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>15.04609571430597</v>
+        <v>14.78249628336889</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>15.32045498142131</v>
+        <v>15.05655592553081</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>10.16331229745865</v>
+        <v>9.839534917144547</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>9.038821078971502</v>
+        <v>8.71637285028843</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>5.158927682571253</v>
+        <v>4.79159027013813</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>8.158533028899875</v>
+        <v>7.837150676261309</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>9.973105273643135</v>
+        <v>9.6661054994388</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>7.399987189250353</v>
+        <v>7.063052559992258</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>7.295003773155003</v>
+        <v>6.958211856171005</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>5.072102545842945</v>
+        <v>5.939535335860775</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>2.820121951219512</v>
+        <v>2.422677442125121</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>1.057409347099608</v>
+        <v>0.6455633729245278</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>0.9814542914569984</v>
+        <v>0.5697174115154269</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>4.914766043304986</v>
+        <v>4.547895827701183</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>7.277849094280349</v>
+        <v>6.941199376947004</v>
       </c>
     </row>
     <row r="32">
@@ -2757,158 +2757,158 @@
         <v>78</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.1720324404031004</v>
+        <v>0.2053067327219296</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>2.400959489861286</v>
+        <v>2.434632498474627</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-1.602843538327413</v>
+        <v>-1.567489114658926</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0.2474657125819704</v>
+        <v>0.2836594300008741</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>5.010401055763076</v>
+        <v>5.076074085658753</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>1.351411822616008</v>
+        <v>1.416886425602279</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.5785456905619171</v>
+        <v>0.644937741711864</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-2.264111519059135</v>
+        <v>-2.197376267143703</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.9405441719852234</v>
+        <v>-0.8738378031777216</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-4.278482146857137</v>
+        <v>-4.210856043316696</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-1.440020315639281</v>
+        <v>-1.372693837052253</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0.8449883449883799</v>
+        <v>0.9126593236023126</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>1.002548408552485</v>
+        <v>1.071548538797444</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>4.62734544367202</v>
+        <v>4.696623508504743</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>3.968414204634634</v>
+        <v>4.038480210924099</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>4.563474254256057</v>
+        <v>4.632867132867133</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>3.147329278055821</v>
+        <v>3.216898713838347</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>0.4782432978580076</v>
+        <v>0.5479554459146314</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>-0.5876848212614547</v>
+        <v>-0.5182044552123202</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>-0.400641025641022</v>
+        <v>-0.3313586452442934</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>-3.507943998741581</v>
+        <v>-3.438007377312928</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>-1.019796490281585</v>
+        <v>-0.9497507746194245</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>-2.027072605850705</v>
+        <v>-1.95732734418862</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>4.307242465137243</v>
+        <v>4.37709681284452</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X ≈ 90.89</t>
+          <t>X ≈ 90.9</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>73</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-2.9891898989015</v>
+        <v>-2.955915606582671</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>7.634538696043236</v>
+        <v>7.668211704656578</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>7.564701245655748</v>
+        <v>7.600055669324234</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>6.85090793246259</v>
+        <v>6.887101649881494</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>6.485638147438522</v>
+        <v>6.551311177334199</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>12.15225481523983</v>
+        <v>12.2177294182261</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>8.639662655788577</v>
+        <v>8.706054706938524</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>8.361108010270016</v>
+        <v>8.427843262185448</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>2.923172020498093</v>
+        <v>2.989878389305595</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>6.258925650824516</v>
+        <v>6.326551754364957</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>2.423695876844</v>
+        <v>2.491022355431028</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>2.144601973369063</v>
+        <v>2.212272951982996</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>2.389973768580589</v>
+        <v>2.458973898825548</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>2.168616957546192</v>
+        <v>2.237895022378915</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>8.359000787002081</v>
+        <v>8.429066793291547</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>10.32392385032212</v>
+        <v>10.3933167289332</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>8.819967142474582</v>
+        <v>8.889536578257108</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>7.345120712680668</v>
+        <v>7.414832860737292</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>3.451654834516596</v>
+        <v>3.52113520056573</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>2.268835616438359</v>
+        <v>2.338117996835088</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>3.095498221139074</v>
+        <v>3.165434842567727</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>3.019543165496422</v>
+        <v>3.089588881158583</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>3.294318331978516</v>
+        <v>3.364063593640601</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>3.218376992710084</v>
+        <v>3.288231340417362</v>
       </c>
     </row>
     <row r="34">
@@ -2921,76 +2921,76 @@
         <v>66</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>11.47739374576436</v>
+        <v>11.51066803808319</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>8.111915200817002</v>
+        <v>8.145588209430343</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>2.126760191276297</v>
+        <v>2.162114614944784</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>5.958421423537708</v>
+        <v>5.994615140956611</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>8.623454668816692</v>
+        <v>8.689127698712369</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>7.295467766671955</v>
+        <v>7.360942369658225</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>9.552904664920952</v>
+        <v>9.619296716070899</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>13.81980456485694</v>
+        <v>13.88653981677237</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>12.34616911472807</v>
+        <v>12.41287548353557</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>7.026879158504094</v>
+        <v>7.094505262044535</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>10.33154145592245</v>
+        <v>10.39886793450948</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>11.56759906759908</v>
+        <v>11.63527004621301</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>10.44310784911193</v>
+        <v>10.51210797935689</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>8.706599522926048</v>
+        <v>8.775877587758771</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>9.562819799040277</v>
+        <v>9.632885805329742</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>7.127576818358612</v>
+        <v>7.196969696969688</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>8.508634639361205</v>
+        <v>8.578204075143731</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>5.373348192962894</v>
+        <v>5.443060341019518</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>4.074319840743193</v>
+        <v>4.143800206792328</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>4.261363636363633</v>
+        <v>4.330646016760362</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>2.203011712214156</v>
+        <v>2.272948333642809</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>6.672511202026094</v>
+        <v>6.742556917688255</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>8.462437883659724</v>
+        <v>8.53218314532181</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>8.386496544391271</v>
+        <v>8.456350892098548</v>
       </c>
     </row>
   </sheetData>
@@ -3180,2297 +3180,2297 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; 11.27</t>
+          <t>X &gt; 11.43</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3342</v>
+        <v>3345</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.1743184159431124</v>
+        <v>0.1596279459504544</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.1226888108771718</v>
+        <v>0.1081301719723058</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.03717567528680377</v>
+        <v>0.02307718178971641</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.03548552218363454</v>
+        <v>-0.04933100700142745</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.08652522533458296</v>
+        <v>-0.1009130176065938</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.1206577744535835</v>
+        <v>-0.1350703895124283</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.07297605354683867</v>
+        <v>-0.08722717843632921</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.0963071177824304</v>
+        <v>-0.1104668461075349</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.1568774365758614</v>
+        <v>-0.1412370705769916</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.1389387343698161</v>
+        <v>-0.1231009880118563</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.1453586931088324</v>
+        <v>-0.1295851490359183</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.138911476120775</v>
+        <v>-0.123063964131731</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.172442223640644</v>
+        <v>-0.1562562348952881</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.1971756994649141</v>
+        <v>-0.1809033362352608</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-0.1222131626265295</v>
+        <v>-0.1058250961718628</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>-0.1958062662184901</v>
+        <v>-0.2093331164312389</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>-0.2226012790947749</v>
+        <v>-0.2360723405646539</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-0.2799590732475963</v>
+        <v>-0.2933548403374644</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>-0.3149568520889119</v>
+        <v>-0.3283843250936869</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-0.3791841004184064</v>
+        <v>-0.3926092290389178</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>-0.3666309022715026</v>
+        <v>-0.3799244805203088</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-0.3649688617697535</v>
+        <v>-0.3782477830387521</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>-0.31166267925326</v>
+        <v>-0.3250683897539659</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>-0.3997501233634608</v>
+        <v>-0.4130607127390533</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; 14.17</t>
+          <t>X &gt; 14.32</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3305</v>
+        <v>3306</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.0522398307583174</v>
+        <v>-0.06512595958581358</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.08684426034102444</v>
+        <v>-0.1132854687400027</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.007025045335140589</v>
+        <v>-0.06186905822708155</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.01241475782478574</v>
+        <v>-0.06644660431565796</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.0002186990103183462</v>
+        <v>0.005723257185174191</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.09653836141602312</v>
+        <v>-0.1081529153215399</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.009607877724029379</v>
+        <v>-0.02058692321086397</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>3.50540305191771e-05</v>
+        <v>-0.01071083544515972</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.05883797197523677</v>
+        <v>0.04803466341019202</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.03484991286644146</v>
+        <v>-0.04496169669953787</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.07450819063351588</v>
+        <v>-0.08484840940571559</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.1251499480320675</v>
+        <v>-0.1352379268266191</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.2068172157709185</v>
+        <v>-0.2159138731750616</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.1992005593446109</v>
+        <v>-0.1779550693308138</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-0.05569485870190505</v>
+        <v>-0.03391797912110661</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-0.1669196098534727</v>
+        <v>-0.1456173076571403</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-0.1925072139545563</v>
+        <v>-0.1710756219174314</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-0.2795260645625177</v>
+        <v>-0.257971718708184</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-0.3475422850464227</v>
+        <v>-0.326148449202833</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-0.444809610154131</v>
+        <v>-0.4537538733797035</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-0.4260601429761905</v>
+        <v>-0.4345436304221266</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-0.4235476630076604</v>
+        <v>-0.4319694829566387</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-0.4332338976744694</v>
+        <v>-0.4418938813708593</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-0.5214941033875675</v>
+        <v>-0.5300649908690502</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; 17.06</t>
+          <t>X &gt; 17.21</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3251</v>
+        <v>3253</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.006639743159105649</v>
+        <v>-0.0366931732975786</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.05549525564399715</v>
+        <v>0.0115438242402206</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.08278745659453079</v>
+        <v>0.08757953307475219</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.0331667294689737</v>
+        <v>-0.05811639327905738</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.1080251442128528</v>
+        <v>0.1125360945978287</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.06779180237928983</v>
+        <v>0.05485396265238762</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.1383799811184332</v>
+        <v>0.1085933521565323</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.06100444242046166</v>
+        <v>0.03140850982094179</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.1507303424368658</v>
+        <v>0.1210465454397962</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.09894746793840881</v>
+        <v>0.0697118736147786</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.08477229371212047</v>
+        <v>0.08600260021120931</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.06860669211266668</v>
+        <v>0.07000019610394759</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.1490181936578878</v>
+        <v>-0.1468715215343863</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.106926723902852</v>
+        <v>-0.1046840816475054</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>0.0192243351994037</v>
+        <v>0.02175301823128706</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-0.07299595447558005</v>
+        <v>-0.07073959465864021</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-0.1274499635742146</v>
+        <v>-0.1250864993124807</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-0.3062602959793352</v>
+        <v>-0.3037294346134516</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-0.3175720511486801</v>
+        <v>-0.3151539759187472</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-0.419546850998465</v>
+        <v>-0.4171698762811999</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-0.4221954919727509</v>
+        <v>-0.4195168588223694</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>-0.3568975488705064</v>
+        <v>-0.3542172758601225</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>-0.4020371247266965</v>
+        <v>-0.3994813794588552</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>-0.4289728216778954</v>
+        <v>-0.4263587745029014</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; 19.96</t>
+          <t>X &gt; 20.1</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3179</v>
+        <v>3182</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.04912140575079604</v>
+        <v>-0.06383992817735873</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.1157030796048772</v>
+        <v>0.08687608821821868</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.05100261551874752</v>
+        <v>0.07244644212564566</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.05150592118176434</v>
+        <v>-0.06030554811042776</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.1010827318106067</v>
+        <v>0.10421667477695</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.2434019094762903</v>
+        <v>0.2286437739450022</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.3017573975033514</v>
+        <v>0.2697032201359448</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.3541622259751733</v>
+        <v>0.3222134122833253</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.3511405573951834</v>
+        <v>0.3191598541503424</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.4096577746055985</v>
+        <v>0.3780448836123185</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.4517282866356069</v>
+        <v>0.4199301534427136</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.4416102543648748</v>
+        <v>0.4099570983820513</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.2132227916406677</v>
+        <v>0.1823062021866875</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.2927336772634135</v>
+        <v>0.2618751376861326</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>0.4681085713303048</v>
+        <v>0.4688314688616089</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>0.3918797155451088</v>
+        <v>0.3923287436928078</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>0.2765967463063745</v>
+        <v>0.2771889046179083</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>0.2218330414477521</v>
+        <v>0.2225147533575296</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>0.1427300737263053</v>
+        <v>0.1433436639629164</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>0.03436223688344597</v>
+        <v>0.03494172105607163</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-0.01876609095898374</v>
+        <v>-0.01786177751904461</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>0.04985585255528946</v>
+        <v>0.03192040177536626</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>0.0290473747975355</v>
+        <v>0.01106241873456781</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-0.09101210612775645</v>
+        <v>-0.1088739521960562</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; 22.85</t>
+          <t>X &gt; 22.99</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3098</v>
+        <v>3097</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.1596931595363316</v>
+        <v>0.1187929893958</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.1453389474264952</v>
+        <v>0.137486628063975</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.1493343447455615</v>
+        <v>0.145483003197505</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.09732214825208274</v>
+        <v>-0.117599550949592</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.004844814251775631</v>
+        <v>0.02861511789129167</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.08171170898526725</v>
+        <v>0.08704659961849615</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.1300542526712505</v>
+        <v>0.1184398180417716</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.1590972344838022</v>
+        <v>0.115755795265116</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.2191126289444867</v>
+        <v>0.2078672013568621</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.2676469651882982</v>
+        <v>0.2575607120089529</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.3034704596944948</v>
+        <v>0.2929828286243747</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.3004878004878009</v>
+        <v>0.2904084921464332</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.2247348692326696</v>
+        <v>0.2162973293929795</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.215702139562481</v>
+        <v>0.2075859759889127</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>0.2523235320222668</v>
+        <v>0.2451944588755026</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>0.4802400485991711</v>
+        <v>0.4722946513149537</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>0.3654887102017526</v>
+        <v>0.3899384400695922</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>0.2605052941064727</v>
+        <v>0.3044442543221777</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>0.2188134393135073</v>
+        <v>0.281630118815805</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>0.1349935525467458</v>
+        <v>0.1973478853983437</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>0.03020333173083856</v>
+        <v>0.09363421113954473</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>0.00584453535943652</v>
+        <v>0.05006713933664031</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>0.0741014701539271</v>
+        <v>0.09858962457531106</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>-0.1762125347800279</v>
+        <v>-0.151686211256596</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; 25.75</t>
+          <t>X &gt; 25.88</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3011</v>
+        <v>3012</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.006961459881424048</v>
+        <v>0.06040866978019466</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.1009704945933194</v>
+        <v>0.155241917696074</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.2129372474104585</v>
+        <v>0.2373814939129346</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.1046857125308094</v>
+        <v>-0.07900940589993155</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.2090597286621687</v>
+        <v>0.2461386542692594</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.249787975699796</v>
+        <v>0.2678702071875207</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.3217964913144371</v>
+        <v>0.3220946891927454</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.3266916171985486</v>
+        <v>0.3082586575262525</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.4865010050599636</v>
+        <v>0.4679719022683528</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.4926316219409657</v>
+        <v>0.4747361422754111</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.7202063978633717</v>
+        <v>0.7019984791219969</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.7253132501394646</v>
+        <v>0.7073274835914205</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.6136878210164056</v>
+        <v>0.5966675773226413</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.5115319207700182</v>
+        <v>0.4947216575962301</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>0.5020330046550612</v>
+        <v>0.4857670523812416</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>0.7194451202037229</v>
+        <v>0.7026025664196638</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>0.6384875450761882</v>
+        <v>0.6217753530537635</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>0.6329736250021298</v>
+        <v>0.6363727757112727</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>0.6170012972177688</v>
+        <v>0.6401065538449586</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>0.4259950248756255</v>
+        <v>0.4487614779415168</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>0.3339561935236119</v>
+        <v>0.357511187538563</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>0.3111880468098178</v>
+        <v>0.314854738243632</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>0.4399822516423626</v>
+        <v>0.423381890154829</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>0.1847514279998634</v>
+        <v>0.1682910104131778</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; 28.64</t>
+          <t>X &gt; 28.77</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2916</v>
+        <v>2913</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.1116903268549265</v>
+        <v>0.186904082740277</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.390430228308837</v>
+        <v>0.3989488838436515</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.4173054804573511</v>
+        <v>0.43051288334307</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.07868269932421157</v>
+        <v>0.0934987135243901</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.3467262794987391</v>
+        <v>0.4070588903277752</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.2461348470318754</v>
+        <v>0.2864379267327308</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.4144046080187138</v>
+        <v>0.4030743419537899</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.3262625877084133</v>
+        <v>0.2957446470298422</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.4899920381888379</v>
+        <v>0.459495530155607</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.5903332482739714</v>
+        <v>0.5613211638809474</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.5770737014546938</v>
+        <v>0.547532133806591</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.7283585087962621</v>
+        <v>0.699422868066037</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.6845575842325502</v>
+        <v>0.6576579674265659</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.6548292534966507</v>
+        <v>0.6283059812830629</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>0.4957713619130999</v>
+        <v>0.4703457075378381</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>0.8033759051166101</v>
+        <v>0.7770473757451128</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>0.6899545185228249</v>
+        <v>0.6637839049813721</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>0.7562626406255504</v>
+        <v>0.7510787971861319</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>0.7325776500801453</v>
+        <v>0.7475737916979952</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>0.5085217540253453</v>
+        <v>0.543287184789321</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>0.3970840324002651</v>
+        <v>0.4332329511879891</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>0.3075243433813739</v>
+        <v>0.323058119198727</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>0.3423269353006049</v>
+        <v>0.3572307376196875</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>0.3212764421341419</v>
+        <v>0.3157273549765662</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; 31.54</t>
+          <t>X &gt; 31.66</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2796</v>
+        <v>2794</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.204882152968068</v>
+        <v>0.2080481110869243</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.2255785244447353</v>
+        <v>0.2652884189380984</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.3873015479030855</v>
+        <v>0.3953377947111036</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.207316063891426</v>
+        <v>0.2525904751970955</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.5893772397214647</v>
+        <v>0.6651962963062701</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.4408770032168334</v>
+        <v>0.4601453762026466</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.578545690561981</v>
+        <v>0.5791446609509308</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.4274197260880683</v>
+        <v>0.4434848911800344</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.5964552980149662</v>
+        <v>0.5562479105858316</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.6988934187536486</v>
+        <v>0.6595676506363333</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.6732610772426426</v>
+        <v>0.6335975415643418</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.7361306192915151</v>
+        <v>0.6967734138169774</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.6676228059609315</v>
+        <v>0.5938677613308059</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.6818680958383254</v>
+        <v>0.6440415551730183</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>0.5444215306419977</v>
+        <v>0.5073446797886163</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>0.696708651156051</v>
+        <v>0.6589203936470795</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>0.6198829335973528</v>
+        <v>0.6179727410739417</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>0.9080374731847058</v>
+        <v>0.9279413282244349</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>0.8025023087398253</v>
+        <v>0.8436311340910763</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>0.5249285203716951</v>
+        <v>0.5869478544575557</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>0.5394327694074832</v>
+        <v>0.6027025689088603</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>0.3204673455131726</v>
+        <v>0.3836926848082811</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>0.3449743675548262</v>
+        <v>0.3718395519073709</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>0.3262806515573615</v>
+        <v>0.3317982793569669</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; 34.43</t>
+          <t>X &gt; 34.55</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2678</v>
+        <v>2676</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.154874876777086</v>
+        <v>0.1537957437108943</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.1914465740286673</v>
+        <v>0.2282451358372626</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.7591810541804449</v>
+        <v>0.7991546582348406</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.3427855105040223</v>
+        <v>0.3838196864111509</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.7210101492717911</v>
+        <v>0.7920768329115049</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.2972595784302925</v>
+        <v>0.3466025428184025</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.2895118077781049</v>
+        <v>0.3187014779756723</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.2556178521774868</v>
+        <v>0.263704318936874</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.2441361266191251</v>
+        <v>0.2307867389468257</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.2366303012161239</v>
+        <v>0.2236004566402841</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.2346711131504691</v>
+        <v>0.2215173625200464</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.4244869926942272</v>
+        <v>0.4112984870459186</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.1793969142600531</v>
+        <v>0.1668521422977705</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.3159040565125721</v>
+        <v>0.3033400619227109</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>0.08973069908550002</v>
+        <v>0.07760141783058572</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>0.1846876806206552</v>
+        <v>0.1722276852825146</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>0.3342847174384787</v>
+        <v>0.3217590276539184</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>0.6773968950698617</v>
+        <v>0.6872152156335289</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>0.5574483627066797</v>
+        <v>0.5895874292785948</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>0.333737864077662</v>
+        <v>0.3879693434150298</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>0.3133156477608168</v>
+        <v>0.3908991421765933</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>0.05065409473210281</v>
+        <v>0.1282071419035162</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>0.06404016487367414</v>
+        <v>0.1037281922032065</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>-0.01190117439479366</v>
+        <v>0.0652651467527221</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; 37.33</t>
+          <t>X &gt; 37.44</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2559</v>
+        <v>2555</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.390444910857525</v>
+        <v>0.4300527697000973</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.288641624917986</v>
+        <v>0.3290118498076211</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.5992328761177248</v>
+        <v>0.6440118892067019</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.3910793917849418</v>
+        <v>0.4374856064215393</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.6092401785228461</v>
+        <v>0.6860348300176256</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.04042708750676383</v>
+        <v>0.09388142125718701</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.2237234011347908</v>
+        <v>0.2568762511962177</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.1622004866921145</v>
+        <v>0.1734447051575856</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.03135757903611847</v>
+        <v>0.0201519883578456</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.05930788851660651</v>
+        <v>0.01002050803522536</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.04446011620954238</v>
+        <v>-0.005172469530926094</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.2169632239835124</v>
+        <v>0.1676295224102304</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.1044275911273758</v>
+        <v>-0.1524777925250262</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.009558858672278348</v>
+        <v>-0.03825909523036586</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-0.1185309990617966</v>
+        <v>-0.1656067342795495</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>0.07028515169195515</v>
+        <v>0.02249053030303827</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>0.03764099837929535</v>
+        <v>-0.01002286009374842</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>0.08896864129144433</v>
+        <v>0.0648055491603543</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>-0.08568584329530182</v>
+        <v>-0.08701004670075463</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-0.2112641656897196</v>
+        <v>-0.1899116728114052</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>-0.1682981034098319</v>
+        <v>-0.1222363903090269</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>-0.4005642180598699</v>
+        <v>-0.3546381247122596</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>-0.399333404840732</v>
+        <v>-0.3541360149699244</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>-0.318963685101771</v>
+        <v>-0.2734124951990751</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; 40.22</t>
+          <t>X &gt; 40.33</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2431</v>
+        <v>2427</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.5027827711533774</v>
+        <v>0.5839272918182417</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.08570717460897015</v>
+        <v>0.1260988117621054</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.8163588808750077</v>
+        <v>0.903010033444815</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.3892158543321358</v>
+        <v>0.4771766046501469</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.6381966835586965</v>
+        <v>0.7566445406344542</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.05248947886824595</v>
+        <v>0.08224895478762306</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.09935275235265095</v>
+        <v>0.1716620428414828</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.1312585884880875</v>
+        <v>0.1805711887364794</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.008716907098069271</v>
+        <v>0.05798946170943253</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-0.1024776015461413</v>
+        <v>-0.07588555627406635</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-0.05060513312069048</v>
+        <v>-0.02432955765352318</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.0225800893152055</v>
+        <v>0.008115544315181467</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-0.2974115602653242</v>
+        <v>-0.3105806987138777</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.1246226868411568</v>
+        <v>-0.1786491842772477</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>-0.3890841084557408</v>
+        <v>-0.4423733653241726</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>-0.2219364135075494</v>
+        <v>-0.2759495406554251</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>-0.2737594371505168</v>
+        <v>-0.3032025840406973</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-0.1730661769808748</v>
+        <v>-0.1777837524470485</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>-0.3271610313259075</v>
+        <v>-0.2668632648266538</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-0.3869292472233639</v>
+        <v>-0.3028334004026121</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-0.2719642921736067</v>
+        <v>-0.186129465360807</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-0.512460688828142</v>
+        <v>-0.4267879525218774</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-0.4844975338639088</v>
+        <v>-0.3995320286677568</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-0.4370328673734249</v>
+        <v>-0.3517548875770586</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; 43.12</t>
+          <t>X &gt; 43.22</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2292</v>
+        <v>2289</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.8910959855535481</v>
+        <v>0.9085651634509233</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.2950509056918307</v>
+        <v>0.2690430451185222</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.9423069633448264</v>
+        <v>0.9207061902538385</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.402426693629927</v>
+        <v>0.4254273993700863</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.7762873433884891</v>
+        <v>0.8297327039233835</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.180843260743103</v>
+        <v>0.1895330214966009</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.6253684330368969</v>
+        <v>0.6365656175365899</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.3719286767896648</v>
+        <v>0.358354172783514</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.3515492872100623</v>
+        <v>0.3127712632746196</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.4735355350690398</v>
+        <v>0.4105565014740904</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.4249845981460894</v>
+        <v>0.3363357779416276</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.4327208738973525</v>
+        <v>0.3442236941910366</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-0.09954624192926076</v>
+        <v>-0.1870403668502902</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.05378264943757216</v>
+        <v>0.009926886324208795</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>-0.1428759014198278</v>
+        <v>-0.1861946635544811</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>-0.1150060786745399</v>
+        <v>-0.1328732349674766</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>-0.1618397379194505</v>
+        <v>-0.1535922821436699</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-0.09230308420670497</v>
+        <v>-0.05779978866156199</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>-0.4870001656029785</v>
+        <v>-0.4274695020920447</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>-0.2999563699825458</v>
+        <v>-0.2406236921240179</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>-0.2323365346524113</v>
+        <v>-0.1715490649830258</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>-0.3955516251990332</v>
+        <v>-0.3347694256931248</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>-0.2952965285249292</v>
+        <v>-0.2350435118130818</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>-0.371237867793397</v>
+        <v>-0.3108757650363572</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; 46.01</t>
+          <t>X &gt; 46.11</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2179</v>
+        <v>2175</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.7840404598184776</v>
+        <v>0.7796751037004199</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.2202412597603427</v>
+        <v>0.2158557034266479</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>1.021052912729537</v>
+        <v>1.022454153250436</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.07863591412256454</v>
+        <v>0.08045753188373794</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.6735856078365074</v>
+        <v>0.7066459874170974</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.1909187320602186</v>
+        <v>-0.1599837953357266</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.5451314596168899</v>
+        <v>0.5339401730872453</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.5674271770724175</v>
+        <v>0.5305798506429227</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.543936259863635</v>
+        <v>0.4804499917880349</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.8497229813479166</v>
+        <v>0.8069388049865509</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.7388208462526933</v>
+        <v>0.6687217636853546</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.5324075557806083</v>
+        <v>0.4625899917731005</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.1525321825666239</v>
+        <v>-0.2210836341648488</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.1578088640436519</v>
+        <v>0.08947224997729819</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-0.1525069424452568</v>
+        <v>-0.2201187700245413</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-0.01637300571970712</v>
+        <v>-0.1033057851239718</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>0.03310374528970783</v>
+        <v>0.01972075781797145</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-0.02598705951599811</v>
+        <v>-0.01176363402503711</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-0.314682620769581</v>
+        <v>-0.2741726249736018</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-0.2653166590178984</v>
+        <v>-0.2252578494883224</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-0.07423528738253538</v>
+        <v>-0.03217183354631459</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-0.3337607881834685</v>
+        <v>-0.2919258409324286</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-0.2884486781492583</v>
+        <v>-0.2473361859216396</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-0.1349269609698069</v>
+        <v>-0.09328338167365047</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; 48.91</t>
+          <t>X &gt; 49</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2036</v>
+        <v>2032</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.7290097097090822</v>
+        <v>0.7218979846072457</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.05136844164010057</v>
+        <v>-0.005035676487665341</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.6175388190412505</v>
+        <v>0.6157688038931113</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.3897965685159051</v>
+        <v>-0.4403224704515907</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.3701782648553547</v>
+        <v>0.3513380373932904</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.1765123080478403</v>
+        <v>-0.1969898941563883</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.3715608945360955</v>
+        <v>0.4036104415610993</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.4637773321777345</v>
+        <v>0.4685362517099847</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.5825980465536631</v>
+        <v>0.6080626493109733</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>1.307015158385305</v>
+        <v>1.256715600725457</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>1.512468372143488</v>
+        <v>1.481755635044244</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>1.017269880683322</v>
+        <v>0.9868535616023095</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>0.3143422738301567</v>
+        <v>0.2361392637414568</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.6131465841122932</v>
+        <v>0.5351492439376528</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>0.376655603052896</v>
+        <v>0.2993738686743797</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>0.4314406035583573</v>
+        <v>0.382882882882889</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>0.4446946500774089</v>
+        <v>0.4750486268555463</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>0.3888271475381302</v>
+        <v>0.350571259351895</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>0.1629070884660138</v>
+        <v>0.1531058617672869</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>0.1043713163064837</v>
+        <v>0.1431012780345284</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>0.4452573513163856</v>
+        <v>0.4371692832968463</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>0.3201863821177824</v>
+        <v>0.3121107234625455</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>0.3493819808199632</v>
+        <v>0.3405224438186139</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>0.3225565551074752</v>
+        <v>0.3631153874457311</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; 51.8</t>
+          <t>X &gt; 51.89</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1888</v>
+        <v>1887</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.7368664442227981</v>
+        <v>0.7460450641578831</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.2850496937707092</v>
+        <v>-0.2229812056506972</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.546776519375058</v>
+        <v>0.6117270180455776</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.3783216010024688</v>
+        <v>-0.3126434918834207</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.3657588516913961</v>
+        <v>0.4615026106221549</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.02466144673726944</v>
+        <v>0.1199275705038971</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.7837551667698861</v>
+        <v>0.880748442638918</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.9057806043213574</v>
+        <v>0.9725158562367895</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>1.083890057631457</v>
+        <v>1.119711283394622</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>1.557903689528622</v>
+        <v>1.56244042765411</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>2.128548049117512</v>
+        <v>2.100770682923859</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>1.849454145642611</v>
+        <v>1.853689032479686</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>1.233426287735448</v>
+        <v>1.238418705667613</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>1.435798290260415</v>
+        <v>1.47283124289136</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>1.30652806817227</v>
+        <v>1.376594074461735</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>1.265994897454668</v>
+        <v>1.335387776065744</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>0.9200367965260909</v>
+        <v>1.021717106892062</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>1.026917787210465</v>
+        <v>1.128853085635797</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>0.6074477298032903</v>
+        <v>0.70881441886538</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>0.6885593220338961</v>
+        <v>0.7366777169097176</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>0.8868843367647585</v>
+        <v>0.9890441085621191</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>0.8638953828170628</v>
+        <v>0.9661923177942455</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>0.9268061425195313</v>
+        <v>1.028690347711382</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>0.8508648032510635</v>
+        <v>0.9528580944881071</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; 54.7</t>
+          <t>X &gt; 54.77</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1728</v>
+        <v>1724</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.105451589055896</v>
+        <v>0.1474698327797128</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.7490545660962198</v>
+        <v>-0.7656759649917362</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.4078981723565889</v>
+        <v>0.4568023833167842</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.3058951408365687</v>
+        <v>-0.2561516361259564</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.4251997596558326</v>
+        <v>0.5069589902278651</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.4392541591600292</v>
+        <v>0.5204144764987504</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.7627527126224365</v>
+        <v>0.8473668915095089</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.9795078331052522</v>
+        <v>1.031850646293734</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>1.228055570271373</v>
+        <v>1.246848528034931</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>1.29732932490802</v>
+        <v>1.225812551246555</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>1.953077814300919</v>
+        <v>1.904730493003626</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>1.847494610652511</v>
+        <v>1.834133682576642</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>1.278545559549634</v>
+        <v>1.266788542954643</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>1.462281341107875</v>
+        <v>1.486295790645123</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>1.382053805774284</v>
+        <v>1.385191470678883</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>1.398410151691955</v>
+        <v>1.399868247694343</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>1.032834976061558</v>
+        <v>1.069239721631817</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>1.043592300707004</v>
+        <v>1.080408298553095</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>0.6810117599351244</v>
+        <v>0.7162532757651334</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>0.8680555555555571</v>
+        <v>0.9611037261043833</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>1.019299591002046</v>
+        <v>1.056608602221885</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>0.8276037946186889</v>
+        <v>0.9227580004415472</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>1.102378961100818</v>
+        <v>1.197232712923601</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>1.084307992202724</v>
+        <v>1.179405100071563</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 57.6</t>
+          <t>X &gt; 57.66</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1571</v>
+        <v>1567</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.4607386451397915</v>
+        <v>0.5683365600374159</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.4469559534740029</v>
+        <v>-0.4041953403532119</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.9123257707350234</v>
+        <v>0.9001325493913086</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.4529853837505229</v>
+        <v>0.4422805707649005</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1.423593461321886</v>
+        <v>1.445775812503335</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.7837860641505614</v>
+        <v>0.8036603659476569</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>1.601250720900602</v>
+        <v>1.562323926955258</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>1.741992709833127</v>
+        <v>1.730541053630752</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>2.101777393569947</v>
+        <v>2.09090578656587</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>1.709864325257563</v>
+        <v>1.700643171753867</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>1.729608697401538</v>
+        <v>1.719600773099472</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>2.278013202583537</v>
+        <v>2.308434363282871</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>1.853712945267624</v>
+        <v>1.823434389598425</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>1.759663581718954</v>
+        <v>1.729987931786162</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>1.609962132624361</v>
+        <v>1.646190518060102</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>1.632138668560195</v>
+        <v>1.602415346831421</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>1.179776355697079</v>
+        <v>1.213233372585286</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>1.265754110830308</v>
+        <v>1.363657506032766</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>1.163608655047931</v>
+        <v>1.196651631054102</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>1.605267345639717</v>
+        <v>1.638762278290798</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>1.571296726584471</v>
+        <v>1.606745784862092</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>1.304380499713353</v>
+        <v>1.339451195501496</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>1.38819449496696</v>
+        <v>1.422477280032041</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>1.503214326927015</v>
+        <v>1.538093654760274</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 60.49</t>
+          <t>X &gt; 60.55</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>1413</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.7813241388036616</v>
+        <v>0.8145984311224908</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.1632631927590538</v>
+        <v>0.1969362013723952</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>1.057367537725248</v>
+        <v>1.092721961393735</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.485016940232228</v>
+        <v>0.5212106576511317</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1.604895670059669</v>
+        <v>1.670568699955346</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>1.084846704565742</v>
+        <v>1.150321307552012</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>1.655686371663066</v>
+        <v>1.722078422813013</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>2.267980592650808</v>
+        <v>2.29252327226078</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>2.097182432620365</v>
+        <v>2.121846380625271</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>2.172603922063246</v>
+        <v>2.197586998789639</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>2.022334739072427</v>
+        <v>2.047318493851137</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>3.017126185915998</v>
+        <v>3.084797164529931</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>2.246492009183989</v>
+        <v>2.315492139428947</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>2.237449423202712</v>
+        <v>2.306727488035435</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>2.144689450973623</v>
+        <v>2.214755457263088</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>1.961264008733714</v>
+        <v>2.03065688734479</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>1.331770456127607</v>
+        <v>1.401339891910133</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>1.792958306840532</v>
+        <v>1.862670454897156</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>1.79676724471927</v>
+        <v>1.866247610768404</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>2.266896673743815</v>
+        <v>2.336179054140544</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>2.360638939905094</v>
+        <v>2.430575561333747</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>2.001598250858372</v>
+        <v>2.071643966520533</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>2.347144825691537</v>
+        <v>2.416890087353622</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>2.412746303125111</v>
+        <v>2.482600650832389</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 63.39</t>
+          <t>X &gt; 63.44</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1277</v>
+        <v>1274</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0.5936937861051206</v>
+        <v>0.6762643465366338</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.2896414779518963</v>
+        <v>-0.2864559368995216</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.6982226625038663</v>
+        <v>0.7088060187790575</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.0155706506892912</v>
+        <v>-0.004148000663683149</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.9504046700031736</v>
+        <v>0.9944414325975259</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1.059260747379582</v>
+        <v>1.181407618694905</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>1.382714114150929</v>
+        <v>1.351374162434077</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>1.887244824936204</v>
+        <v>1.858092074038922</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>1.458909676176539</v>
+        <v>1.428621642138864</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>1.233234014819786</v>
+        <v>1.205156515552929</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>1.350976210674354</v>
+        <v>1.322230286443272</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>2.089893270394448</v>
+        <v>2.063889046260577</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>1.826795943841532</v>
+        <v>1.804149271398181</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>1.527130597176786</v>
+        <v>1.504577459315797</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>1.024816429400254</v>
+        <v>1.003420033006819</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>1.22833380086972</v>
+        <v>1.20534227677085</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>1.015931571090405</v>
+        <v>0.992932204157583</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>1.302490833147054</v>
+        <v>1.280556178515369</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>1.283688389187709</v>
+        <v>1.260968752532314</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>1.627349256068911</v>
+        <v>1.604800433771928</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>1.867234203374792</v>
+        <v>1.925676557799612</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>1.869587683362575</v>
+        <v>1.928323532026312</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>2.144362849844704</v>
+        <v>2.281291180144152</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>2.225038581837005</v>
+        <v>2.362444798192463</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 66.28</t>
+          <t>X &gt; 66.33</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1117</v>
+        <v>1113</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0.7573915754488425</v>
+        <v>0.806592239667772</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>0.1536395164893918</v>
+        <v>0.2022736623422077</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>1.220653466011136</v>
+        <v>1.190130624092888</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.2382836085028401</v>
+        <v>0.2076348256744112</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>1.573998604141288</v>
+        <v>1.48909502698158</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>1.044959098974395</v>
+        <v>1.047130395468898</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>0.7197205407789085</v>
+        <v>0.7244180098714423</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>1.515472072520872</v>
+        <v>1.524373681021338</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>1.377937108000083</v>
+        <v>1.386166343618882</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>1.230780300632631</v>
+        <v>1.242181485192454</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>1.505139567747968</v>
+        <v>1.60608838701296</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>1.584147723359905</v>
+        <v>1.686728022199276</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>1.623488196904987</v>
+        <v>1.641733071246136</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>1.133554841555508</v>
+        <v>1.151112415823796</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>1.190827720691885</v>
+        <v>1.211747195511883</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>1.338260196454712</v>
+        <v>1.267050559503396</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>0.7565389284472417</v>
+        <v>0.6838971242330132</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>1.009657571438808</v>
+        <v>0.9384454590461573</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>1.0467297048272</v>
+        <v>1.0644895803119</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>1.144247985675918</v>
+        <v>1.161488130621343</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>1.675353753938481</v>
+        <v>1.697109078558277</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>1.68892421306758</v>
+        <v>1.71111037680776</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>2.23227592386484</v>
+        <v>2.255126868265556</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>1.887758040281241</v>
+        <v>1.909752836066538</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 69.18</t>
+          <t>X &gt; 69.22</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>963</v>
+        <v>961</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>1.466065510137049</v>
+        <v>1.510037381885411</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>0.7155213558250182</v>
+        <v>0.7590274930049006</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.7296111305758544</v>
+        <v>0.7778242608313448</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.01581781738269683</v>
+        <v>0.0648702413886042</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.3774431517771291</v>
+        <v>0.457487677270052</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.6684499247008375</v>
+        <v>0.7485121360001088</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.1044162073531893</v>
+        <v>-0.02343654789024185</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>1.278503705799082</v>
+        <v>1.363284369479466</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>1.631546250572491</v>
+        <v>1.716946369292195</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>1.480763799304619</v>
+        <v>1.568380329051749</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>1.9628073862538</v>
+        <v>2.050556516479027</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>1.891397802612758</v>
+        <v>2.083981930929042</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>1.701486023377953</v>
+        <v>1.897344317767001</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>1.272444892509739</v>
+        <v>1.468148896055069</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>1.548093092724777</v>
+        <v>1.746530052168573</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>1.727784502678453</v>
+        <v>1.924683883580862</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>1.178322168861833</v>
+        <v>1.374533656072693</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>0.969496592849616</v>
+        <v>1.165634679618847</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>1.081777595864509</v>
+        <v>1.277467787910489</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>0.7496105919003071</v>
+        <v>0.8399639620824644</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>1.556358261822403</v>
+        <v>1.650175338341207</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>1.376561046262857</v>
+        <v>1.470271104299428</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>2.37823133216348</v>
+        <v>2.47315372521021</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>2.71765863256271</v>
+        <v>2.813554562517631</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; 72.07</t>
+          <t>X &gt; 72.11</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>828</v>
+        <v>825</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>1.156796468645339</v>
+        <v>1.147031674446815</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0.9423939008609139</v>
+        <v>0.9334669973091252</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>1.193514692813423</v>
+        <v>1.192417645247829</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.1241433546792408</v>
+        <v>-0.1265969802555063</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.4767704351759292</v>
+        <v>0.5073095168941819</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>1.871664516781756</v>
+        <v>1.906396915112772</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>1.21957133158763</v>
+        <v>1.255660352434539</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>2.873383835827525</v>
+        <v>2.916842847075408</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>2.43180811341054</v>
+        <v>2.47348154414162</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>2.74492922438025</v>
+        <v>2.791474959014231</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>3.381607332075298</v>
+        <v>3.307958843600396</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>3.223286375460283</v>
+        <v>3.15042156136451</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>2.944205784992469</v>
+        <v>2.875744342993251</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>2.118984239658595</v>
+        <v>2.048604860486051</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>2.909328362940144</v>
+        <v>2.845007017450953</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>2.658977784542195</v>
+        <v>2.590909090909093</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>2.283338196673462</v>
+        <v>2.214567711507371</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>1.816035939998471</v>
+        <v>1.746090644049829</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>2.032159102930287</v>
+        <v>1.961982024974155</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>1.736111111111114</v>
+        <v>1.663979350093705</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>2.279867223852285</v>
+        <v>2.212342273036761</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>1.962366274489867</v>
+        <v>1.894072069203411</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>3.444870909571037</v>
+        <v>3.380667993806675</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>4.455886092041688</v>
+        <v>4.3957448314925</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &gt; 74.97</t>
+          <t>X &gt; 75</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>1.247419250454627</v>
+        <v>1.230213058487806</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>1.340203792871641</v>
+        <v>1.181969211427386</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>1.897650261738427</v>
+        <v>1.749680821422182</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.1852834820688045</v>
+        <v>0.1771279481112487</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>2.102467334705246</v>
+        <v>2.133601085879164</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>4.286778880664954</v>
+        <v>4.32629793100233</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>2.943299339195804</v>
+        <v>2.838016868888488</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>4.804544978983948</v>
+        <v>4.708802558805893</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>4.703407691652806</v>
+        <v>4.607023265075895</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>5.213452452067393</v>
+        <v>5.123505869841694</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>5.48781171918273</v>
+        <v>5.397565512003617</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>4.780757758646487</v>
+        <v>4.832283157266225</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>4.226879949574467</v>
+        <v>4.282186992988905</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>3.434909729124989</v>
+        <v>3.488042213963517</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>4.202512013625501</v>
+        <v>4.262563672829963</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>4.084305301477976</v>
+        <v>4.140618216549441</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>3.379598197913936</v>
+        <v>3.433635176993178</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>2.846654724757315</v>
+        <v>2.755728570593199</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>3.205431240042898</v>
+        <v>3.114886427162226</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>2.679208273894439</v>
+        <v>2.585399858906754</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>2.99192797901916</v>
+        <v>2.902452544808916</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>2.488012866315216</v>
+        <v>2.396807156465719</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>3.761361499273804</v>
+        <v>3.674147198460666</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>4.826646978835576</v>
+        <v>4.744446750394992</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &gt; 77.86</t>
+          <t>X &gt; 77.89</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>2.017647420869174</v>
+        <v>1.895181006075937</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>2.382997300270375</v>
+        <v>2.439138829870245</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>2.869741669809457</v>
+        <v>2.934335949556299</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>2.50621105363907</v>
+        <v>2.572875778971195</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>3.366860708194707</v>
+        <v>3.467313777425687</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>5.480470154826712</v>
+        <v>5.587496132240105</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>3.306553234681623</v>
+        <v>3.409572052919174</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>5.304706119811037</v>
+        <v>5.416070625740801</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>5.171090836322293</v>
+        <v>5.106063958797861</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>5.272912168109784</v>
+        <v>5.21188290490548</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>5.54727143522512</v>
+        <v>5.661689471496224</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>5.093046183238833</v>
+        <v>5.207193143619406</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>4.143686313263075</v>
+        <v>4.25977800119211</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>3.0466727596718</v>
+        <v>3.159964502601412</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>3.613660960214183</v>
+        <v>3.732049676022598</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>3.683326964301415</v>
+        <v>3.799195824679131</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>3.023839224618335</v>
+        <v>3.138037914415193</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>2.568593111500292</v>
+        <v>2.681703361736368</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>2.084190880386572</v>
+        <v>2.1946070449454</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>1.57070928196147</v>
+        <v>1.502718232769318</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>1.72803426700905</v>
+        <v>1.663159762518575</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>1.827210559877827</v>
+        <v>1.93880764996711</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>2.802511120405491</v>
+        <v>2.740523135735643</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>4.653014614762235</v>
+        <v>4.597907051229406</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &gt; 80.76</t>
+          <t>X &gt; 80.78</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>3.656294349172619</v>
+        <v>3.721790249205391</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>2.883482073040319</v>
+        <v>2.727672791514919</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>4.069602177881983</v>
+        <v>3.92701637984657</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>4.231082387664749</v>
+        <v>4.093183239524706</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>6.053996410080529</v>
+        <v>5.955194964779629</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>8.866981592015108</v>
+        <v>8.779523788239644</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>5.468294891033288</v>
+        <v>5.370212466986658</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>7.377924052954555</v>
+        <v>7.289803220035779</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>6.76298497574524</v>
+        <v>6.671949742609819</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>5.989149564975811</v>
+        <v>5.899034066573329</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>6.044690451347165</v>
+        <v>5.953313488955033</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>5.546778167128281</v>
+        <v>5.454783865726817</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>4.64110532938512</v>
+        <v>4.551402018650919</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>3.763293376118817</v>
+        <v>3.670982482863671</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>4.854909183033364</v>
+        <v>4.771080943524872</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>4.793514090422796</v>
+        <v>4.706127206127206</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>3.784146873297949</v>
+        <v>3.69308919002885</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>3.241526695714711</v>
+        <v>3.14868804664723</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>2.363557954926613</v>
+        <v>2.265678328670461</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>2.112964989059087</v>
+        <v>2.01296369907805</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>1.569764580061133</v>
+        <v>1.47041753111202</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>1.274991143674534</v>
+        <v>1.1747913499227</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>2.425039833132601</v>
+        <v>2.328386941525629</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>4.318463920559971</v>
+        <v>4.230576666324325</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &gt; 83.65</t>
+          <t>X &gt; 83.67</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>3.119356855118774</v>
+        <v>3.034902205369129</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>3.32765960134401</v>
+        <v>3.245084535084708</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>4.877089572040482</v>
+        <v>4.804340690413383</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>3.891557128412536</v>
+        <v>3.818907106937942</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>6.515417778171106</v>
+        <v>6.480391838750343</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>10.50693021726484</v>
+        <v>10.48207192130549</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>7.831890172167341</v>
+        <v>7.802766289186259</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>9.727248570127045</v>
+        <v>9.704391356694771</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>8.410068982975758</v>
+        <v>8.383480718445981</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>7.364494441771548</v>
+        <v>7.338085478376797</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>7.638853708886884</v>
+        <v>7.61214512053872</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>5.729325022803287</v>
+        <v>5.69851833289453</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>4.333094673881362</v>
+        <v>4.302876702005719</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>4.655216123716563</v>
+        <v>4.626756953624522</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>5.626719667287965</v>
+        <v>5.603491040240151</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>6.221779716909346</v>
+        <v>6.197877962183142</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>5.000729501021297</v>
+        <v>4.974042569074882</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>4.35226782405644</v>
+        <v>4.3242427371883</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>4.0249127261187</v>
+        <v>4.267654554079925</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>2.853260869565219</v>
+        <v>2.819622979851765</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>2.038321330132476</v>
+        <v>2.004597247853042</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>1.962366274489867</v>
+        <v>1.928751286443941</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>3.052358832276347</v>
+        <v>3.020664691024088</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>4.335113145181786</v>
+        <v>4.307230257964299</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &gt; 86.55</t>
+          <t>X &gt; 86.56</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>286</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>2.969235237605851</v>
+        <v>3.00250952992468</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>4.032661121562917</v>
+        <v>4.066334130176259</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>2.942611007127134</v>
+        <v>2.977965430795621</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>3.627419092535376</v>
+        <v>3.66361280995428</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>6.409002454364476</v>
+        <v>6.474675484260153</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>9.043719514923708</v>
+        <v>9.109194117909979</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>7.921203033219321</v>
+        <v>7.987595084369268</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>9.041249786302174</v>
+        <v>9.107985038217606</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>6.984863753422701</v>
+        <v>7.051570122230203</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>5.162077293702232</v>
+        <v>5.229703397242673</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>5.436436560817569</v>
+        <v>5.503763039404596</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>4.45804195804196</v>
+        <v>4.525712936655893</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>2.98390038990447</v>
+        <v>3.052900520149429</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>4.510795327121862</v>
+        <v>4.580073391954585</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>4.9008151370356</v>
+        <v>4.970881143325066</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>5.146224837006649</v>
+        <v>5.215617715617725</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>4.312830443557019</v>
+        <v>4.382399879339545</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>3.508546328161046</v>
+        <v>3.57825847621767</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>3.724669491092861</v>
+        <v>3.794149857141996</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>2.86276223776224</v>
+        <v>2.932044618158969</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>2.319561828764286</v>
+        <v>2.389498450192939</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>2.243606773121677</v>
+        <v>2.313652488783838</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>2.518381939603806</v>
+        <v>2.588127201265891</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>3.491391649286392</v>
+        <v>3.561245996993669</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &gt; 89.44</t>
+          <t>X &gt; 89.45</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>208</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>4.01818628655689</v>
+        <v>4.051460578875719</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>4.644549233451031</v>
+        <v>4.678222242064372</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>4.647156461672587</v>
+        <v>4.682510885341074</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>4.894901610017897</v>
+        <v>4.9310953274368</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>6.933477978839996</v>
+        <v>6.999151008735673</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>11.9283348995391</v>
+        <v>11.99380950252537</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>10.67469953671584</v>
+        <v>10.74109158786579</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>13.28076027581267</v>
+        <v>13.3474955277281</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>9.956891725450674</v>
+        <v>10.02359809425818</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>8.702287083912005</v>
+        <v>8.769913187452445</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>8.015107889488888</v>
+        <v>8.082434368075916</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>5.81293706293706</v>
+        <v>5.880608041550992</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>3.726907382911456</v>
+        <v>3.795907513156415</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>4.467089033415562</v>
+        <v>4.536367098248284</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>5.250465486685961</v>
+        <v>5.320531492975427</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>5.364756305538116</v>
+        <v>5.434149184149192</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>4.749893380619966</v>
+        <v>4.819462816402492</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>4.644909964524686</v>
+        <v>4.71462211258131</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>5.341802358225728</v>
+        <v>5.411282724274862</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>4.08653846153846</v>
+        <v>4.155820841935189</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>4.50487651407898</v>
+        <v>4.574813135507632</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>3.467382996897896</v>
+        <v>3.537428712560057</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>4.222927394149252</v>
+        <v>4.292672655811337</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>3.185447593342325</v>
+        <v>3.255301941049602</v>
       </c>
     </row>
     <row r="34">
@@ -5483,76 +5483,76 @@
         <v>135</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>7.807360075730685</v>
+        <v>7.840634368049514</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>3.027740116641915</v>
+        <v>3.061413125255257</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>3.069521134037252</v>
+        <v>3.104875557705739</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>3.837209302325583</v>
+        <v>3.873403019744487</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>7.175643221005245</v>
+        <v>7.241316250900923</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>11.80725227845647</v>
+        <v>11.87272688144274</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>11.77512688714318</v>
+        <v>11.84151893829313</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>15.94101668606906</v>
+        <v>16.00775193798449</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>13.76031052886948</v>
+        <v>13.82701689767698</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>10.02351215513709</v>
+        <v>10.09113825867753</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>11.03861216299316</v>
+        <v>11.10593864158019</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>7.796555296555297</v>
+        <v>7.86422627516923</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>4.449841855845939</v>
+        <v>4.518841986090898</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>5.709966526293066</v>
+        <v>5.779244591125789</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>3.569553805774284</v>
+        <v>3.639619812063749</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>2.683132373914177</v>
+        <v>2.752525252525253</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>2.549038679765253</v>
+        <v>2.618608115547779</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>3.184796004410714</v>
+        <v>3.254508152467338</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>6.363882130305491</v>
+        <v>6.433362496354626</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>5.069444444444443</v>
+        <v>5.138726824841171</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>5.266984776187236</v>
+        <v>5.336921397615889</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>3.709548239063146</v>
+        <v>3.779593954725307</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>4.725064146286009</v>
+        <v>4.794809407948094</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>3.16764132553606</v>
+        <v>3.237495673243338</v>
       </c>
     </row>
     <row r="35">
@@ -5565,76 +5565,76 @@
         <v>69</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>4.296893087002829</v>
+        <v>4.330167379321658</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-1.835383876916865</v>
+        <v>-1.801710868303523</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>3.971292470591202</v>
+        <v>4.006646894259688</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>1.808223795079208</v>
+        <v>1.844417512498111</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>5.790780097011677</v>
+        <v>5.856453126907354</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>16.12287224625035</v>
+        <v>16.18834684923662</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>13.90073075187748</v>
+        <v>13.96712280302743</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>17.97000219331545</v>
+        <v>18.03673744523088</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>15.1129675337004</v>
+        <v>15.1796739025079</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>12.88985676061213</v>
+        <v>12.95748286415257</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>11.71494066540862</v>
+        <v>11.78226714399565</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>4.189469950339515</v>
+        <v>4.257140928953447</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-1.282847355104145</v>
+        <v>-1.213847224859187</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>2.843621920818016</v>
+        <v>2.912899985650739</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>-2.163135405175801</v>
+        <v>-2.093069398886335</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>-1.56807535555442</v>
+        <v>-1.498682476943344</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>-3.151444412022187</v>
+        <v>-3.081874976239661</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>1.091398258839064</v>
+        <v>1.161110406895688</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>8.553898233365082</v>
+        <v>8.623378599414217</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>5.842391304347828</v>
+        <v>5.911673684744557</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>8.197741619987561</v>
+        <v>8.267678241416213</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>0.8754097527507483</v>
+        <v>0.9454554684129093</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>1.150184919232878</v>
+        <v>1.219930180894963</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>-1.824307144673277</v>
+        <v>-1.754452796966</v>
       </c>
     </row>
   </sheetData>
@@ -5824,2297 +5824,2297 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; 11.27</t>
+          <t>X &lt; 11.43</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-11.02706258222138</v>
+        <v>-10.16258624386675</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-9.891649861571594</v>
+        <v>-9.048087679897726</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-6.919585619775376</v>
+        <v>-6.138280641972187</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-4.692202462380301</v>
+        <v>-3.952683936777255</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-2.116295776816116</v>
+        <v>-1.389923684686842</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.4585429285152074</v>
+        <v>0.2463178637293737</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-2.701997295863357</v>
+        <v>-1.974906182479813</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-1.509963706087795</v>
+        <v>-0.8038422649140529</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>1.472728829523078</v>
+        <v>0.6869202793194944</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.6988934187536486</v>
+        <v>-0.08599539671699574</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.9732526858689852</v>
+        <v>0.1880642454449273</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.6941587823940836</v>
+        <v>-0.09068515800306898</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>2.510844034495172</v>
+        <v>1.6847034997785</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>3.760075458754933</v>
+        <v>2.912899985650739</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>0.1599677491293932</v>
+        <v>-0.643794036567499</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>3.696204269339013</v>
+        <v>4.298418972332009</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>5.032698810484206</v>
+        <v>5.613777197673386</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>7.868891864977172</v>
+        <v>8.407487218489891</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>9.555603263203089</v>
+        <v>10.07265396173305</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>12.68382352941177</v>
+        <v>13.15805049633876</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>12.14062312041381</v>
+        <v>12.61550432837273</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>12.0646680647712</v>
+        <v>12.53965836696363</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>9.398266760665088</v>
+        <v>9.915582354807995</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>13.73409012727898</v>
+        <v>14.18757618854124</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; 14.17</t>
+          <t>X &lt; 14.32</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.09946349990958225</v>
+        <v>0.4875932535405099</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.2764173653191619</v>
+        <v>1.070247647851247</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-3.068045003528873</v>
+        <v>-1.285202593840296</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-3.78183831672203</v>
+        <v>-1.998156613283037</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-4.147108101746078</v>
+        <v>-4.168809471151413</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-1.102800631596438</v>
+        <v>-0.7198657111498505</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-3.78042866841237</v>
+        <v>-3.343666246892049</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-4.058983313930931</v>
+        <v>-3.621877691645125</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-5.922229153670209</v>
+        <v>-5.432242361582283</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-2.886540754915821</v>
+        <v>-2.501454333915063</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-1.659800535419535</v>
+        <v>-1.301468765827224</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.03413253413252448</v>
+        <v>0.2716336825766419</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>2.650900056904135</v>
+        <v>2.852175319424227</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>2.42954324586978</v>
+        <v>1.705170517051712</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-2.038911802691324</v>
+        <v>-2.656676484232555</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>1.413291104072911</v>
+        <v>0.7154882154882145</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>2.231578362304937</v>
+        <v>1.507497004436672</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>4.983737803352511</v>
+        <v>4.180434078393262</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>7.104622871046224</v>
+        <v>6.248177311169449</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>10.14880952380952</v>
+        <v>10.13872682484117</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>9.605609114811564</v>
+        <v>9.596180656875141</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>9.529654059168955</v>
+        <v>9.52033469546604</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>9.804429225651084</v>
+        <v>9.794809407948094</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>12.58563074352548</v>
+        <v>12.49675493250259</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; 17.06</t>
+          <t>X &lt; 17.21</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.8790903498501734</v>
+        <v>-0.2666139845976048</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-2.75929692039513</v>
+        <v>-1.828384647978105</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-3.876670340456101</v>
+        <v>-3.879900629524428</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-2.074740383209011</v>
+        <v>-1.525369986390487</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-4.955733438673306</v>
+        <v>-4.928645121514442</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-4.139638008056458</v>
+        <v>-3.806285464236275</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-5.541434957720547</v>
+        <v>-4.8734569071175</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-3.933197150408922</v>
+        <v>-3.28831431460349</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-5.778473538216474</v>
+        <v>-5.110181169955872</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-4.665516496155718</v>
+        <v>-4.019742808725276</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-4.391157229040381</v>
+        <v>-4.366801178985718</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-4.041320314905221</v>
+        <v>-4.024432570011349</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.4945658250981992</v>
+        <v>0.4424674749337711</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.3557218035462171</v>
+        <v>-0.3997294139351766</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>-2.901445495413704</v>
+        <v>-2.921226748782821</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-1.048523810572199</v>
+        <v>-1.084603801995108</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>0.07524413049900147</v>
+        <v>0.02371508587214066</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>3.7438456200641</v>
+        <v>3.645582456585117</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>3.959968782995915</v>
+        <v>3.861473837509443</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>6.033805031446533</v>
+        <v>5.911673684744557</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>6.119535440058648</v>
+        <v>5.990245529200884</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>4.785718749195915</v>
+        <v>4.672163542947068</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>5.689424733288099</v>
+        <v>5.567756267851479</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>6.242414211629701</v>
+        <v>6.113042027050561</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; 19.96</t>
+          <t>X &lt; 20.1</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.02605273622290127</v>
+        <v>0.1727122086019293</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-2.716193472119258</v>
+        <v>-2.280708657544494</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-2.202244137728016</v>
+        <v>-2.447541265897513</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-1.184435719319438</v>
+        <v>-1.041851217543652</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-3.281307235945221</v>
+        <v>-3.270898091100662</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-5.258644787440595</v>
+        <v>-4.99336998465413</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-6.031510919494622</v>
+        <v>-5.545224027848981</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-6.742965997913622</v>
+        <v>-6.252620021958279</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-6.701449932890988</v>
+        <v>-6.211132840043575</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-7.475285343660417</v>
+        <v>-6.984048516080065</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-8.066726942345937</v>
+        <v>-7.568357972630579</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-7.912920412920414</v>
+        <v>-7.417922826722361</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-4.708407302403231</v>
+        <v>-4.249239400016243</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-5.795564979238442</v>
+        <v>-5.328687375175278</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-8.186097949877485</v>
+        <v>-8.132753419536961</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-7.158137467355658</v>
+        <v>-7.10918194823774</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-5.560629429902853</v>
+        <v>-5.526360887790318</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-4.799811980197269</v>
+        <v>-4.772832492899056</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-3.71788795146459</v>
+        <v>-3.698572013262293</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-2.232142857142861</v>
+        <v>-2.224172555225593</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-1.476641967439512</v>
+        <v>-1.47916507512295</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-2.418397888882986</v>
+        <v>-2.165489059323228</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>-2.143622722400856</v>
+        <v>-1.891014346841175</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-0.4879623300675959</v>
+        <v>-0.242708669029966</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; 22.85</t>
+          <t>X &lt; 22.99</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-2.091842924738138</v>
+        <v>-1.640847113431967</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-2.263265174363369</v>
+        <v>-2.123772059929934</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-2.582755346264697</v>
+        <v>-2.472466490224534</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.4303066212413</v>
+        <v>-0.2259758622430965</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-1.43251908142458</v>
+        <v>-1.633727016665723</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-2.200768481156651</v>
+        <v>-2.212921266705408</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-2.655163275631054</v>
+        <v>-2.501915405141219</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-2.933717921149615</v>
+        <v>-2.466647226069838</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-3.529144531286221</v>
+        <v>-3.365598915628482</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-3.984508604476034</v>
+        <v>-3.825034967840523</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-4.34709201251993</v>
+        <v>-4.177934573327505</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-4.307714578415215</v>
+        <v>-4.143204352951045</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-3.521377771424653</v>
+        <v>-3.385488676860454</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-3.424263244879384</v>
+        <v>-3.293087929482596</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-3.764723146337069</v>
+        <v>-3.637751603238712</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-6.03590513493225</v>
+        <v>-5.864681295715776</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-4.8961134787627</v>
+        <v>-5.058159561219902</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-3.867623827561829</v>
+        <v>-4.222561393567723</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>-3.472300205876842</v>
+        <v>-4.006670012643397</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-2.644230769230774</v>
+        <v>-3.192864955026465</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-1.584867075664619</v>
+        <v>-2.168013003870243</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>-1.34030931079441</v>
+        <v>-1.748009120047584</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>-2.027072605850748</v>
+        <v>-2.236385825139884</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>0.4610886189833536</v>
+        <v>0.2114412276305373</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; 25.75</t>
+          <t>X &lt; 25.88</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.4562996235725763</v>
+        <v>-0.8427935854514317</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-1.403837863323169</v>
+        <v>-1.780501960562269</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-2.463922757615592</v>
+        <v>-2.601907019492479</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.3024415704923769</v>
+        <v>-0.489342078294726</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-2.662723824344354</v>
+        <v>-2.899733890149228</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-2.974312328544549</v>
+        <v>-3.07345082335565</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-3.497801901995082</v>
+        <v>-3.467123037015519</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-3.526979988910156</v>
+        <v>-3.36518535574487</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-4.732346716904978</v>
+        <v>-4.561321936206404</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-4.758052451863932</v>
+        <v>-4.59166335481715</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-6.478705653576526</v>
+        <v>-6.297801732457209</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-6.508422998447926</v>
+        <v>-6.329026383429962</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-5.637901748107147</v>
+        <v>-5.471990430484098</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-4.86175232472754</v>
+        <v>-4.702970297029694</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-4.772553887954359</v>
+        <v>-4.618539337184508</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-6.421882865764402</v>
+        <v>-6.251875187518749</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-5.807846884102858</v>
+        <v>-5.643218067070478</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-5.778166958552248</v>
+        <v>-5.74805877089166</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-5.67733201617181</v>
+        <v>-5.779692142442585</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-4.23715538847118</v>
+        <v>-4.35522257009832</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-3.52722296538893</v>
+        <v>-3.660144975688105</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>-3.352551454615501</v>
+        <v>-3.348427366844405</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>-4.330909120213569</v>
+        <v>-4.176998220575953</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>-2.401837928153718</v>
+        <v>-2.262780722555448</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; 28.64</t>
+          <t>X &lt; 28.77</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>494</v>
+        <v>501</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.9795106273076755</v>
+        <v>-1.39035787664136</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-2.80929692039512</v>
+        <v>-2.799153323546491</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-3.144388166044386</v>
+        <v>-3.154310937237142</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-1.343513589240679</v>
+        <v>-1.40218753143661</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-2.913602651373161</v>
+        <v>-3.207949582980298</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-2.324831612663559</v>
+        <v>-2.520480555242955</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-3.298500957568997</v>
+        <v>-3.185983811981892</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-2.773842751681933</v>
+        <v>-2.563676633444068</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-3.736342750916329</v>
+        <v>-3.514252943592865</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-4.309374948834353</v>
+        <v>-4.088755921216652</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-4.235818894570421</v>
+        <v>-4.013108977467432</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-5.117322436599537</v>
+        <v>-4.887096476153516</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-4.836191165126849</v>
+        <v>-4.621369654120755</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-4.655941550458387</v>
+        <v>-4.44562313374194</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-3.708447086684444</v>
+        <v>-3.516464844020916</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-5.523025591279925</v>
+        <v>-5.303030303030305</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>-4.85390643402323</v>
+        <v>-4.64329664635698</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-5.251003980685041</v>
+        <v>-5.144962747003568</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-5.126559924652696</v>
+        <v>-5.127484064491938</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-3.819444444444443</v>
+        <v>-3.94857476246041</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-3.150523641321186</v>
+        <v>-3.300644739950258</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-2.620418090903186</v>
+        <v>-2.66764851637403</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-2.836789205041029</v>
+        <v>-2.87672666996248</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-2.71030139451193</v>
+        <v>-2.639638946406251</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; 31.54</t>
+          <t>X &lt; 31.66</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>614</v>
+        <v>620</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-1.18615992902528</v>
+        <v>-1.184428729913748</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-1.436949653514098</v>
+        <v>-1.594671530829395</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-2.30890076612377</v>
+        <v>-2.313483978300845</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-1.646661665416353</v>
+        <v>-1.827233922930667</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-3.37781815636567</v>
+        <v>-3.671318872260521</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-2.70600087776922</v>
+        <v>-2.761044269900296</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-3.317316121293366</v>
+        <v>-3.28736995059576</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-2.6265654356326</v>
+        <v>-2.678145497912944</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-3.392803813259405</v>
+        <v>-3.1909963001115</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-3.843537446969059</v>
+        <v>-3.642884688828573</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-3.73072906838361</v>
+        <v>-3.529338690326355</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-4.009822971858512</v>
+        <v>-3.808088093774352</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-3.680356193576671</v>
+        <v>-3.326113724033362</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-3.740162116081137</v>
+        <v>-3.547192600479953</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-3.106686246879342</v>
+        <v>-2.921226748782821</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-3.804033305497057</v>
+        <v>-3.61094897611752</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-3.453474334056324</v>
+        <v>-3.423838825775562</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-4.761985728778782</v>
+        <v>-4.812788678874433</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-4.294620781033721</v>
+        <v>-4.436383654290395</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-3.043831168831169</v>
+        <v>-3.286455982364103</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>-3.100018590816134</v>
+        <v>-3.347461219351004</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>-2.107976602851949</v>
+        <v>-2.367839652515379</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>-2.227523620634003</v>
+        <v>-2.322742926995545</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>-2.140598510391065</v>
+        <v>-2.144822128429304</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; 34.43</t>
+          <t>X &lt; 34.55</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>732</v>
+        <v>738</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.7804471123456835</v>
+        <v>-0.7703531214426462</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-1.044337351661973</v>
+        <v>-1.168137280765741</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-3.222276736707975</v>
+        <v>-3.338676428014914</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-1.838466373350094</v>
+        <v>-1.971101001703232</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-3.212769549004285</v>
+        <v>-3.442253224614866</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-1.672424963061097</v>
+        <v>-1.839937395737671</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-1.633383111353282</v>
+        <v>-1.731084620851483</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-1.50598376499093</v>
+        <v>-1.530433147370402</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-1.464467699968296</v>
+        <v>-1.413648869304573</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-1.426395126975876</v>
+        <v>-1.376847946150782</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-1.422671854447827</v>
+        <v>-1.372693837052289</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-2.107719749803643</v>
+        <v>-2.056301540095433</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-1.20244100888619</v>
+        <v>-1.155172108975833</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-1.694433814507825</v>
+        <v>-1.646156518485853</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>-0.8648670833150831</v>
+        <v>-0.8198193842175527</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>-1.217033014749177</v>
+        <v>-1.170101827996568</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>-1.757080700779028</v>
+        <v>-1.708877264569175</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-3.00309920787474</v>
+        <v>-3.028292867175786</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>-2.574255464548521</v>
+        <v>-2.677448719719742</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>-1.766304347826086</v>
+        <v>-1.95079184362487</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>-1.686907891991147</v>
+        <v>-1.953526945464034</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>-0.7298502875288406</v>
+        <v>-1.005190830059483</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>-0.7835003527286943</v>
+        <v>-0.9216242110565673</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>-0.5057041510881035</v>
+        <v>-0.7823778588253134</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; 37.33</t>
+          <t>X &lt; 37.44</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>851</v>
+        <v>859</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-1.353935790901602</v>
+        <v>-1.456939067454954</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-1.163768465110572</v>
+        <v>-1.271366144232871</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-2.193183430992889</v>
+        <v>-2.303043882471762</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-1.680834935159858</v>
+        <v>-1.801337464684579</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-2.332256286894264</v>
+        <v>-2.536290455112258</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.6299401587359696</v>
+        <v>-0.784091786936628</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-1.169706057689758</v>
+        <v>-1.26033291355872</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.9820602370078575</v>
+        <v>-1.010401789323346</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.5908938223348699</v>
+        <v>-0.555555930371483</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.665428533803599</v>
+        <v>-0.5164066412107644</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-0.6241694997885006</v>
+        <v>-0.4743655605337551</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-1.13636363636364</v>
+        <v>-0.9851335254666793</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.1629527569486768</v>
+        <v>-0.02012853895851663</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.5008596845331468</v>
+        <v>-0.3572166961475673</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-0.1108398746193942</v>
+        <v>0.02872353295400387</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>-0.6812809904991894</v>
+        <v>-0.5369823525276018</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>-0.5822744515478746</v>
+        <v>-0.4388809280201471</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-0.7349930962418654</v>
+        <v>-0.6597309125837896</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>-0.2162494030970663</v>
+        <v>-0.2118209701745499</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>0.1571637426900594</v>
+        <v>0.09103412053593729</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>0.03496118350790312</v>
+        <v>-0.1034842052027116</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>0.7326909597439624</v>
+        <v>0.5869239327869877</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>0.7266290915129261</v>
+        <v>0.5829231030385387</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>0.4866995141594685</v>
+        <v>0.3443813715143662</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; 40.22</t>
+          <t>X &lt; 40.33</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>979</v>
+        <v>987</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-1.403687500604477</v>
+        <v>-1.588795061379912</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.4739433850415864</v>
+        <v>-0.5688102845272667</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-2.365074229779545</v>
+        <v>-2.555067233631227</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-1.405705677431506</v>
+        <v>-1.608524691098886</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-2.019448527278001</v>
+        <v>-2.291533181446006</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.3125270753654377</v>
+        <v>-0.6416184498039925</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.6801247170445919</v>
+        <v>-0.8540164762755182</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.7560451173757201</v>
+        <v>-0.8739684921230193</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.4105776845719333</v>
+        <v>-0.5737006715572406</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-0.1712418694041702</v>
+        <v>-0.2366264384110863</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-0.3021510926637063</v>
+        <v>-0.3661994904974009</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.4799278735448951</v>
+        <v>-0.4431325468212819</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.3206062372486116</v>
+        <v>0.350960684001727</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.1033848189731827</v>
+        <v>0.0289736339930684</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>0.5548065357078613</v>
+        <v>0.6826365927192697</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>0.136695359392057</v>
+        <v>0.2679417790416849</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>0.2659645305653413</v>
+        <v>0.3358409891883269</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>0.0187873561685592</v>
+        <v>0.02918393824302967</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>0.3973057978755037</v>
+        <v>0.2450753191673556</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>0.5436164801627683</v>
+        <v>0.3310129555733141</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>0.2650989800040762</v>
+        <v>0.05072611142059458</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>0.8621136485092862</v>
+        <v>0.6421187646717499</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>0.7908237834742238</v>
+        <v>0.5730370282809787</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>0.6745455740133437</v>
+        <v>0.4569035309490701</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; 43.12</t>
+          <t>X &lt; 43.22</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1118</v>
+        <v>1125</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-1.953026966209755</v>
+        <v>-1.974180446765295</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.8290849062608459</v>
+        <v>-0.771058503528927</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-2.221764846903895</v>
+        <v>-2.162324858879551</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-1.207038485285032</v>
+        <v>-1.245330489490343</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-1.966501581015557</v>
+        <v>-2.060979002098563</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.7557894867129562</v>
+        <v>-0.7688133371899895</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-1.656796606892108</v>
+        <v>-1.668181238073714</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-1.136770950724781</v>
+        <v>-1.103163037008144</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-1.095254885702147</v>
+        <v>-1.012009407780418</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-1.336703428680984</v>
+        <v>-1.204666830231012</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-1.239806450829178</v>
+        <v>-1.057286530494544</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-1.252706920408777</v>
+        <v>-1.070549208278813</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-0.1589195231017726</v>
+        <v>0.01867810539604164</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.4690074787678995</v>
+        <v>-0.3793919214930312</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>-0.06316498222400924</v>
+        <v>0.02441168358127754</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>-0.1252354966206539</v>
+        <v>-0.08916599624564014</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>-0.02873909801252239</v>
+        <v>-0.04609198278063786</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-0.1696260332853399</v>
+        <v>-0.2394282618230577</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>0.6338600334089506</v>
+        <v>0.5074365704287018</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>0.2506684491978675</v>
+        <v>0.1274090411584652</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>0.1174820174070348</v>
+        <v>-0.007838255654405657</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>0.4522731067880059</v>
+        <v>0.3243374559905448</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>0.2448734998755313</v>
+        <v>0.1194591020471734</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>0.4014583267949234</v>
+        <v>0.2745327102803756</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; 46.01</t>
+          <t>X &lt; 46.11</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1231</v>
+        <v>1239</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-1.507187216344697</v>
+        <v>-1.48773706558508</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.5956423019212309</v>
+        <v>-0.5837643746708494</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-2.072791596699908</v>
+        <v>-2.059010372953345</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.4910288312222875</v>
+        <v>-0.4911053735408899</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-1.536112012489127</v>
+        <v>-1.582387452802791</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.01535195349505614</v>
+        <v>-0.07045729552846325</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-1.307310388842474</v>
+        <v>-1.278139181364985</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-1.343929550490081</v>
+        <v>-1.271050521251006</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-1.302413485467447</v>
+        <v>-1.184575754365113</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-1.834313412365901</v>
+        <v>-1.751789005936487</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-1.640599306540885</v>
+        <v>-1.512853784286186</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-1.274531919693203</v>
+        <v>-1.148516371013933</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.06031346076099453</v>
+        <v>0.05951127274088464</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-0.6042509169566372</v>
+        <v>-0.4831110120658266</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-0.05350473663909838</v>
+        <v>0.06453347170408819</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-0.297766200204741</v>
+        <v>-0.1449381272532406</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-0.3840074519884666</v>
+        <v>-0.3592411163207458</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-0.2793795697082686</v>
+        <v>-0.3033101159618639</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>0.2276002173245573</v>
+        <v>0.1537388212325652</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>0.1391700404858227</v>
+        <v>0.0667683015552214</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-0.193727151299413</v>
+        <v>-0.2669433366836316</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>0.2653741379547299</v>
+        <v>0.1887024992085387</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>0.1832171044389668</v>
+        <v>0.1084294796326759</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-0.08776680395818204</v>
+        <v>-0.1613026408092111</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; 48.91</t>
+          <t>X &lt; 49</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1374</v>
+        <v>1382</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-1.190320109854468</v>
+        <v>-1.171269447003908</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.2628992258706262</v>
+        <v>-0.1790623071972561</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-1.159163210003967</v>
+        <v>-1.148409985902383</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.2585657236819969</v>
+        <v>0.3296440527430562</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.8601904465973789</v>
+        <v>-0.8270679983878537</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.05476870206161522</v>
+        <v>-0.02542126670540767</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.8592428405020271</v>
+        <v>-0.9007128693592392</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.9931843262230515</v>
+        <v>-0.9946461435502698</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-1.168588000896726</v>
+        <v>-1.200580894499645</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-2.231649731261243</v>
+        <v>-2.149228909643526</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-2.535743103336067</v>
+        <v>-2.483743325895574</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-1.802544888228191</v>
+        <v>-1.753119982407739</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.7578387097521997</v>
+        <v>-0.6412423953345154</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-1.196115260482863</v>
+        <v>-1.078615431838777</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-0.8427543809373716</v>
+        <v>-0.7273859824835043</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-0.9283807310866266</v>
+        <v>-0.8539795940661108</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-0.947622354911708</v>
+        <v>-0.987896731043584</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-0.8651234802913734</v>
+        <v>-0.8043452214545255</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-0.5337624323136865</v>
+        <v>-0.5163557871776447</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-0.4490203193033366</v>
+        <v>-0.5034088172944706</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-0.9494277147350587</v>
+        <v>-0.9312962785440249</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-0.7645043018498683</v>
+        <v>-0.7478091709437251</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-0.8102893890675205</v>
+        <v>-0.7920789988969261</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-0.770576368140155</v>
+        <v>-0.8253225719193367</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; 51.8</t>
+          <t>X &lt; 51.89</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1522</v>
+        <v>1527</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-1.011783743413133</v>
+        <v>-1.019487890130996</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.181736218006435</v>
+        <v>0.1046869690472363</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.8976319748583705</v>
+        <v>-0.9742392019015611</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.1807356523581163</v>
+        <v>0.09908395359662592</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.7337896493651286</v>
+        <v>-0.8491492957619116</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.3148372377698507</v>
+        <v>-0.4312654225495649</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-1.246747660155087</v>
+        <v>-1.361859879120772</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-1.39492420919386</v>
+        <v>-1.473825868690838</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-1.614164337130802</v>
+        <v>-1.656247759302708</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-2.192432603180556</v>
+        <v>-2.197634889470621</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-2.895909059663651</v>
+        <v>-2.864383472064397</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-2.552071216454777</v>
+        <v>-2.556813657271348</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-1.784846844596188</v>
+        <v>-1.790724909795223</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-2.033965395184552</v>
+        <v>-2.076950366046368</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-1.871576416544713</v>
+        <v>-1.953334705972203</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-1.826671547654456</v>
+        <v>-1.907767373869071</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-1.399802247492936</v>
+        <v>-1.520172124927377</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-1.532093660122925</v>
+        <v>-1.652355658506067</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-1.015874836877806</v>
+        <v>-1.137472045759289</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-1.118119266055054</v>
+        <v>-1.173777711046775</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-1.36082335981763</v>
+        <v>-1.482250715673871</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-1.332738141805919</v>
+        <v>-1.454521782987563</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-1.413405248913527</v>
+        <v>-1.534451790423049</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-1.319631755692342</v>
+        <v>-1.441249869942283</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; 54.7</t>
+          <t>X &lt; 54.77</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1682</v>
+        <v>1690</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.2035331704566801</v>
+        <v>-0.245062570106434</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.6110680001463749</v>
+        <v>0.623087277439069</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.6197865482032867</v>
+        <v>-0.6656945434622514</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.0540625728028985</v>
+        <v>0.002435277808999103</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.6907963317550667</v>
+        <v>-0.7698991898919871</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.7066775806061329</v>
+        <v>-0.785110051203354</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-1.033478648735077</v>
+        <v>-1.113174885965911</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-1.253001417039947</v>
+        <v>-1.299714258370585</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-1.506644738085789</v>
+        <v>-1.519388331081188</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-1.572097622290876</v>
+        <v>-1.494325957746078</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-2.242248390594661</v>
+        <v>-2.188132815035438</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-2.134095969004413</v>
+        <v>-2.113525328024068</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-1.545651570244068</v>
+        <v>-1.528795757659928</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-1.732901874022154</v>
+        <v>-1.749874634106519</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-1.648047000235756</v>
+        <v>-1.642411335691783</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-1.669267363100943</v>
+        <v>-1.661800682130675</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-1.295445235766614</v>
+        <v>-1.324297665896601</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-1.306602977509598</v>
+        <v>-1.335813301061663</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-0.9372660837057865</v>
+        <v>-0.9674896832586128</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-1.130634638196916</v>
+        <v>-1.218350441326997</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-1.283185572202704</v>
+        <v>-1.313119074043016</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-1.086792044213013</v>
+        <v>-1.17706483172072</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-1.371192538205968</v>
+        <v>-1.459215166596884</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-1.352991078568401</v>
+        <v>-1.441443621080573</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 57.6</t>
+          <t>X &lt; 57.66</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1839</v>
+        <v>1847</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.4769156024192611</v>
+        <v>-0.5643356099541705</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.2380149075618689</v>
+        <v>0.1999649533145771</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.9573352005113804</v>
+        <v>-0.9412273207484958</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.619195433949983</v>
+        <v>-0.6067684700732983</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-1.439207494007022</v>
+        <v>-1.448982627065519</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.8990855248640841</v>
+        <v>-0.9106143997526175</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-1.588155532743009</v>
+        <v>-1.545491260311266</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-1.704985110876123</v>
+        <v>-1.686483650987938</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-2.010994756998919</v>
+        <v>-1.991240908759224</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-1.675634374014841</v>
+        <v>-1.659160427105029</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-1.694769166500478</v>
+        <v>-1.677517218798741</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-2.15962454617236</v>
+        <v>-2.171436068185415</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-1.794402388398311</v>
+        <v>-1.757520490486876</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-1.71426679301868</v>
+        <v>-1.678423092713146</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-1.584366348145871</v>
+        <v>-1.605032167502024</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-1.607308581388722</v>
+        <v>-1.572122845707753</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-1.222479317104856</v>
+        <v>-1.243312057052009</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-1.295782134704005</v>
+        <v>-1.370624265433563</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-1.210633817312413</v>
+        <v>-1.23122433669873</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-1.588781877373847</v>
+        <v>-1.60717629059193</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-1.557722667412719</v>
+        <v>-1.577993517299028</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-1.330385774254907</v>
+        <v>-1.351908559146061</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-1.404162906854083</v>
+        <v>-1.424526811388127</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-1.502771338351316</v>
+        <v>-1.522976764543657</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 60.49</t>
+          <t>X &lt; 60.55</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1997</v>
+        <v>2001</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.628058998618549</v>
+        <v>-0.6502391055229211</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.2431918658857057</v>
+        <v>-0.2664250987253993</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.9125571266726311</v>
+        <v>-0.9356617633857596</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.5576319675156824</v>
+        <v>-0.5820425248099639</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-1.341956264336176</v>
+        <v>-1.385616774249044</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.9784331090164073</v>
+        <v>-1.022695795942276</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-1.376057083712922</v>
+        <v>-1.420200887630962</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-1.803643025803758</v>
+        <v>-1.819629014396448</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-1.684796606098487</v>
+        <v>-1.700967662565638</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-1.73478019987332</v>
+        <v>-1.75115090238026</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-1.631371253258912</v>
+        <v>-1.647828538416498</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-2.33046570154584</v>
+        <v>-2.373671831581341</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-1.783742325945418</v>
+        <v>-1.828996906479603</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-1.777161857696306</v>
+        <v>-1.822648699479586</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>-1.709424075397031</v>
+        <v>-1.755626180197176</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>-1.583977628856665</v>
+        <v>-1.629975715341565</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>-1.140249410720443</v>
+        <v>-1.187279445319859</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-1.465635755357042</v>
+        <v>-1.512141905662546</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-1.470135703712337</v>
+        <v>-1.516491644925232</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-1.803785607196403</v>
+        <v>-1.84935851735888</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-1.86820040899795</v>
+        <v>-1.914132051042351</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-1.614965869843168</v>
+        <v>-1.661503658114704</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>-1.861522440300583</v>
+        <v>-1.907377294238607</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>-1.908491392058856</v>
+        <v>-1.954352846941006</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 63.39</t>
+          <t>X &lt; 63.44</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2133</v>
+        <v>2140</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.4273681589975524</v>
+        <v>-0.4739492863399732</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>0.05102790559096348</v>
+        <v>0.04842789210350418</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.574345573896295</v>
+        <v>-0.5779187590543344</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.1943745341816197</v>
+        <v>-0.2006710543295895</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.7659786983118479</v>
+        <v>-0.7884643402506839</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.8318303187851228</v>
+        <v>-0.9000737226831603</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-1.020738745931752</v>
+        <v>-0.9973004095665488</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-1.319724744053467</v>
+        <v>-1.295896794235659</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-1.065884381124313</v>
+        <v>-1.042794909489814</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-0.928548428968206</v>
+        <v>-0.9075205672793487</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-1.000323324218179</v>
+        <v>-0.9784913527429708</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-1.439393939393931</v>
+        <v>-1.416718238117291</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-1.278115579201057</v>
+        <v>-1.258315924958232</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-1.099110399442758</v>
+        <v>-1.080359198710568</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>-0.7970817373318511</v>
+        <v>-0.7806962694901216</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>-0.9216213756317302</v>
+        <v>-0.903588962248179</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-0.7946788695597746</v>
+        <v>-0.7773448938192971</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-0.9656377392909121</v>
+        <v>-0.9479701879420332</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-0.9558698012331561</v>
+        <v>-0.9377848747927473</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>-1.162552643893314</v>
+        <v>-1.143404186767448</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>-1.303968199260126</v>
+        <v>-1.332164860831085</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>-1.305630874476627</v>
+        <v>-1.334007041228631</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>-1.471957617746057</v>
+        <v>-1.545945171947068</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>-1.52059121079774</v>
+        <v>-1.594626168224302</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 66.28</t>
+          <t>X &lt; 66.33</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2293</v>
+        <v>2301</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.4357794368388781</v>
+        <v>-0.4566818810739619</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.186402751928604</v>
+        <v>-0.2089428958541077</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.7385393032366636</v>
+        <v>-0.7194138479790126</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.3045978745010487</v>
+        <v>-0.2885961185579689</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.948475707611955</v>
+        <v>-0.9020426252165805</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.6939897684368077</v>
+        <v>-0.6911176875764724</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.5336754216591331</v>
+        <v>-0.5331335398968733</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.9176522903998219</v>
+        <v>-0.916431632724759</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.8516671333681458</v>
+        <v>-0.8505881685291143</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-0.7774318317626836</v>
+        <v>-0.778392178887465</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.9118552167890499</v>
+        <v>-0.9549467900917605</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.9493272454226869</v>
+        <v>-0.9929577571120802</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.9639312923022132</v>
+        <v>-0.9668686380280391</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-0.725761429191742</v>
+        <v>-0.730042714353651</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>-0.7510048067044082</v>
+        <v>-0.7567245842806543</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>-0.8254870669086571</v>
+        <v>-0.7862842369122092</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-0.5427487598482728</v>
+        <v>-0.504827278251561</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-0.6655092813012686</v>
+        <v>-0.6273971598671011</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>-0.6847592003201726</v>
+        <v>-0.689441139892196</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-0.7332934262080926</v>
+        <v>-0.7373879015989289</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>-0.9896289804265237</v>
+        <v>-0.9940971209026372</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>-0.9963341138780422</v>
+        <v>-1.000966023403066</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>-1.262536357443523</v>
+        <v>-1.265621135540663</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>-1.094929138517173</v>
+        <v>-1.098783239306755</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 69.18</t>
+          <t>X &lt; 69.22</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2447</v>
+        <v>2453</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.6376841587872306</v>
+        <v>-0.6521556756290607</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.3843475481796546</v>
+        <v>-0.3998663360242034</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.4246862013370105</v>
+        <v>-0.4419372211199715</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.1838689303456817</v>
+        <v>-0.2026180073481214</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.3236809206546738</v>
+        <v>-0.3539732133205931</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.4382589528559748</v>
+        <v>-0.4680558276119271</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.1332425212262294</v>
+        <v>-0.1647788574783533</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-0.6728688194120593</v>
+        <v>-0.7034671790669407</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.8114017195283907</v>
+        <v>-0.8416306802088442</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-0.7495852006502375</v>
+        <v>-0.7809661116027655</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-0.9397076202046719</v>
+        <v>-0.9702981791821728</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-0.9109891734942508</v>
+        <v>-0.9825921456857003</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-0.8323809690945509</v>
+        <v>-0.9056409383920396</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-0.6636598473333208</v>
+        <v>-0.7376498916639491</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>-0.769329051023881</v>
+        <v>-0.8439376690566931</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>-0.8425521701003049</v>
+        <v>-0.9162634061049317</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>-0.6267287747308075</v>
+        <v>-0.7011750822842018</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-0.5445754379652143</v>
+        <v>-0.6193942167583302</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>-0.5897762589157054</v>
+        <v>-0.664247725747046</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>-0.4602713178294522</v>
+        <v>-0.4941588080444674</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>-0.7753432661408155</v>
+        <v>-0.80917583968656</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>-0.7046495438565685</v>
+        <v>-0.7387737000985695</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>-1.1000992524068</v>
+        <v>-1.132927620033428</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-1.233817755122033</v>
+        <v>-1.26643753024144</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; 72.07</t>
+          <t>X &lt; 72.11</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2582</v>
+        <v>2589</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.4303594095895633</v>
+        <v>-0.4249206203232347</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.3994658912092532</v>
+        <v>-0.3946204648265947</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.5123857824835625</v>
+        <v>-0.5094284014257937</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.1289705593193133</v>
+        <v>-0.128130134720827</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.3189101559010794</v>
+        <v>-0.3274181276494161</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.7639727927685982</v>
+        <v>-0.7710100660916765</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.55354653425821</v>
+        <v>-0.5623354149088868</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-1.079768533330473</v>
+        <v>-1.087577556577244</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.9395568394615026</v>
+        <v>-0.9476886834802158</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-1.036808566200584</v>
+        <v>-1.04586889830658</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-1.241413527437153</v>
+        <v>-1.21108245330408</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-1.190280421197919</v>
+        <v>-1.160507801467958</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-1.097286452562741</v>
+        <v>-1.069477102228198</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-0.8332433502501431</v>
+        <v>-0.806479262778133</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>-1.083590268442741</v>
+        <v>-1.057155485173453</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>-1.006271315489514</v>
+        <v>-0.979130931961123</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>-0.8860070264276061</v>
+        <v>-0.8593922268593488</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-0.7364358920916558</v>
+        <v>-0.7103815927692239</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>-0.806728758898366</v>
+        <v>-0.7801501681989009</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>-0.7129737045630336</v>
+        <v>-0.6863578047170407</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>-0.8853183973925383</v>
+        <v>-0.8590662567050984</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>-0.783629148851098</v>
+        <v>-0.7577647084535073</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>-1.260224278026804</v>
+        <v>-1.232646619507932</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>-1.584632249355643</v>
+        <v>-1.556290001191243</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &lt; 74.97</t>
+          <t>X &lt; 75</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2709</v>
+        <v>2716</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.3798315082398105</v>
+        <v>-0.3732311952136413</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.4391760855360971</v>
+        <v>-0.3963689811754989</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.6138325493164203</v>
+        <v>-0.5725760992855484</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.2082285870111775</v>
+        <v>-0.2055443486765611</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.6996147348978852</v>
+        <v>-0.7037037233695216</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-1.2620546522366</v>
+        <v>-1.264448333274537</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.9142022071749096</v>
+        <v>-0.8819839279100634</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-1.392316647264259</v>
+        <v>-1.359256358745611</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-1.366953298834879</v>
+        <v>-1.333892822002419</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-1.495917667634636</v>
+        <v>-1.463603296064029</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-1.568131244631942</v>
+        <v>-1.535240463505104</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-1.385526454434938</v>
+        <v>-1.390145398557273</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-1.239155965504821</v>
+        <v>-1.245734471554869</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-1.034615495964573</v>
+        <v>-1.042037439253825</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>-1.230544305582107</v>
+        <v>-1.238395818245458</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>-1.202689406644438</v>
+        <v>-1.209785075423838</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-1.020753498274345</v>
+        <v>-1.028513115121015</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-0.8831393342428555</v>
+        <v>-0.85467082812972</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>-0.9769295730706915</v>
+        <v>-0.9479107283585151</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-0.842010689273863</v>
+        <v>-0.8130705607797353</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>-0.921150261505332</v>
+        <v>-0.8927654425895284</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>-0.7909094299670087</v>
+        <v>-0.7629618461086451</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>-1.121594320298662</v>
+        <v>-1.09240279505358</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>-1.397388820889432</v>
+        <v>-1.367588055551728</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &lt; 77.86</t>
+          <t>X &lt; 77.89</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2839</v>
+        <v>2845</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.4595861157438037</v>
+        <v>-0.4330367926509311</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.5664447707970837</v>
+        <v>-0.5748565591483654</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.6937526292364993</v>
+        <v>-0.7032451938902398</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.6538714951560607</v>
+        <v>-0.664118795264244</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.8247714694024566</v>
+        <v>-0.840879072914511</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-1.248141231959792</v>
+        <v>-1.263196327830101</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.811240993342345</v>
+        <v>-0.8279429764518014</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-1.210180044812432</v>
+        <v>-1.226315404436562</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-1.184017120433644</v>
+        <v>-1.165213094553017</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-1.202098313375586</v>
+        <v>-1.183977360614371</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-1.25841136825197</v>
+        <v>-1.274902661584413</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-1.166901320356239</v>
+        <v>-1.183855758562082</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.9731600934718045</v>
+        <v>-0.9915844066884389</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.7528599365333974</v>
+        <v>-0.7719651124481928</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>-0.8644869765811194</v>
+        <v>-0.8839857837212506</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>-0.880853107879517</v>
+        <v>-0.8997705764267252</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>-0.7483767961463599</v>
+        <v>-0.7677094783434484</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-0.6569015806963563</v>
+        <v>-0.6765361854517806</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>-0.5606373258595383</v>
+        <v>-0.5802827278169147</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>-0.4583626450932101</v>
+        <v>-0.4429587568444049</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>-0.4882215208909813</v>
+        <v>-0.4732637875693015</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>-0.5080590197268009</v>
+        <v>-0.5282544627121624</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>-0.7052957911161783</v>
+        <v>-0.6896912557514412</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>-1.077463236581536</v>
+        <v>-1.061143915378672</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &lt; 80.76</t>
+          <t>X &lt; 80.78</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2953</v>
+        <v>2959</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.6163257068260677</v>
+        <v>-0.6227384615204983</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.5303053237564654</v>
+        <v>-0.503634646434584</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.7415326904664639</v>
+        <v>-0.7156563836315613</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.797839469958312</v>
+        <v>-0.772451293783547</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-1.077185650935348</v>
+        <v>-1.056074491083514</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-1.51087230860113</v>
+        <v>-1.488723248566338</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.9858158737995808</v>
+        <v>-0.9653807032839339</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-1.279147229952038</v>
+        <v>-1.258354504592532</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-1.185032388171557</v>
+        <v>-1.164390111214892</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-1.063631611480893</v>
+        <v>-1.043891826907547</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-1.073472949766256</v>
+        <v>-1.053475146366573</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-0.996149718746679</v>
+        <v>-0.9765431377980889</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.853052131258579</v>
+        <v>-0.8346933674444585</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.7172031340861835</v>
+        <v>-0.6993053633419919</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>-0.8836434833446916</v>
+        <v>-0.8659706840927939</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>-0.8764758665451211</v>
+        <v>-0.8583049912675733</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>-0.7204808397542735</v>
+        <v>-0.7027375051909672</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-0.6365650660209923</v>
+        <v>-0.6190787565327156</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>-0.5018680011647163</v>
+        <v>-0.4844662635793995</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>-0.4639414947582026</v>
+        <v>-0.4464533604065082</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>-0.3782815997963311</v>
+        <v>-0.3614305667725404</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-0.3325649401058755</v>
+        <v>-0.3158692896741186</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>-0.5115265405416451</v>
+        <v>-0.4942296310909455</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>-0.804464881585389</v>
+        <v>-0.7866366036770387</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &lt; 83.65</t>
+          <t>X &lt; 83.67</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3042</v>
+        <v>3047</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.4277918788339932</v>
+        <v>-0.416091413106237</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.484492742849433</v>
+        <v>-0.4728542799798845</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.6987525264988932</v>
+        <v>-0.6874369634203319</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.6108638524751981</v>
+        <v>-0.6000237816901404</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.9253162814570359</v>
+        <v>-0.9177038259273758</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-1.406255346815854</v>
+        <v>-1.397770369478657</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-1.082379196907524</v>
+        <v>-1.074785094198894</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-1.309909845433005</v>
+        <v>-1.302075029041291</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-1.151912783746376</v>
+        <v>-1.144316290507938</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-1.023850652696929</v>
+        <v>-1.016826942721188</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-1.058132699709148</v>
+        <v>-1.05092410351785</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.8274714807131289</v>
+        <v>-0.820771242780225</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.6557616185751058</v>
+        <v>-0.6498715279463667</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.69409152914114</v>
+        <v>-0.6882435054103979</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>-0.8093383607285105</v>
+        <v>-0.8036126874514764</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>-0.8833521433900131</v>
+        <v>-0.8772256112681589</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>-0.7358270321257194</v>
+        <v>-0.7300057242251938</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>-0.657432050415764</v>
+        <v>-0.6517892356512078</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>-0.6188209534806219</v>
+        <v>-0.6459055003445684</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>-0.4780860144451751</v>
+        <v>-0.472548166964792</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>-0.3779705239404834</v>
+        <v>-0.3728539515037284</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>-0.3686626919730216</v>
+        <v>-0.3635981058167062</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>-0.5015032031863598</v>
+        <v>-0.4960917294097413</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>-0.6565971140869991</v>
+        <v>-0.6509677820071147</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &lt; 86.55</t>
+          <t>X &lt; 86.56</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3124</v>
+        <v>3128</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.3217222954870493</v>
+        <v>-0.3244396237461515</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.4492206330461102</v>
+        <v>-0.4518143879722487</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.3774552541156027</v>
+        <v>-0.380299042108426</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.4694064737558463</v>
+        <v>-0.4722132445502965</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.7215062351642629</v>
+        <v>-0.7267662262378067</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.9621562134217854</v>
+        <v>-0.9670932311046485</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.8577925652605103</v>
+        <v>-0.8629502367642772</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.9591956281559888</v>
+        <v>-0.9642582401325512</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.772272388549375</v>
+        <v>-0.7775717826355333</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.6039221625457998</v>
+        <v>-0.6095242115584654</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.6300025786212586</v>
+        <v>-0.6355449623675966</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.5400849150849183</v>
+        <v>-0.5457760838777119</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.4021872067094492</v>
+        <v>-0.408181246125082</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.5409493544888022</v>
+        <v>-0.546794641223201</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>-0.5746222886092838</v>
+        <v>-0.5805008505178719</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>-0.5991153910922051</v>
+        <v>-0.6049010513296196</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>-0.5227523703074937</v>
+        <v>-0.5286539790827405</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-0.4490934761241263</v>
+        <v>-0.4551044595064724</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>-0.4696820186948898</v>
+        <v>-0.4756467363060537</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>-0.3916240409207106</v>
+        <v>-0.3976716425917814</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>-0.3403302459023436</v>
+        <v>-0.346507160293676</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>-0.3332469553635278</v>
+        <v>-0.3394452122371874</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>-0.3593802981584346</v>
+        <v>-0.3655187054001559</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>-0.4483306002950229</v>
+        <v>-0.4543675454740992</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &lt; 89.44</t>
+          <t>X &lt; 89.45</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3202</v>
+        <v>3206</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.3097803204794829</v>
+        <v>-0.3116430254790359</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.3802646623306103</v>
+        <v>-0.3820675301213114</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.4071109432774165</v>
+        <v>-0.4089946806764218</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.4520520260418834</v>
+        <v>-0.4539373398339421</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.5827018984078691</v>
+        <v>-0.5864184605547251</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.9061132609960225</v>
+        <v>-0.9094163039262497</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.8229884695928646</v>
+        <v>-0.8264577569873168</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.9908250375688041</v>
+        <v>-0.9941102594084228</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.77635233853632</v>
+        <v>-0.7799029684791492</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.693043953210065</v>
+        <v>-0.6967614422656538</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.6496546419143883</v>
+        <v>-0.653406910868803</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.5064708160538842</v>
+        <v>-0.5104255674751457</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.3680853150224195</v>
+        <v>-0.37230343349718</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.4154428182943661</v>
+        <v>-0.4196221860991969</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>-0.4642651268300781</v>
+        <v>-0.4684384795093237</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>-0.4736692875603836</v>
+        <v>-0.4777865776621155</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>-0.433545025785115</v>
+        <v>-0.437725529021165</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-0.4265460109213279</v>
+        <v>-0.4307462177185357</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>-0.47255205879474</v>
+        <v>-0.4766805270487211</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>-0.3918434185901418</v>
+        <v>-0.396060298730994</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>-0.4174203777967023</v>
+        <v>-0.4216511356528159</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>-0.3499607080862575</v>
+        <v>-0.3542843125694262</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>-0.3999922244775078</v>
+        <v>-0.4042343504969779</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>-0.3324859097566986</v>
+        <v>-0.3368210015100104</v>
       </c>
     </row>
     <row r="34">
@@ -8124,79 +8124,79 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3275</v>
+        <v>3279</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.369088052203189</v>
+        <v>-0.3701021104035007</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.2028061712292057</v>
+        <v>-0.2040395434085696</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.2305507825395097</v>
+        <v>-0.2318247789946</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.2902565550340555</v>
+        <v>-0.2914954343325107</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.4260568397112081</v>
+        <v>-0.4284274770599126</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.6166322802595445</v>
+        <v>-0.6187636992198193</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.6131544683313663</v>
+        <v>-0.6153311156443024</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.7833831923873262</v>
+        <v>-0.7853689522532363</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.6942656278343406</v>
+        <v>-0.6963589371742671</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.5387436245099906</v>
+        <v>-0.5410669802692851</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.5814202782071618</v>
+        <v>-0.5836792874059071</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.447593933295181</v>
+        <v>-0.450031464794975</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.3068137650823601</v>
+        <v>-0.3094817784030823</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.358019267720131</v>
+        <v>-0.3606380704960088</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>-0.2681328455542697</v>
+        <v>-0.2708965437080835</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>-0.2335765982318989</v>
+        <v>-0.2363534954043018</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-0.2277234571431421</v>
+        <v>-0.2305161151954351</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-0.2536317558701455</v>
+        <v>-0.2564000159750748</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>-0.3852145273277472</v>
+        <v>-0.3878131250645964</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>-0.3326090271424178</v>
+        <v>-0.3352637664202049</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>-0.3391888165635351</v>
+        <v>-0.3418652500921553</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>-0.2749000481010455</v>
+        <v>-0.2776604957019586</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>-0.3176708964490302</v>
+        <v>-0.3203667438134232</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>-0.2533369046024774</v>
+        <v>-0.2561168780087399</v>
       </c>
     </row>
     <row r="35">
@@ -8206,79 +8206,79 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3341</v>
+        <v>3345</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.1366659955248792</v>
+        <v>-0.1372841680638004</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.03962698283937272</v>
+        <v>-0.04036997652784891</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.1842740055401535</v>
+        <v>-0.1848847908781295</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.1675511856244256</v>
+        <v>-0.1682017350846365</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.2482985779365592</v>
+        <v>-0.2495455978681846</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.4611697607306766</v>
+        <v>-0.4621592982248899</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.4133450869154487</v>
+        <v>-0.4144133771275875</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.4962785179821623</v>
+        <v>-0.4972564920462474</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.4378089255074329</v>
+        <v>-0.4388561181960355</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.3899117009097282</v>
+        <v>-0.3910378739898306</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.3666750562475514</v>
+        <v>-0.3678221948965543</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.2110884939694913</v>
+        <v>-0.2124294690468389</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.09515063067400575</v>
+        <v>-0.09666147923379498</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.1794860417629067</v>
+        <v>-0.1809033362352608</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>-0.07444840539211839</v>
+        <v>-0.07600995007764766</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>-0.08850758494585165</v>
+        <v>-0.0900369637321603</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>-0.05550134412960972</v>
+        <v>-0.05707472719950601</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>-0.1426724858901594</v>
+        <v>-0.144145649051282</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>-0.2972500119981945</v>
+        <v>-0.2985335788250296</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>-0.2419656203288554</v>
+        <v>-0.2433109310395167</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>-0.2890138061271443</v>
+        <v>-0.2903187457532965</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>-0.1377390721786966</v>
+        <v>-0.1392277651122598</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>-0.1442755704504748</v>
+        <v>-0.1457498003935456</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>-0.08266075745084578</v>
+        <v>-0.08421168433846304</v>
       </c>
     </row>
   </sheetData>

--- a/workspaces/nasdaq_hourly_24hrs/rsi/rsi_10.xlsx
+++ b/workspaces/nasdaq_hourly_24hrs/rsi/rsi_10.xlsx
@@ -618,165 +618,165 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ 12.88</t>
+          <t>X ≈ 12.9</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>39</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>19.21184363064075</v>
+        <v>20.49635658233144</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>18.87736371542996</v>
+        <v>19.0669964873255</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>7.223904604751546</v>
+        <v>9.003494211407435</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>1.401545011481936</v>
+        <v>0.7704438141228422</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-9.14038800380019</v>
+        <v>-7.152307562597464</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-2.416843970925314</v>
+        <v>0.6520946960971585</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-5.736270352163494</v>
+        <v>-5.241095762955005</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-8.566707134564183</v>
+        <v>-8.098039739603408</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-16.18565636702877</v>
+        <v>-18.18349667561781</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-6.746908605410418</v>
+        <v>-8.768186622014611</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-3.921884154612236</v>
+        <v>-5.94548278178214</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.9089134889268067</v>
+        <v>1.442012097760205</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>4.900875871590735</v>
+        <v>5.442567756163747</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.4308256538270783</v>
+        <v>0.08390889026229331</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-6.201336095397579</v>
+        <v>-5.710446848765685</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>-5.6104732140507</v>
+        <v>-5.152369593620456</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>-5.745794182813846</v>
+        <v>-5.257546225445765</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-3.292754843065488</v>
+        <v>-2.832300085198113</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>-0.5179178044571131</v>
+        <v>-0.05872599283507896</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>4.790575237387785</v>
+        <v>5.277594159564799</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>4.250098841925983</v>
+        <v>4.712335492802026</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>4.175699394616082</v>
+        <v>4.638637761986452</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>9.578138668846876</v>
+        <v>10.01033059813027</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>9.505301941049602</v>
+        <v>9.851238932131942</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ 15.77</t>
+          <t>X ≈ 15.78</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-1.810255276484241</v>
+        <v>-2.616987327875663</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-7.77497773411028</v>
+        <v>-8.280975551992114</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-9.234628822469652</v>
+        <v>-9.527303798740796</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.5777329534108304</v>
+        <v>-1.083158396499329</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-6.550166556086616</v>
+        <v>-6.780330390920376</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-10.11308450115524</v>
+        <v>-10.24384234235421</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-7.949330994345893</v>
+        <v>-9.228967673693091</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-2.595884989231024</v>
+        <v>-4.107114987301877</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-4.433241793991968</v>
+        <v>-5.790373335304565</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-7.083322531274447</v>
+        <v>-8.395777936448596</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-10.57123207513866</v>
+        <v>-11.74930158078389</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-12.73221177386677</v>
+        <v>-13.84014885710575</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-4.453551040856205</v>
+        <v>-5.895170153729978</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-4.675134747327377</v>
+        <v>-6.144177449648105</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-3.450856741146069</v>
+        <v>-5.012621642527733</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-4.741413541319837</v>
+        <v>-6.268175500731466</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-2.993766486707962</v>
+        <v>-4.559425318435025</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>2.550516014118699</v>
+        <v>0.751019599366586</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-1.000960177374864</v>
+        <v>-0.8500609296098958</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-2.699182978312407</v>
+        <v>-2.452080788772001</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-1.356847177856203</v>
+        <v>-1.203116988161128</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-5.204194571352559</v>
+        <v>-4.912722156024905</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-3.045061215706241</v>
+        <v>-2.852962011368376</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-6.895278610474342</v>
+        <v>-6.652257571364565</v>
       </c>
     </row>
     <row r="8">
@@ -786,2211 +786,2211 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>1.179940263708545</v>
+        <v>2.50965375875596</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-3.364614823337334</v>
+        <v>-1.829368793031662</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.765797778145803</v>
+        <v>2.334583354406767</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.03999474296593775</v>
+        <v>1.129123563673303</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.485386712486104</v>
+        <v>0.2530066678216798</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-7.733866875841784</v>
+        <v>-6.402679083150524</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-7.111851717005308</v>
+        <v>-7.195517939227308</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-13.00156613292972</v>
+        <v>-12.95377135375013</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-8.757778078742589</v>
+        <v>-8.739370100017155</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-13.74881823641581</v>
+        <v>-13.62677247770522</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-14.8795956305299</v>
+        <v>-14.72416503764127</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-15.16581477641606</v>
+        <v>-15.0043885958902</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-14.89959711140029</v>
+        <v>-14.75562112112675</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-16.53273247488185</v>
+        <v>-16.37301596214244</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>-20.01491782551064</v>
+        <v>-19.78995661362859</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-20.82402765993054</v>
+        <v>-20.6028597112542</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-18.15382361630544</v>
+        <v>-17.979263995457</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-23.88836332367905</v>
+        <v>-23.58699724686723</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-20.86359749850269</v>
+        <v>-22.01248708835336</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-20.67941075976289</v>
+        <v>-21.80513158212341</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-18.4204530377964</v>
+        <v>-19.64159539554093</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>-17.65971150453752</v>
+        <v>-19.72278490422556</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>-18.79878230694401</v>
+        <v>-19.48534490721019</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>-14.65504475450835</v>
+        <v>-15.54391386028112</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ 21.55</t>
+          <t>X ≈ 21.54</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-6.718123995519186</v>
+        <v>-6.912973553223388</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-1.757133816514681</v>
+        <v>-1.575725577701192</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-2.588662141868916</v>
+        <v>-2.837153486465887</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>2.027218296511791</v>
+        <v>2.153430780779892</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>2.858781635657969</v>
+        <v>1.87551580827482</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>5.387778466758895</v>
+        <v>3.775859646469911</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>5.781029764673129</v>
+        <v>4.103881729375658</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>7.844557411170399</v>
+        <v>6.037725008933201</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>4.374140391813746</v>
+        <v>2.812496300882948</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>4.767921112502016</v>
+        <v>3.139487892500398</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>5.045293270647022</v>
+        <v>3.411637227368466</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>4.765745727931439</v>
+        <v>3.137028345105655</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-1.056170514964982</v>
+        <v>-2.45231504278933</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>2.239916711524884</v>
+        <v>0.659735859589901</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>8.617111703296381</v>
+        <v>6.702473930013291</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-2.521252619904857</v>
+        <v>-3.942968687748575</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-3.830873581192463</v>
+        <v>-5.169323140230837</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-2.762610711201475</v>
+        <v>-4.182364930401235</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-4.895163991088538</v>
+        <v>-6.213395051119392</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-5.882374643273927</v>
+        <v>-7.123500285679597</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-4.080250917232654</v>
+        <v>-5.447767892101474</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-0.6292613185455096</v>
+        <v>-2.156091948900965</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>-3.178017069368742</v>
+        <v>-5.283037064637661</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>1.451003298515673</v>
+        <v>-0.9525640065022003</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ 24.43</t>
+          <t>X ≈ 24.42</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>2.187658526833346</v>
+        <v>2.763643169553887</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.4916772821935709</v>
+        <v>0.234368108788459</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-3.110967044271611</v>
+        <v>-3.298028355490999</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-1.485052690826834</v>
+        <v>-1.603096225366279</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-7.679395371172745</v>
+        <v>-7.589152411099569</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-6.320491118004057</v>
+        <v>-6.290723554659998</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-7.098130439684269</v>
+        <v>-7.083356441010274</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-6.705639747447087</v>
+        <v>-7.389049795544224</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-9.009019376824277</v>
+        <v>-9.551024944777112</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-7.43811453460966</v>
+        <v>-8.058289572853987</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-14.20060704547943</v>
+        <v>-14.65688007817802</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-14.48323859293931</v>
+        <v>-14.93732215879425</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-13.26223427959703</v>
+        <v>-13.76283436429284</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-9.967151353437671</v>
+        <v>-10.57788360487744</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-8.279566148645763</v>
+        <v>-8.969363512282676</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-7.688734058042606</v>
+        <v>-8.411948897214614</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-7.825270758851779</v>
+        <v>-8.518709417087109</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-11.45754052713594</v>
+        <v>-12.09589787824952</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>-12.42108779068813</v>
+        <v>-13.03348540171687</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-8.71156671154305</v>
+        <v>-9.380069269397936</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-9.256924058434954</v>
+        <v>-9.950280439189257</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>-9.332759306638202</v>
+        <v>-10.02888103814542</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>-11.41051983337206</v>
+        <v>-12.08683316114362</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>-11.49017317207257</v>
+        <v>-11.10366822967177</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ 27.32</t>
+          <t>X ≈ 27.3</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-3.661623026711979</v>
+        <v>-2.526646431876003</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-7.015650934707054</v>
+        <v>-6.745686444749623</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-5.445363328410117</v>
+        <v>-5.010286884126046</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-5.154930131991115</v>
+        <v>-4.606995487550307</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-4.488817382482843</v>
+        <v>-2.890965578458392</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.2784708739758344</v>
+        <v>0.2462196272656882</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-2.060670245079599</v>
+        <v>-1.538260037975647</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.6764739360719076</v>
+        <v>1.141566852909122</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.7173827301919857</v>
+        <v>2.265086568249096</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-2.072962523754086</v>
+        <v>-0.5171789385390255</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>5.247053670069121</v>
+        <v>6.723516794875174</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.939914807080676</v>
+        <v>2.466443861054145</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-1.197928446644177</v>
+        <v>0.3597590203745185</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-3.435895866643698</v>
+        <v>-1.881160316850753</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>0.939528441561535</v>
+        <v>2.422668467714715</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-1.487879550398873</v>
+        <v>-0.008102086447507872</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-0.6142944627554954</v>
+        <v>0.8854324044499862</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-2.738765007685252</v>
+        <v>-1.242983210236048</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-2.522035505406436</v>
+        <v>-1.029570893770014</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-2.332585835670955</v>
+        <v>-0.8162290592648702</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-1.870544342873686</v>
+        <v>-0.3847172952169444</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>0.07347646832248955</v>
+        <v>1.538363336273399</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>2.369829438992134</v>
+        <v>3.781570211466644</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>-4.169911734164067</v>
+        <v>-3.379530298637512</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ 30.21</t>
+          <t>X ≈ 30.18</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.3095363811297602</v>
+        <v>-1.466077465909407</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>3.537161816164186</v>
+        <v>2.39736451156616</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>1.256388493744161</v>
+        <v>0.3299404381947895</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-3.641815421883649</v>
+        <v>-4.366612588300505</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-5.653747095419433</v>
+        <v>-7.102018915720457</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-3.792037819644833</v>
+        <v>-4.483721043300172</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-3.730879198197435</v>
+        <v>-5.275070595850984</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-3.173047303857764</v>
+        <v>-4.758989125559822</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-1.812152796920358</v>
+        <v>-3.810537910130229</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-1.745407273047917</v>
+        <v>-2.959126682144273</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-1.473196851698916</v>
+        <v>-2.689478545921652</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.7616293821153164</v>
+        <v>-0.4966246239499554</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>2.155387680296705</v>
+        <v>0.03881211777232352</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.2588505741527456</v>
+        <v>-1.032262178967891</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-0.3983528510225298</v>
+        <v>-1.713241078152947</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>3.55054979576132</v>
+        <v>2.967088510142659</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>1.739383837396034</v>
+        <v>1.215189234223345</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-3.401475082822643</v>
+        <v>-3.865120231712723</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-1.507755743144635</v>
+        <v>-2.002772161126231</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-0.4818213114550005</v>
+        <v>-0.9646052792792617</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-3.545742779165749</v>
+        <v>-4.008850102163578</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-1.100580337213884</v>
+        <v>-0.7823441493931966</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>0.01423050972213957</v>
+        <v>-0.5392852461585278</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-0.06160174350113579</v>
+        <v>0.1246019327678667</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ 33.1</t>
+          <t>X ≈ 33.06</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>1.438381459377425</v>
+        <v>1.212675214643603</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>1.105354737394244</v>
+        <v>0.9693689777865302</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-8.762407347573159</v>
+        <v>-8.159407430281213</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-2.723421128267489</v>
+        <v>-4.018612776534695</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-2.212196211792126</v>
+        <v>-2.712734749243005</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>3.035065902780786</v>
+        <v>0.5945410334568422</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>6.485466335881341</v>
+        <v>6.114587619312402</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>4.520542614253785</v>
+        <v>4.234978685274598</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>7.937045328432944</v>
+        <v>6.732075998596386</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>10.54641689752977</v>
+        <v>9.100703778731656</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>9.978737873111292</v>
+        <v>8.584776281711086</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>7.170764126015087</v>
+        <v>5.94229316659343</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>10.27771349465613</v>
+        <v>10.36659230347441</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>8.37045846990037</v>
+        <v>8.541664197833192</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>10.25304780690484</v>
+        <v>11.02832896507852</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>11.69612113588063</v>
+        <v>12.38354588905911</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>7.335497292870443</v>
+        <v>8.326273215274988</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>6.38711994935403</v>
+        <v>8.19724416980776</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>6.604825660177518</v>
+        <v>8.413812259533401</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>5.099375782845854</v>
+        <v>7.045448459958621</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>5.405973500566098</v>
+        <v>7.273752594965117</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>6.17758516627584</v>
+        <v>7.993827335283363</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>6.452059878757893</v>
+        <v>7.446753226029664</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>6.376227625534618</v>
+        <v>8.080787161679986</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ 35.99</t>
+          <t>X ≈ 35.94</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>121</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-5.679565424903991</v>
+        <v>-4.747595615110846</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-1.899514816181515</v>
+        <v>-1.707966799552189</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>4.075103210853804</v>
+        <v>4.436336261817488</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.7493739138081992</v>
+        <v>-0.2576094448577209</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>3.031228216331691</v>
+        <v>3.574853099068271</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>5.682986555949817</v>
+        <v>6.189396495593044</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>1.624184572368314</v>
+        <v>2.117097241665242</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>2.169599469400339</v>
+        <v>2.63588962526412</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>4.678487464193488</v>
+        <v>5.229047116742628</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>4.733491106937088</v>
+        <v>4.438814417628059</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>5.008232411199572</v>
+        <v>4.711238708416509</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>5.556539847741526</v>
+        <v>5.261117418627407</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>6.909728038762744</v>
+        <v>6.620533134359711</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>7.51644623156001</v>
+        <v>7.199515095334625</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>5.213112398337977</v>
+        <v>4.874530116734938</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>3.334032899931799</v>
+        <v>2.964588604318976</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>7.327566657367001</v>
+        <v>6.983453735144202</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>13.82983255314559</v>
+        <v>13.45037089657201</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>14.87641843033025</v>
+        <v>14.49402554952879</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>12.59033295051046</v>
+        <v>12.23780995249653</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>11.22611637771995</v>
+        <v>10.85014462702448</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>10.32382413531912</v>
+        <v>9.952938091110788</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>9.771852566809244</v>
+        <v>10.20025419838546</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>7.216681470610958</v>
+        <v>6.736172180701566</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ 38.88</t>
+          <t>X ≈ 38.82</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-2.487552427024553</v>
+        <v>-1.652400507086028</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>4.176433282123767</v>
+        <v>4.260253113986579</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-4.266835736307975</v>
+        <v>-3.939628832263281</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.3150929303035923</v>
+        <v>0.08456809451333669</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.6527914798811096</v>
+        <v>-0.1954605375819227</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.3144438909573921</v>
+        <v>2.278713615200331</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>1.872617529922252</v>
+        <v>2.684137949363198</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.03831989542345582</v>
+        <v>2.048913077590463</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.6972819790194009</v>
+        <v>1.405829027389437</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>1.638880024274705</v>
+        <v>3.697632524211471</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.358063881043833</v>
+        <v>2.427638577606757</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>3.192164091446891</v>
+        <v>5.239731513545131</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>2.845301530290058</v>
+        <v>4.902160568824037</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>2.623668608806952</v>
+        <v>3.885443599837643</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>5.082148059043071</v>
+        <v>6.296250417225416</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>5.681194063242231</v>
+        <v>6.858922404120378</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>5.54893956193159</v>
+        <v>6.758055509310573</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>4.664526135106826</v>
+        <v>5.855109216025554</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>3.323175581358107</v>
+        <v>5.297575504791581</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>1.951190146437398</v>
+        <v>3.965881209401836</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>1.089236212430521</v>
+        <v>2.626643809741992</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>1.013390251021598</v>
+        <v>2.552273589118784</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>0.5066149635038286</v>
+        <v>2.022048134485324</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>1.212032710280376</v>
+        <v>2.635973577331704</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ 41.77</t>
+          <t>X ≈ 41.7</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-4.800826970262904</v>
+        <v>-5.911318455866379</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-2.244910971954219</v>
+        <v>-2.733221955814685</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.6094846498516091</v>
+        <v>-0.5494021858079989</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>1.335538422664953</v>
+        <v>0.9144754509259982</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.4556656460926263</v>
+        <v>-0.7270990674870959</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-1.697267195189568</v>
+        <v>-3.316139713626768</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-7.539673337427196</v>
+        <v>-8.214392226498596</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-2.768307437956693</v>
+        <v>-3.038460457976633</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-4.16806520338281</v>
+        <v>-4.96858949708092</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-8.144478818488011</v>
+        <v>-8.504799382162076</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-6.006669798068813</v>
+        <v>-6.866015299521713</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-5.566895724277941</v>
+        <v>-5.77188179392143</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-2.359738812016353</v>
+        <v>-2.767377298840664</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-3.306552268384024</v>
+        <v>-2.328172604491755</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>-4.691598353373614</v>
+        <v>-3.696562301335796</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>-2.649150002392773</v>
+        <v>-1.763590646849181</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>-2.78478215681082</v>
+        <v>-1.867860775799265</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-2.167952543062889</v>
+        <v>-1.312948905593025</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>2.397105409814685</v>
+        <v>2.341012734926132</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-1.334703126849647</v>
+        <v>-1.574501707117449</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-0.4279739324965064</v>
+        <v>-0.7640762615754397</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-1.953095256224778</v>
+        <v>-2.217938370691222</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-3.127895906061568</v>
+        <v>-3.353943661932071</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-1.029815115806578</v>
+        <v>-1.448495815878658</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ 44.66</t>
+          <t>X ≈ 44.58</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>114</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>3.367651829743465</v>
+        <v>2.585558805934149</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>1.283801537924255</v>
+        <v>1.466970046637748</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-1.020537840602387</v>
+        <v>-0.6441762163259526</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>7.007089344833311</v>
+        <v>6.60132913467838</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>3.178097689898628</v>
+        <v>2.847454295077213</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>6.857945974218701</v>
+        <v>7.352204217792824</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>2.594551070846364</v>
+        <v>2.211851733943938</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-2.927530470586881</v>
+        <v>-3.318022178701945</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-2.886362372836487</v>
+        <v>-3.192224137292634</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-7.152000605013825</v>
+        <v>-6.59920385672936</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-6.005238950063763</v>
+        <v>-5.460188098188482</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-1.914080667571817</v>
+        <v>-1.376311162971653</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.4624693384933138</v>
+        <v>1.002021804478616</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-1.507714920215065</v>
+        <v>-1.863306846462713</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>0.4610415783084747</v>
+        <v>0.07643959655844412</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>-0.6969890543499702</v>
+        <v>-1.985922185061106</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>-3.460222649832936</v>
+        <v>-3.839085659054938</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-0.9361211600161212</v>
+        <v>-0.4739575174039956</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>-3.35221255237812</v>
+        <v>-2.886533368978206</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>-0.5337877950420591</v>
+        <v>-0.04646495790093752</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>-2.830719927920377</v>
+        <v>-2.364877993004988</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>-1.152179924416991</v>
+        <v>-0.6885935198737911</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>-0.0005122294788080239</v>
+        <v>0.4315302732926796</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>-4.462309394982775</v>
+        <v>-4.11637240390025</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ 47.55</t>
+          <t>X ≈ 47.46</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1.600675844940433</v>
+        <v>0.5671053118486711</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>3.354675871159948</v>
+        <v>2.374835023674805</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>6.801367649013329</v>
+        <v>6.597881439071109</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>7.480632110522912</v>
+        <v>6.689924233201417</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>5.755497417125888</v>
+        <v>5.045638490378614</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.3658651053886359</v>
+        <v>0.4099261046424303</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>2.385898316172103</v>
+        <v>3.723091486391993</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>1.412206375340375</v>
+        <v>2.733702852451508</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-1.332899099726767</v>
+        <v>1.200737934252579</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-5.584295103694856</v>
+        <v>-4.38239342872312</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-10.88431898177799</v>
+        <v>-8.912002703444386</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-6.987085350135693</v>
+        <v>-5.07963606621383</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-6.718125092525838</v>
+        <v>-5.508985511089371</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-6.243504335529217</v>
+        <v>-5.070756651500091</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-7.602000181466558</v>
+        <v>-6.440357886002076</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-7.011944759878794</v>
+        <v>-5.196752230272459</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-6.450392737876811</v>
+        <v>-4.615223713702733</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-5.160466454597987</v>
+        <v>-4.750256110628428</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-6.345710282718308</v>
+        <v>-5.915174963911291</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-5.459563773449425</v>
+        <v>-4.327177365998033</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-6.701410640716311</v>
+        <v>-6.272743984464505</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-8.875158700027349</v>
+        <v>-8.418342002965076</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-8.600683987545295</v>
+        <v>-8.178883456427052</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-6.578614142866478</v>
+        <v>-5.586426850361583</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ 50.45</t>
+          <t>X ≈ 50.34</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.4076528872826799</v>
+        <v>1.419852620992536</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>2.831262347861646</v>
+        <v>5.112789227825751</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.6683677686814065</v>
+        <v>1.901907920282234</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-2.101910281197377</v>
+        <v>-0.007204847144940629</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-1.082320925936806</v>
+        <v>1.696389995507332</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-4.321288210114709</v>
+        <v>-1.438258194812761</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-5.805764786258521</v>
+        <v>-3.537205510507285</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-6.090150049959533</v>
+        <v>-3.839790451160198</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-6.050426816315579</v>
+        <v>-4.368465198718688</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-2.721924043511535</v>
+        <v>-0.555021114914851</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-6.573978125982187</v>
+        <v>-4.888061066320574</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-10.29396391112614</v>
+        <v>-8.459902081948691</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-12.8073180253251</v>
+        <v>-10.23570827044274</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-11.66765028727381</v>
+        <v>-9.169011373155563</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-13.71934701629618</v>
+        <v>-11.17225573259415</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-12.01281872702086</v>
+        <v>-9.959607959335507</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-6.639181868516253</v>
+        <v>-5.449858453158427</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-9.777827404080625</v>
+        <v>-7.566087305961453</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-7.078770326123184</v>
+        <v>-5.375407635976082</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-7.581579688568787</v>
+        <v>-7.146948263648397</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-6.744815511706918</v>
+        <v>-5.071951247955596</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-8.199971817943762</v>
+        <v>-6.47347258581933</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-8.615152277875502</v>
+        <v>-6.895534471867705</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-7.31167418627119</v>
+        <v>-6.399397848306158</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ 53.33</t>
+          <t>X ≈ 53.23</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>7.076988002169905</v>
+        <v>6.823826134683451</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>5.516931463698725</v>
+        <v>3.437626616219099</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>2.250316406219966</v>
+        <v>2.186871010114245</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.9101401748642459</v>
+        <v>-0.2893801913826834</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.01927529391919336</v>
+        <v>-0.5632092357709411</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-4.11589712848459</v>
+        <v>-4.801955323004059</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>1.233814664400271</v>
+        <v>0.6835480302843848</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.3449503466774786</v>
+        <v>-0.248585613995246</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.2249795740280049</v>
+        <v>-0.7482541486734462</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>5.122848151130334</v>
+        <v>4.478060348985274</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>4.174226433982064</v>
+        <v>4.126133402867268</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>2.060519849859119</v>
+        <v>1.965084811843177</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0.9383598131347952</v>
+        <v>1.482468021703276</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>1.330420934133841</v>
+        <v>1.237410942883287</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>1.285662104655799</v>
+        <v>0.5584035831833845</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>0.6533980025215058</v>
+        <v>-0.1432268465425679</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>0.5190852798287651</v>
+        <v>-0.2486771040327582</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>1.641238441038119</v>
+        <v>0.8799711401499266</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>0.6301359569317668</v>
+        <v>-0.1694616003222791</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-1.637005963161407</v>
+        <v>-1.218607117660959</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>0.2744355989336285</v>
+        <v>-0.5221114061798957</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>1.425583502555199</v>
+        <v>1.298167034260167</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-0.7539295150240974</v>
+        <v>-0.3557508707586337</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-1.443258700762705</v>
+        <v>-1.151682197371464</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ 56.22</t>
+          <t>X ≈ 56.11</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-4.053155400422888</v>
+        <v>-2.585221904274036</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-4.37357493829473</v>
+        <v>-2.835770701096052</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-3.968028000369699</v>
+        <v>-4.069318091227579</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-7.227127866686345</v>
+        <v>-7.125055238650845</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-8.863270057578873</v>
+        <v>-7.391329456514043</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-2.30663207615374</v>
+        <v>-1.696792063978968</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-6.288541863544594</v>
+        <v>-6.176045256525377</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-5.941702654961702</v>
+        <v>-4.630627734456198</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-7.177595574627368</v>
+        <v>-5.732303205249437</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-3.513420457256373</v>
+        <v>-1.59704284212075</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>3.752490181473696</v>
+        <v>4.220315775891727</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-2.899810054153676</v>
+        <v>-2.833551212752624</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-4.289033378642834</v>
+        <v>-5.79809283298804</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.9459690830364664</v>
+        <v>-2.344259207335533</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-1.219811760189735</v>
+        <v>-1.789827149797219</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-0.6217324169413274</v>
+        <v>-1.850965532435303</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-0.3679453168656721</v>
+        <v>-0.7211606688315655</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-1.746671371005249</v>
+        <v>-1.473379863582224</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-4.078550690717655</v>
+        <v>-4.357797535800408</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-5.802532906227476</v>
+        <v>-6.624724304244268</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-4.434251048715801</v>
+        <v>-4.715781256916429</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-3.236211659806429</v>
+        <v>-4.174846003137581</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-1.050908921846592</v>
+        <v>-3.313806239855751</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-2.400626525388418</v>
+        <v>-4.721145205469512</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 59.1</t>
+          <t>X ≈ 58.99</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>154</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-1.691196062321168</v>
+        <v>-0.9302496113452889</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-5.919772408264159</v>
+        <v>-4.396461670678441</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.8669378347608543</v>
+        <v>1.446884275831117</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.2819286030677901</v>
+        <v>1.498669240205551</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.6167719145726238</v>
+        <v>0.5915357825996637</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-2.377066325526101</v>
+        <v>-1.189136839220559</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0.09652455911761848</v>
+        <v>0.6026192778179578</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-3.425828264059106</v>
+        <v>-3.557334668145579</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>1.807015790423463</v>
+        <v>1.717155031877823</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-2.858977786697743</v>
+        <v>-2.933299373612591</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-1.287315716654504</v>
+        <v>-0.7354231644319498</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-4.81494640400345</v>
+        <v>-3.581602935228602</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-2.691355224106246</v>
+        <v>-0.1847354187557784</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-3.561784749903559</v>
+        <v>-1.077469218187964</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-3.570577398133466</v>
+        <v>-1.757707728185608</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-2.326839826839894</v>
+        <v>0.08979958950248346</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-0.5127050157653485</v>
+        <v>1.921376745320494</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-3.214948316989208</v>
+        <v>-1.443003647149432</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-4.947108884116759</v>
+        <v>-2.525433243250859</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-4.760263074148796</v>
+        <v>-2.312993649199022</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-5.952159891465406</v>
+        <v>-4.177883043644513</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-5.378655203523863</v>
+        <v>-3.609499145536944</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-7.701583088444551</v>
+        <v>-5.965115258752284</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-7.128064692317025</v>
+        <v>-5.483426402533532</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 61.99</t>
+          <t>X ≈ 61.87</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>2.082495004952598</v>
+        <v>-1.054736670522736</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>4.627451195317875</v>
+        <v>0.8194617797041133</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>4.611491104495222</v>
+        <v>0.9854066047614083</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>5.336368432421473</v>
+        <v>3.928211320622019</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>7.867591279911181</v>
+        <v>6.484849865355258</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.8654007291631913</v>
+        <v>0.9833703837557195</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>5.119756320099022</v>
+        <v>4.434700717380252</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>6.27428835524384</v>
+        <v>5.545989362351996</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>8.475575278694862</v>
+        <v>7.794245049895032</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>11.29367646385131</v>
+        <v>10.53561538862883</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>8.69309098476932</v>
+        <v>8.396162187980849</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>12.44189747154546</v>
+        <v>11.67425758991401</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>7.002188642099419</v>
+        <v>5.612423356950821</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>9.658807607379444</v>
+        <v>8.204277786001093</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>13.31721107238882</v>
+        <v>11.78713433712506</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>9.595051231741877</v>
+        <v>8.093209328703239</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>5.144587332174481</v>
+        <v>3.018482979297126</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>7.19802000964826</v>
+        <v>5.022596157158475</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>7.413911390572586</v>
+        <v>5.239266026499507</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>9.039606121404006</v>
+        <v>6.881398977469928</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>7.058211032574583</v>
+        <v>6.319694799437841</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>3.385242769007206</v>
+        <v>2.680943730823117</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>3.659717481489345</v>
+        <v>3.638945756747702</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>3.583885228265984</v>
+        <v>3.477612558505648</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ 64.88</t>
+          <t>X ≈ 64.75</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.2246980451090508</v>
+        <v>0.65418094073231</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-3.665064905570603</v>
+        <v>-2.148773621093014</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-2.618611904912221</v>
+        <v>-0.8272702458099346</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-1.468211887087953</v>
+        <v>-0.1479877783621717</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-2.425120372057442</v>
+        <v>-2.322865881679924</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>2.109671900996453</v>
+        <v>1.657328759251932</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>5.685549304062768</v>
+        <v>6.614008318204732</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>4.165101834464835</v>
+        <v>5.678716899111997</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>1.722116966690095</v>
+        <v>3.888176094524496</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.9492012906536047</v>
+        <v>3.735262075691594</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.6400931044514806</v>
+        <v>2.730341066596132</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>4.67121960390169</v>
+        <v>6.933509169892474</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>2.926939524623144</v>
+        <v>5.193396459227266</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>3.94809667302134</v>
+        <v>6.866966924324053</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>-0.4367546990933775</v>
+        <v>2.352303186219082</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>0.7787502352719784</v>
+        <v>2.27239068498011</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>3.129305147983942</v>
+        <v>4.092026232277568</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>3.645582456585117</v>
+        <v>4.60593551778156</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>2.619237812664721</v>
+        <v>4.822816542665379</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>4.669437659899835</v>
+        <v>6.326551270685499</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>3.50577347951144</v>
+        <v>3.835625619606041</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>3.429927518102339</v>
+        <v>2.473708453458464</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>2.46216620573967</v>
+        <v>0.7841691444314378</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>5.491924014628204</v>
+        <v>4.491437443298196</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ 67.78</t>
+          <t>X ≈ 67.63</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-3.640847113431889</v>
+        <v>-2.550892686035773</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-3.317729174939679</v>
+        <v>-0.9391878570120724</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>3.796883354976693</v>
+        <v>5.280130383652939</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>1.110245125007715</v>
+        <v>2.198811053084043</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>8.011296757723528</v>
+        <v>8.769590262145215</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>2.935105049084058</v>
+        <v>3.331906032137468</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>5.452630049404164</v>
+        <v>6.265359086029605</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>2.542839657282748</v>
+        <v>2.248845786802917</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.7051468450130827</v>
+        <v>-1.349340053879708</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-0.8201677842074702</v>
+        <v>-2.139340759703778</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-1.20400287888765</v>
+        <v>-3.107933837342578</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.8248575454934652</v>
+        <v>-0.8981395915388504</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>0.02566459817673206</v>
+        <v>0.4846990643647615</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-0.8533090151121101</v>
+        <v>-0.3887573478961954</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>-2.169347049534693</v>
+        <v>-1.686863370333</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>-2.890749601275843</v>
+        <v>-0.5062892563693211</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-3.68256147509549</v>
+        <v>-0.6147877028862325</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-0.4979284947062226</v>
+        <v>2.378476614119066</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>-0.2820371137818327</v>
+        <v>0.7169328393768097</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>3.194282380396807</v>
+        <v>4.062494406867479</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>1.993841475588596</v>
+        <v>3.502524569915657</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>3.233784987863778</v>
+        <v>4.68425090579219</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>0.8766807529773359</v>
+        <v>2.418181211980318</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>-3.804414658140672</v>
+        <v>-2.146825896121626</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X ≈ 70.66</t>
+          <t>X ≈ 70.51</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>3.712094063038663</v>
+        <v>1.076090388417484</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.2991533235464914</v>
+        <v>-2.230022387325604</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-1.737172372577483</v>
+        <v>-2.712207850009214</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>1.226344196215038</v>
+        <v>1.277886604462473</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.1552596060207421</v>
+        <v>0.2433137232279847</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-6.275421266705408</v>
+        <v>-4.183669734377183</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-7.782664068242774</v>
+        <v>-5.743448129038811</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-8.060875512995892</v>
+        <v>-6.037715495021502</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-2.87232950755174</v>
+        <v>-0.5597527289816853</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-5.85112753652944</v>
+        <v>-5.172184084728471</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-5.577067894367516</v>
+        <v>-5.662514837067903</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-4.385229062521447</v>
+        <v>-5.181898504965083</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-4.037802894083399</v>
+        <v>-4.769101221522142</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-2.05299941758873</v>
+        <v>-1.957957990008474</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>-4.917025068110632</v>
+        <v>-4.176567552553713</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>-2.11675579322646</v>
+        <v>-1.316217583630973</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>-3.721261165497928</v>
+        <v>-3.731861077898159</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-2.355513634024952</v>
+        <v>-3.099751834207993</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>-2.874916370747769</v>
+        <v>-2.118930805487715</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>-4.158658796073986</v>
+        <v>-4.222978574340736</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>-1.760028493451649</v>
+        <v>-1.711902415455278</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>-1.100580337213742</v>
+        <v>-1.79036471023624</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>-3.031987977672735</v>
+        <v>-2.333866625709724</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-6.784290819131385</v>
+        <v>-7.441545802513161</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X ≈ 73.56</t>
+          <t>X ≈ 73.39</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.6898615479853163</v>
+        <v>4.695622398958378</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.4323168251676037</v>
+        <v>0.6846077511161823</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-1.870335874198595</v>
+        <v>-0.5829067822776466</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-1.795888318838145</v>
+        <v>-0.4124972709656092</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-8.430891389810661</v>
+        <v>-6.725281440742947</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-11.39353150292588</v>
+        <v>-10.34277959706663</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-7.441070737997421</v>
+        <v>-8.877398329488855</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-6.931880607947264</v>
+        <v>-8.446313419554613</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-9.252598150442054</v>
+        <v>-10.57418581458926</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-10.02551382647845</v>
+        <v>-9.121428967727425</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-8.176651034710225</v>
+        <v>-6.592227154631438</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-6.093195713748869</v>
+        <v>-3.403827711956787</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-4.854153056195486</v>
+        <v>-2.266244849794674</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-5.862633507445224</v>
+        <v>-4.028821342015775</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>-4.945973655419444</v>
+        <v>-3.214912531839197</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>-5.926389883082749</v>
+        <v>-4.170766247360213</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>-4.485503870454011</v>
+        <v>-2.763876534943066</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-3.802942999472002</v>
+        <v>-2.141157358118249</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>-4.374453193350824</v>
+        <v>-3.454828443001318</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>-3.400205808579607</v>
+        <v>-2.481246763737765</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>-1.580547252136192</v>
+        <v>-0.02261620008574283</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>-0.8689916387422301</v>
+        <v>0.3745584734390022</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>1.767687798149232</v>
+        <v>2.614669764354424</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>2.479257119729198</v>
+        <v>2.45253077006501</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X ≈ 76.44</t>
+          <t>X ≈ 76.27</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>129</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-1.702862617307886</v>
+        <v>-0.7995353723488137</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-4.363220811006634</v>
+        <v>-1.80148952584819</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-3.475658464688742</v>
+        <v>-2.268207829739893</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-10.39016287172839</v>
+        <v>-8.984248559965366</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-3.749209158229135</v>
+        <v>-2.357314793563141</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-1.236661576782929</v>
+        <v>-0.6495162545830695</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>0.3169711346756472</v>
+        <v>1.600116455926248</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>1.589147286821714</v>
+        <v>2.852902762686313</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>2.405828267186017</v>
+        <v>3.741440201623639</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>4.733687784947939</v>
+        <v>3.724242081488619</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>4.232553628660249</v>
+        <v>3.996477096092953</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>3.178610426762681</v>
+        <v>2.184994448741783</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>4.381029755255405</v>
+        <v>3.367768487509082</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>4.935144677258435</v>
+        <v>4.645427349266505</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>6.602582775026796</v>
+        <v>7.051676704532234</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>5.646582100070432</v>
+        <v>5.309539848660307</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>4.737471164643395</v>
+        <v>4.436640336333063</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>3.082242863922978</v>
+        <v>4.305555204517546</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>7.174103237095359</v>
+        <v>9.160196935341347</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>7.360949047063386</v>
+        <v>7.838193955763259</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>8.368790475996541</v>
+        <v>8.055997197445365</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>4.416975522339435</v>
+        <v>5.655253280141245</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>7.792225428619929</v>
+        <v>8.224469160768415</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>5.390811780047819</v>
+        <v>5.736748771130159</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X ≈ 79.34</t>
+          <t>X ≈ 79.15</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-5.395233078344248</v>
+        <v>-5.226012634691266</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>1.287533982955111</v>
+        <v>0.7802868693385818</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-1.027678048532067</v>
+        <v>-2.222049330304543</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-3.495018032887096</v>
+        <v>-4.600300010803693</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-6.462387452802787</v>
+        <v>-8.41629534560721</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-7.152614249161552</v>
+        <v>-8.22810197093132</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-4.415791003227383</v>
+        <v>-4.591559201429931</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-2.062423500611985</v>
+        <v>-3.072424779208177</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-1.143743336241094</v>
+        <v>-2.060254897755733</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>2.469305900003121</v>
+        <v>3.402846562020393</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>4.497751507077318</v>
+        <v>5.45745675068472</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>4.219002103629322</v>
+        <v>5.173928180951783</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>3.095840036773204</v>
+        <v>3.170702217944743</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>1.120375195414283</v>
+        <v>1.118316263785132</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>-0.4149610846224618</v>
+        <v>-2.240741336596997</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>0.1794258373205722</v>
+        <v>0.1063162579895334</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>0.9227016827992998</v>
+        <v>-0.006496194823874646</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>0.8178609789780609</v>
+        <v>-1.952567216765367</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>1.910945342358531</v>
+        <v>-0.8431062214501495</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>-0.5337877950418601</v>
+        <v>0.2739572370508085</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>2.432437966816671</v>
+        <v>4.25050036869272</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>4.988170952775981</v>
+        <v>4.175337846737435</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>4.385452682801898</v>
+        <v>6.237154150197576</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>6.064006394490953</v>
+        <v>7.893196974089982</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X ≈ 82.22</t>
+          <t>X ≈ 82.03</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>6.58642561384066</v>
+        <v>4.043020662815813</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>0.5698306336727583</v>
+        <v>-1.519847008438084</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.2681752210054071</v>
+        <v>1.530824566593303</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>5.237039383380854</v>
+        <v>5.184437305821277</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>3.76488527446994</v>
+        <v>6.028384758688503</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>1.679124187840053</v>
+        <v>3.053413497899889</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-4.774642677868485</v>
+        <v>-4.167343899415314</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-2.780126849894323</v>
+        <v>-1.237844563414804</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.4659123952523743</v>
+        <v>0.9942074892780397</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.1024644349252597</v>
+        <v>1.252915326421501</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.9647684291269769</v>
+        <v>-0.6059504105676368</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>4.438300349243242</v>
+        <v>4.407450861926023</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>5.587865555114398</v>
+        <v>6.491951213118973</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.3150315031503084</v>
+        <v>-0.1563331135610184</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>1.299552471996407</v>
+        <v>2.398086212912624</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>-1.515151515151508</v>
+        <v>-0.2688561091447639</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>-1.649068652129081</v>
+        <v>0.6871566521310868</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-1.753909355950164</v>
+        <v>1.626689730306474</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>-6.083472520480392</v>
+        <v>-1.408467387151418</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>-1.351172165057811</v>
+        <v>0.9645493255655282</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>-0.757354696660208</v>
+        <v>1.483701949720398</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-1.969564294432942</v>
+        <v>1.408539427765113</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>-0.5587259455872555</v>
+        <v>0.5652173913044223</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>3.910896346643945</v>
+        <v>3.663947962232285</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X ≈ 85.12</t>
+          <t>X ≈ 84.91</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>3.149276343358153</v>
+        <v>3.599435473967084</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>0.345363742539206</v>
+        <v>3.354146925536106</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>11.25302370585388</v>
+        <v>11.61498907489744</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>4.367230180238316</v>
+        <v>3.886862118558959</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>6.500575510160175</v>
+        <v>5.99266119036448</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>15.32951700489953</v>
+        <v>13.28810184662103</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>7.150160913601802</v>
+        <v>5.356367645948545</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>11.81022107378696</v>
+        <v>9.810142759075717</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>13.08627615693624</v>
+        <v>11.12565883834774</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>14.78249628336889</v>
+        <v>13.896387719166</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>15.05655592553081</v>
+        <v>14.16862273377033</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>9.839534917144547</v>
+        <v>9.133345222763253</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>8.71637285028843</v>
+        <v>8.736728353505065</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>4.79159027013813</v>
+        <v>5.657675096669514</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>7.837150676261309</v>
+        <v>8.606906182562717</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>9.6661054994388</v>
+        <v>9.18499440485833</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>7.063052559992258</v>
+        <v>7.884792775535693</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>6.958211856171005</v>
+        <v>7.76599265618367</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>5.939535335860775</v>
+        <v>5.576061695448161</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>2.422677442125121</v>
+        <v>3.36851720543774</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>0.6455633729245278</v>
+        <v>1.589746488426613</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>0.5697174115154269</v>
+        <v>1.514583966471363</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>4.547895827701183</v>
+        <v>5.4167550371156</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>6.941199376947004</v>
+        <v>7.693640433070037</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X ≈ 88</t>
+          <t>X ≈ 87.79</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.2053067327219296</v>
+        <v>-0.9164124186047502</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>2.434632498474627</v>
+        <v>-1.150252713482985</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-1.567489114658926</v>
+        <v>-2.404946815374565</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0.2836594300008741</v>
+        <v>-0.458617125662208</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>5.076074085658753</v>
+        <v>4.355355052105274</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>1.416886425602279</v>
+        <v>2.027856203297716</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.644937741711864</v>
+        <v>1.232774191064998</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-2.197376267143703</v>
+        <v>-0.3143624797464</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.8738378031777216</v>
+        <v>1.037682846102165</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-4.210856043316696</v>
+        <v>-2.309167078463446</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-1.372693837052253</v>
+        <v>0.483700013423217</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0.9126593236023126</v>
+        <v>2.709650324995977</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>1.071548538797444</v>
+        <v>1.58269166671964</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>4.696623508504743</v>
+        <v>6.405888111915026</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>4.038480210924099</v>
+        <v>3.231681591690517</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>4.632867132867133</v>
+        <v>5.071691974460094</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>3.216898713838347</v>
+        <v>1.142213826341525</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>0.5479554459146314</v>
+        <v>-1.561433065778047</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>-0.5182044552123202</v>
+        <v>-2.652144087405013</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>-0.3313586452442934</v>
+        <v>-2.445337302299585</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>-3.438007377312928</v>
+        <v>-3.541707423515021</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>-0.9497507746194245</v>
+        <v>-2.318168646769038</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>-1.95732734418862</v>
+        <v>-3.373235460191978</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>4.37709681284452</v>
+        <v>4.256833337726349</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X ≈ 90.9</t>
+          <t>X ≈ 90.67</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-2.955915606582671</v>
+        <v>-0.6452477185968206</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>7.668211704656578</v>
+        <v>9.970646946994506</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>7.600055669324234</v>
+        <v>10.07064588886167</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>6.887101649881494</v>
+        <v>9.490372265666124</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>6.551311177334199</v>
+        <v>6.553942340499987</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>12.2177294182261</v>
+        <v>12.2266767264343</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>8.706054706938524</v>
+        <v>8.722208626684122</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>8.427843262185448</v>
+        <v>7.1111094419674</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>2.989878389305595</v>
+        <v>1.735366147327944</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>6.326551754364957</v>
+        <v>2.257621969029373</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>2.491022355431028</v>
+        <v>-0.2037862551090939</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>2.212272951982996</v>
+        <v>-1.895704131402496</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>2.458973898825548</v>
+        <v>-1.680160356319824</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>2.237895022378915</v>
+        <v>-3.270958885899013</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>8.429066793291547</v>
+        <v>5.630679091988902</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>10.3933167289332</v>
+        <v>6.218832336917274</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>8.889536578257108</v>
+        <v>6.154782863849768</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>7.414832860737292</v>
+        <v>4.660237884170307</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>3.52113520056573</v>
+        <v>2.070992512366864</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>2.338117996835088</v>
+        <v>1.744961515399957</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>3.165434842567727</v>
+        <v>2.585967718244561</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>3.089588881158583</v>
+        <v>3.919255900514628</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>3.364063593640601</v>
+        <v>5.571341090018386</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>3.288231340417362</v>
+        <v>2.592300687278204</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X ≈ 93.78</t>
+          <t>X ≈ 93.55</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>11.51066803808319</v>
+        <v>7.098594645935208</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>8.145588209430343</v>
+        <v>6.662938628115754</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>2.162114614944784</v>
+        <v>-0.9090946231760597</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>5.994615140956611</v>
+        <v>1.67298518455879</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>8.689127698712369</v>
+        <v>6.301461940860754</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>7.360942369658225</v>
+        <v>5.01346643017402</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>9.619296716070899</v>
+        <v>7.424491288170287</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>13.88653981677237</v>
+        <v>13.56340944890563</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>12.41287548353557</v>
+        <v>10.4536066246748</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>7.094505262044535</v>
+        <v>7.959627103283154</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>10.39886793450948</v>
+        <v>9.803290689316057</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>11.63527004621301</v>
+        <v>9.400209280101038</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>10.51210797935689</v>
+        <v>8.190442571592449</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>8.775877587758771</v>
+        <v>4.862601094674076</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>9.632885805329742</v>
+        <v>6.625795257374229</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>7.196969696969688</v>
+        <v>5.657311908186074</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>8.578204075143731</v>
+        <v>7.291666666666664</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>5.443060341019518</v>
+        <v>4.022011936284699</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>4.143800206792328</v>
+        <v>2.633661455317508</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>4.330646016760362</v>
+        <v>2.848247900376492</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>2.272948333642809</v>
+        <v>-2.719196601004249</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>6.742556917688255</v>
+        <v>3.87230754370713</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>8.53218314532181</v>
+        <v>2.449275362318851</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>8.456350892098548</v>
+        <v>5.620469701362715</v>
       </c>
     </row>
   </sheetData>
@@ -3180,247 +3180,247 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; 11.43</t>
+          <t>X &gt; 11.46</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3345</v>
+        <v>3369</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.1596279459504544</v>
+        <v>0.2014770454743058</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.1081301719723058</v>
+        <v>0.2073378605441292</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.02307718178971641</v>
+        <v>0.1485127472733012</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.04933100700142745</v>
+        <v>0.07401899945740098</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.1009130176065938</v>
+        <v>0.02151565536278355</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.1350703895124283</v>
+        <v>-0.07075867969022198</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.08722717843632921</v>
+        <v>-0.1110611598145752</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.1104668461075349</v>
+        <v>-0.133429675527168</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.1412370705769916</v>
+        <v>-0.1364934292063182</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.1231009880118563</v>
+        <v>-0.1472685914326419</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.1295851490359183</v>
+        <v>-0.1537517581268446</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.123063964131731</v>
+        <v>-0.1176758029066107</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.1562562348952881</v>
+        <v>-0.1209084379382261</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.1809033362352608</v>
+        <v>-0.1150671190637951</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-0.1058250961718628</v>
+        <v>-0.01013601088387617</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>-0.2093331164312389</v>
+        <v>-0.08266028021063221</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>-0.2360723405646539</v>
+        <v>-0.08022314375987349</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-0.2933548403374644</v>
+        <v>-0.1067266977541976</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>-0.3283843250936869</v>
+        <v>-0.1118433856230183</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-0.3926092290389178</v>
+        <v>-0.1762604502510428</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>-0.3799244805203088</v>
+        <v>-0.1331942285249994</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-0.3782477830387521</v>
+        <v>-0.1907795718866581</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>-0.3250683897539659</v>
+        <v>-0.137272609985807</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>-0.4130607127390533</v>
+        <v>-0.2818752081059657</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; 14.32</t>
+          <t>X &gt; 14.34</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3306</v>
+        <v>3330</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.06512595958581358</v>
+        <v>-0.0362107328852872</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.1132854687400027</v>
+        <v>-0.01354102427403348</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.06186905822708155</v>
+        <v>0.04480575715280111</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.06644660431565796</v>
+        <v>0.06586267279916314</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.005723257185174191</v>
+        <v>0.1055334047623262</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.1081529153215399</v>
+        <v>-0.0792245300372727</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.02058692321086397</v>
+        <v>-0.05097967347148824</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.01071083544515972</v>
+        <v>-0.04015045856051103</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.04803466341019202</v>
+        <v>0.07486787007597684</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.04496169669953787</v>
+        <v>-0.04630288476816702</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.08484840940571559</v>
+        <v>-0.08592067406600989</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.1352379268266191</v>
+        <v>-0.1359424179594768</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.2159138731750616</v>
+        <v>-0.1860662672385232</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.1779550693308138</v>
+        <v>-0.1173974687225723</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-0.03391797912110661</v>
+        <v>0.05662438631654254</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-0.1456173076571403</v>
+        <v>-0.02328530626980552</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-0.1710756219174314</v>
+        <v>-0.01958782838877937</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-0.257971718708184</v>
+        <v>-0.07480556799134064</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-0.326148449202833</v>
+        <v>-0.1124654812142296</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-0.4537538733797035</v>
+        <v>-0.240134423158807</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-0.4345436304221266</v>
+        <v>-0.1899436757117101</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-0.4319694829566387</v>
+        <v>-0.2473403154365172</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-0.4418938813708593</v>
+        <v>-0.2561184133241028</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-0.5300649908690502</v>
+        <v>-0.4005513196583053</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; 17.21</t>
+          <t>X &gt; 17.22</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3253</v>
+        <v>3275</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.0366931732975786</v>
+        <v>0.007130553442799226</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.0115438242402206</v>
+        <v>0.1253013876418407</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.08757953307475219</v>
+        <v>0.2055587420609442</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.05811639327905738</v>
+        <v>0.08515920984081049</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.1125360945978287</v>
+        <v>0.2211738654531743</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.05485396265238762</v>
+        <v>0.0914789752077354</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.1085933521565323</v>
+        <v>0.103154476150543</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.03140850982094179</v>
+        <v>0.02814970909774672</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.1210465454397962</v>
+        <v>0.1733681040594703</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.0697118736147786</v>
+        <v>0.09391730693944567</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.08600260021120931</v>
+        <v>0.1099528984132192</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.07000019610394759</v>
+        <v>0.09420456040787428</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.1468715215343863</v>
+        <v>-0.09018818670202933</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.1046840816475054</v>
+        <v>-0.01618436980625404</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>0.02175301823128706</v>
+        <v>0.1417567623734683</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-0.07073959465864021</v>
+        <v>0.08159071226313586</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-0.1250864993124807</v>
+        <v>0.05665371724558099</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-0.3037294346134516</v>
+        <v>-0.08867438759582313</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-0.3151539759187472</v>
+        <v>-0.1000783820808664</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-0.4171698762811999</v>
+        <v>-0.2029872322859063</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-0.4195168588223694</v>
+        <v>-0.1729285513804939</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>-0.3542172758601225</v>
+        <v>-0.1689903913961075</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>-0.3994813794588552</v>
+        <v>-0.212507299463816</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>-0.4263587745029014</v>
+        <v>-0.2955608329884285</v>
       </c>
     </row>
     <row r="9">
@@ -3430,2211 +3430,2211 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3182</v>
+        <v>3202</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.06383992817735873</v>
+        <v>-0.04992259895816176</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.08687608821821868</v>
+        <v>0.169864449224967</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.07244644212564566</v>
+        <v>0.1570207043653582</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.06030554811042776</v>
+        <v>0.06135864836992511</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.10421667477695</v>
+        <v>0.2204481332317769</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.2286437739450022</v>
+        <v>0.2395344212602524</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.2697032201359448</v>
+        <v>0.2695514425223706</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.3222134122833253</v>
+        <v>0.3241148051589207</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.3191598541503424</v>
+        <v>0.3765629475627748</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.3780448836123185</v>
+        <v>0.4067250378198466</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.4199301534427136</v>
+        <v>0.4481448438635596</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.4099570983820513</v>
+        <v>0.4384260783372156</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.1823062021866875</v>
+        <v>0.2441580357255262</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.2618751376861326</v>
+        <v>0.3567227839228266</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>0.4688314688616089</v>
+        <v>0.5961649686346036</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>0.3923287436928078</v>
+        <v>0.5531600067405833</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>0.2771889046179083</v>
+        <v>0.4678410979536736</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>0.2225147533575296</v>
+        <v>0.4470462772157902</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>0.1433436639629164</v>
+        <v>0.3994862136586335</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>0.03494172105607163</v>
+        <v>0.2895038787503665</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-0.01786177751904461</v>
+        <v>0.2709230037799415</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>0.03192040177536626</v>
+        <v>0.2768019257296075</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>0.01106241873456781</v>
+        <v>0.2268796915934885</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-0.1088739521960562</v>
+        <v>0.05207494808351498</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; 22.99</t>
+          <t>X &gt; 22.98</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3097</v>
+        <v>3113</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.1187929893958</v>
+        <v>0.1462905507140562</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.137486628063975</v>
+        <v>0.2197704923976076</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.145483003197505</v>
+        <v>0.2426235000556858</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.117599550949592</v>
+        <v>0.001546756373628</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.02861511789129167</v>
+        <v>0.1731301046166749</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.08704659961849615</v>
+        <v>0.1384316441822975</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.1184398180417716</v>
+        <v>0.1599287648706067</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.115755795265116</v>
+        <v>0.1607639191531689</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.2078672013568621</v>
+        <v>0.3069201372686834</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.2575607120089529</v>
+        <v>0.328595935967428</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.2929828286243747</v>
+        <v>0.3634192344411602</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.2904084921464332</v>
+        <v>0.3612736203409455</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.2162973293929795</v>
+        <v>0.3212496206878726</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.2075859759889127</v>
+        <v>0.3480597053059356</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>0.2451944588755026</v>
+        <v>0.4215869096681075</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>0.4722946513149537</v>
+        <v>0.68170335843012</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>0.3899384400695922</v>
+        <v>0.6290064102564088</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>0.3044442543221777</v>
+        <v>0.5794001472697303</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>0.281630118815805</v>
+        <v>0.5885470657515484</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>0.1973478853983437</v>
+        <v>0.5014400723367061</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>0.09363421113954473</v>
+        <v>0.4344191456795343</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>0.05006713933664031</v>
+        <v>0.346357837982147</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>0.09858962457531106</v>
+        <v>0.3844070257742018</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>-0.151686211256596</v>
+        <v>0.08079735957022649</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; 25.88</t>
+          <t>X &gt; 25.86</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3012</v>
+        <v>3026</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.06040866978019466</v>
+        <v>0.07103950053591745</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.155241917696074</v>
+        <v>0.2193507988662091</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.2373814939129346</v>
+        <v>0.3444201660942099</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.07900940589993155</v>
+        <v>0.04768156781161537</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.2461386542692594</v>
+        <v>0.3963021399330415</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.2678702071875207</v>
+        <v>0.3232751677445265</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.3220946891927454</v>
+        <v>0.3681791987475549</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.3082586575262525</v>
+        <v>0.3778273009042152</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.4679719022683528</v>
+        <v>0.5903442027472039</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.4747361422754111</v>
+        <v>0.5697258233658005</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.7019984791219969</v>
+        <v>0.7952652490471905</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.7073274835914205</v>
+        <v>0.8011208882803871</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.5966675773226413</v>
+        <v>0.7261786711483253</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.4947216575962301</v>
+        <v>0.6621896021948857</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>0.4857670523812416</v>
+        <v>0.6915844928504313</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>0.7026025664196638</v>
+        <v>0.9431533737113824</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>0.6217753530537635</v>
+        <v>0.8920107978898741</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>0.6363727757112727</v>
+        <v>0.9438254374945103</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>0.6401065538449586</v>
+        <v>0.9801917533489615</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>0.4487614779415168</v>
+        <v>0.7855416297494244</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>0.357511187538563</v>
+        <v>0.732987838304652</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>0.314854738243632</v>
+        <v>0.6446545274147581</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>0.423381890154829</v>
+        <v>0.7429654845520801</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>0.1682910104131778</v>
+        <v>0.4023599855662781</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; 28.77</t>
+          <t>X &gt; 28.74</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2913</v>
+        <v>2926</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.186904082740277</v>
+        <v>0.1598189240633161</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.3989488838436515</v>
+        <v>0.4573903492290157</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.43051288334307</v>
+        <v>0.5274245082069982</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.0934987135243901</v>
+        <v>0.2067614398335564</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.4070588903277752</v>
+        <v>0.5086489519081354</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.2864379267327308</v>
+        <v>0.3259086448627357</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.4030743419537899</v>
+        <v>0.4333343332903894</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.2957446470298422</v>
+        <v>0.351725470692152</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.459495530155607</v>
+        <v>0.5331076215612143</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.5613211638809474</v>
+        <v>0.6068722608881814</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.547532133806591</v>
+        <v>0.5926592495315361</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.699422868066037</v>
+        <v>0.7442062275567451</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.6576579674265659</v>
+        <v>0.7387015573675271</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.6283059812830629</v>
+        <v>0.7491120191137384</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>0.4703457075378381</v>
+        <v>0.6324223611052346</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>0.7770473757451128</v>
+        <v>0.9756638132246707</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>0.6637839049813721</v>
+        <v>0.8922356233662896</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>0.7510787971861319</v>
+        <v>1.018562575147634</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>0.7475737916979952</v>
+        <v>1.048878104925144</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>0.543287184789321</v>
+        <v>0.8402843053821769</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>0.4332329511879891</v>
+        <v>0.77118692010648</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>0.323058119198727</v>
+        <v>0.6141108223956664</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>0.3572307376196875</v>
+        <v>0.6391170659972403</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>0.3157273549765662</v>
+        <v>0.5316111914515744</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; 31.66</t>
+          <t>X &gt; 31.62</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2794</v>
+        <v>2805</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.2080481110869243</v>
+        <v>0.2299556310817437</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.2652884189380984</v>
+        <v>0.3737051892850687</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.3953377947111036</v>
+        <v>0.5359434288741909</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.2525904751970955</v>
+        <v>0.4040442410471812</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.6651962963062701</v>
+        <v>0.8369522716881974</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.4601453762026466</v>
+        <v>0.533382866705054</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.5791446609509308</v>
+        <v>0.679579251802366</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.4434848911800344</v>
+        <v>0.5721876689618526</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.5562479105858316</v>
+        <v>0.7204805660655538</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.6595676506363333</v>
+        <v>0.7606996662738936</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.6335975415643418</v>
+        <v>0.7342416642373664</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.6967734138169774</v>
+        <v>0.7977322642884133</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.5938677613308059</v>
+        <v>0.7688928665265422</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.6440415551730183</v>
+        <v>0.8259556119721623</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>0.5073446797886163</v>
+        <v>0.7336078427987331</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>0.6589203936470795</v>
+        <v>0.8897592184556657</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>0.6179727410739417</v>
+        <v>0.8783042911332402</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>0.9279413282244349</v>
+        <v>1.229231245247497</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>0.8436311340910763</v>
+        <v>1.180517920323432</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>0.5869478544575557</v>
+        <v>0.9181422874656064</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>0.6027025689088603</v>
+        <v>0.9773845955769431</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>0.3836926848082811</v>
+        <v>0.6743500564728393</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>0.3718395519073709</v>
+        <v>0.6899501069137628</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>0.3317982793569669</v>
+        <v>0.5491684535908732</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; 34.55</t>
+          <t>X &gt; 34.5</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2676</v>
+        <v>2679</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.1537957437108943</v>
+        <v>0.1837358970284484</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.2282451358372626</v>
+        <v>0.3456896471606967</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.7991546582348406</v>
+        <v>0.9449072990696337</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.3838196864111509</v>
+        <v>0.612052745793477</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.7920768329115049</v>
+        <v>1.003902837062334</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.3466025428184025</v>
+        <v>0.5305064467682428</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.3187014779756723</v>
+        <v>0.423957357697752</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.263704318936874</v>
+        <v>0.3999175427746806</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.2307867389468257</v>
+        <v>0.4377403553530144</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.2236004566402841</v>
+        <v>0.3684486329891996</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.2215173625200464</v>
+        <v>0.3650115926428512</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.4112984870459186</v>
+        <v>0.5557708332729447</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.1668521422977705</v>
+        <v>0.3174893095816245</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.3033400619227109</v>
+        <v>0.4630667423123995</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>0.07760141783058572</v>
+        <v>0.2494216310005797</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>0.1722276852825146</v>
+        <v>0.3491779864675948</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>0.3217590276539184</v>
+        <v>0.5280078803673334</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>0.6872152156335289</v>
+        <v>0.9015083529389543</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>0.5895874292785948</v>
+        <v>0.8403181865643958</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>0.3879693434150298</v>
+        <v>0.6299599142912555</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>0.3908991421765933</v>
+        <v>0.6812508262888173</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>0.1282071419035162</v>
+        <v>0.3300969257784985</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>0.1037281922032065</v>
+        <v>0.3721609344581438</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>0.0652651467527221</v>
+        <v>0.1949377864690973</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; 37.44</t>
+          <t>X &gt; 37.38</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2555</v>
+        <v>2558</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.4300527697000973</v>
+        <v>0.417000601081952</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.3290118498076211</v>
+        <v>0.4428328958128631</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.6440118892067019</v>
+        <v>0.7797537007535738</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.4374856064215393</v>
+        <v>0.6531900112621258</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.6860348300176256</v>
+        <v>0.8822902562559634</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.09388142125718701</v>
+        <v>0.2628263467260936</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.2568762511962177</v>
+        <v>0.343867472646906</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.1734447051575856</v>
+        <v>0.2941502941502847</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.0201519883578456</v>
+        <v>0.2110991832935483</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.01002050803522536</v>
+        <v>0.1759098292592256</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-0.005172469530926094</v>
+        <v>0.1594238361891414</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.1676295224102304</v>
+        <v>0.3331957993292818</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.1524777925250262</v>
+        <v>0.01933907392949408</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.03825909523036586</v>
+        <v>0.1444153542296505</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-0.1656067342795495</v>
+        <v>0.03064206619453103</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>0.02249053030303827</v>
+        <v>0.2254623161157525</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>-0.01002286009374842</v>
+        <v>0.2226486354775759</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>0.0648055491603543</v>
+        <v>0.3079147767936732</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>-0.08701004670075463</v>
+        <v>0.1944625998096328</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-0.1899116728114052</v>
+        <v>0.08087865759740964</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>-0.1222363903090269</v>
+        <v>0.2002359123369004</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>-0.3546381247122596</v>
+        <v>-0.1250882896261984</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>-0.3541360149699244</v>
+        <v>-0.09273323478939943</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>-0.2734124951990751</v>
+        <v>-0.1144794776834175</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; 40.33</t>
+          <t>X &gt; 40.26</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2427</v>
+        <v>2429</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.5839272918182417</v>
+        <v>0.5269029242411349</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.1260988117621054</v>
+        <v>0.2400962930362525</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.903010033444815</v>
+        <v>1.030391966195793</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.4771766046501469</v>
+        <v>0.6833885403937003</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.7566445406344542</v>
+        <v>0.9395277418076589</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.08224895478762306</v>
+        <v>0.155766051282221</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.1716620428414828</v>
+        <v>0.2195797445709857</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.1805711887364794</v>
+        <v>0.2009578696695229</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.05798946170943253</v>
+        <v>0.1476491421702946</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-0.07588555627406635</v>
+        <v>-0.01112278813429413</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-0.02432955765352318</v>
+        <v>0.03896286391952941</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.008115544315181467</v>
+        <v>0.07261815127088767</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-0.3105806987138777</v>
+        <v>-0.2399791528475319</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.1786491842772477</v>
+        <v>-0.05426420265937537</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>-0.4423733653241726</v>
+        <v>-0.3021135852187982</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>-0.2759495406554251</v>
+        <v>-0.1268293065077941</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>-0.3032025840406973</v>
+        <v>-0.1244355500821044</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-0.1777837524470485</v>
+        <v>0.01331284897939611</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>-0.2668632648266538</v>
+        <v>-0.07655492375671713</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-0.3028334004026121</v>
+        <v>-0.1254471263395018</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-0.186129465360807</v>
+        <v>0.07137357443435377</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-0.4267879525218774</v>
+        <v>-0.2672783605846547</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-0.3995320286677568</v>
+        <v>-0.2050456253354724</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-0.3517548875770586</v>
+        <v>-0.260551294932057</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; 43.22</t>
+          <t>X &gt; 43.14</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2289</v>
+        <v>2284</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.9085651634509233</v>
+        <v>0.9356341414546208</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.2690430451185222</v>
+        <v>0.4288577405333598</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.9207061902538385</v>
+        <v>1.130685377772217</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.4254273993700863</v>
+        <v>0.6687179615726819</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.8297327039233835</v>
+        <v>1.045333734516831</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.1895330214966009</v>
+        <v>0.376180383993173</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.6365656175365899</v>
+        <v>0.7550114152387124</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.358354172783514</v>
+        <v>0.4066127109605304</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.3127712632746196</v>
+        <v>0.4724541345921054</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.4105565014740904</v>
+        <v>0.5280992373184361</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.3363357779416276</v>
+        <v>0.4773261886563915</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.3442236941910366</v>
+        <v>0.4436568956022739</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-0.1870403668502902</v>
+        <v>-0.07952699384184569</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.009926886324208795</v>
+        <v>0.09009513108217959</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>-0.1861946635544811</v>
+        <v>-0.08661662206775844</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>-0.1328732349674766</v>
+        <v>-0.02291932649488615</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>-0.1535922821436699</v>
+        <v>-0.0137540011639814</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-0.05779978866156199</v>
+        <v>0.09751072744393241</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>-0.4274695020920447</v>
+        <v>-0.2300344817729325</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>-0.2406236921240179</v>
+        <v>-0.03345373132514595</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>-0.1715490649830258</v>
+        <v>0.1244122023771865</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>-0.3347694256931248</v>
+        <v>-0.1434404877889293</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>-0.2350435118130818</v>
+        <v>-0.005137475026160132</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>-0.3108757650363572</v>
+        <v>-0.1851345017896548</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; 46.11</t>
+          <t>X &gt; 46.02</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2175</v>
+        <v>2170</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.7796751037004199</v>
+        <v>0.8489560715234319</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.2158557034266479</v>
+        <v>0.374320965005289</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>1.022454153250436</v>
+        <v>1.22392695460502</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.08045753188373794</v>
+        <v>0.3570508308196665</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.7066459874170974</v>
+        <v>0.9506601198145788</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.1599837953357266</v>
+        <v>0.009698025904150143</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.5339401730872453</v>
+        <v>0.6784769468827747</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.5305798506429227</v>
+        <v>0.6022847742884281</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.4804499917880349</v>
+        <v>0.6649764032533341</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.8069388049865509</v>
+        <v>0.9025289851163407</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.6687217636853546</v>
+        <v>0.7892509023431629</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.4625899917731005</v>
+        <v>0.5392681207992425</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.2210836341648488</v>
+        <v>-0.1363456864725023</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.08947224997729819</v>
+        <v>0.1927162487965219</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-0.2201187700245413</v>
+        <v>-0.09518270912922588</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-0.1033057851239718</v>
+        <v>0.08020616930076585</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>0.01972075781797145</v>
+        <v>0.1872081227989568</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-0.01176363402503711</v>
+        <v>0.1275325615050633</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-0.2741726249736018</v>
+        <v>-0.09047647571698292</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-0.2252578494883224</v>
+        <v>-0.03277019223314426</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-0.03217183354631459</v>
+        <v>0.2551859730101711</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-0.2919258409324286</v>
+        <v>-0.1148011119098129</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-0.2473361859216396</v>
+        <v>-0.02807762401617708</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-0.09328338167365047</v>
+        <v>0.02139136034888622</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; 49</t>
+          <t>X &gt; 48.9</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2032</v>
+        <v>2025</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.7218979846072457</v>
+        <v>0.8691379777717501</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.005035676487665341</v>
+        <v>0.2310742793227831</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.6157688038931113</v>
+        <v>0.8391252754704226</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.4403224704515907</v>
+        <v>-0.09641417823976184</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.3513380373932904</v>
+        <v>0.6574394463667872</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.1969898941563883</v>
+        <v>-0.01896028096846436</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.4036104415610993</v>
+        <v>0.4604675107203846</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.4685362517099847</v>
+        <v>0.4496647143705843</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.6080626493109733</v>
+        <v>0.626613231897835</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>1.256715600725457</v>
+        <v>1.280955528329535</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>1.481755635044244</v>
+        <v>1.48390856794277</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>0.9868535616023095</v>
+        <v>0.9416094082643696</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>0.2361392637414568</v>
+        <v>0.2483618565247525</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.5351492439376528</v>
+        <v>0.5696069009165257</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>0.2993738686743797</v>
+        <v>0.3591631677332714</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>0.382882882882889</v>
+        <v>0.4580624497640287</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>0.4750486268555463</v>
+        <v>0.5310859580052494</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>0.350571259351895</v>
+        <v>0.4768063182751234</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>0.1531058617672869</v>
+        <v>0.3266006999808866</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>0.1431012780345284</v>
+        <v>0.2747305683574339</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>0.4371692832968463</v>
+        <v>0.7226179946565026</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>0.3121107234625455</v>
+        <v>0.4797734210299396</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>0.3405224438186139</v>
+        <v>0.5555603244774474</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>0.3631153874457311</v>
+        <v>0.4229388371651837</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; 51.89</t>
+          <t>X &gt; 51.78</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1887</v>
+        <v>1874</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.7460450641578831</v>
+        <v>0.8247634254097775</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.2229812056506972</v>
+        <v>-0.1622762848308739</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.6117270180455776</v>
+        <v>0.7534901744210032</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.3126434918834207</v>
+        <v>-0.1036023367217922</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.4615026106221549</v>
+        <v>0.5737246475833189</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.1199275705038971</v>
+        <v>0.09540150397844371</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.880748442638918</v>
+        <v>0.7825852408193086</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.9725158562367895</v>
+        <v>0.795293172212169</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>1.119711283394622</v>
+        <v>1.029098206830106</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>1.56244042765411</v>
+        <v>1.428891746648588</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>2.100770682923859</v>
+        <v>1.997338351706787</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>1.853689032479686</v>
+        <v>1.699148487785273</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>1.238418705667613</v>
+        <v>1.093129513500259</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>1.47283124289136</v>
+        <v>1.354308800268107</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>1.376594074461735</v>
+        <v>1.288322321388257</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>1.335387776065744</v>
+        <v>1.297479862663721</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>1.021717106892062</v>
+        <v>1.013008373205736</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>1.128853085635797</v>
+        <v>1.124872987036973</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>0.70881441886538</v>
+        <v>0.7860474762506229</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>0.7366777169097176</v>
+        <v>0.8727420430814874</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>0.9890441085621191</v>
+        <v>1.189522986990774</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>0.9661923177942455</v>
+        <v>1.040040308454827</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>1.028690347711382</v>
+        <v>1.155942028985514</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>0.9528580944881071</v>
+        <v>0.9726575348739246</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; 54.77</t>
+          <t>X &gt; 54.67</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1724</v>
+        <v>1716</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.1474698327797128</v>
+        <v>0.2724021736235116</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.7656759649917362</v>
+        <v>-0.4937358759531918</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.4568023833167842</v>
+        <v>0.6215122186870161</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.2561516361259564</v>
+        <v>-0.08649691653739922</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.5069589902278651</v>
+        <v>0.6784073711089391</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.5204144764987504</v>
+        <v>0.5463236360665604</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.8473668915095089</v>
+        <v>0.791704051579508</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1.031850646293734</v>
+        <v>0.8914078856275367</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>1.246848528034931</v>
+        <v>1.192747199935916</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>1.225812551246555</v>
+        <v>1.148140791421781</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>1.904730493003626</v>
+        <v>1.801330415760773</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>1.834133682576642</v>
+        <v>1.674662509229833</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>1.266788542954643</v>
+        <v>1.057281329178544</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>1.486295790645123</v>
+        <v>1.365072122801216</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>1.385191470678883</v>
+        <v>1.355529291456072</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>1.399868247694343</v>
+        <v>1.430132345213018</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>1.069239721631817</v>
+        <v>1.129177548848908</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>1.080408298553095</v>
+        <v>1.147422224687411</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>0.7162532757651334</v>
+        <v>0.8740255846996448</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>0.9611037261043833</v>
+        <v>1.065302163942377</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>1.056608602221885</v>
+        <v>1.347121025522803</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>0.9227580004415472</v>
+        <v>1.016273395472759</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>1.197232712923601</v>
+        <v>1.295130536071511</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>1.179405100071563</v>
+        <v>1.168255249148267</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 57.66</t>
+          <t>X &gt; 57.55</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1567</v>
+        <v>1555</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.5683365600374159</v>
+        <v>0.5682719334572752</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.4041953403532119</v>
+        <v>-0.2512486689769915</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.9001325493913086</v>
+        <v>1.107186610903256</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.4422805707649005</v>
+        <v>0.6422541380351205</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1.445775812503335</v>
+        <v>1.513923531396593</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.8036603659476569</v>
+        <v>0.7785690558140459</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>1.562323926955258</v>
+        <v>1.513123754862399</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>1.730541053630752</v>
+        <v>1.463142763333963</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>2.09090578656587</v>
+        <v>1.909745987868291</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>1.700643171753867</v>
+        <v>1.432368807499174</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>1.719600773099472</v>
+        <v>1.550875982975505</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>2.308434363282871</v>
+        <v>2.141429331891679</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>1.823434389598425</v>
+        <v>1.76706604950575</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>1.729987931786162</v>
+        <v>1.74912507723981</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>1.646190518060102</v>
+        <v>1.681189990518305</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>1.602415346831421</v>
+        <v>1.769847302320017</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>1.213233372585286</v>
+        <v>1.320755975245412</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>1.363657506032766</v>
+        <v>1.418772151511476</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>1.196651631054102</v>
+        <v>1.415712737368779</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>1.638762278290798</v>
+        <v>1.861504261291607</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>1.606745784862092</v>
+        <v>1.974855602675682</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>1.339451195501496</v>
+        <v>1.553746207804764</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>1.422477280032041</v>
+        <v>1.772325919302567</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>1.538093654760274</v>
+        <v>1.778025971459172</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 60.55</t>
+          <t>X &gt; 60.43</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1413</v>
+        <v>1401</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.8145984311224908</v>
+        <v>0.7329916464477009</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.1969362013723952</v>
+        <v>0.2043992983763445</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>1.092721961393735</v>
+        <v>1.069846539240949</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.5212106576511317</v>
+        <v>0.5481157185245991</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1.670568699955346</v>
+        <v>1.61531376217085</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>1.150321307552012</v>
+        <v>0.9948622091583275</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>1.722078422813013</v>
+        <v>1.613207758763068</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>2.29252327226078</v>
+        <v>2.015001096273181</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>2.121846380625271</v>
+        <v>1.930915871681663</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>2.197586998789639</v>
+        <v>1.912249535472924</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>2.047318493851137</v>
+        <v>1.802189379621296</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>3.084797164529931</v>
+        <v>2.770513535415255</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>2.315492139428947</v>
+        <v>1.981610964646556</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>2.306727488035435</v>
+        <v>2.059828518707242</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>2.214755457263088</v>
+        <v>2.059198733330867</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>2.03065688734479</v>
+        <v>1.954520641202173</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>1.401339891910133</v>
+        <v>1.254734848484844</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>1.862670454897156</v>
+        <v>1.733342796046642</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>1.866247610768404</v>
+        <v>1.848929354795928</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>2.336179054140544</v>
+        <v>2.320371269297006</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>2.430575561333747</v>
+        <v>2.651173769366125</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>2.071643966520533</v>
+        <v>2.121297802676011</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>2.416890087353622</v>
+        <v>2.622836941015947</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>2.482600650832389</v>
+        <v>2.576215597151446</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 63.44</t>
+          <t>X &gt; 63.31</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1274</v>
+        <v>1261</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0.6762643465366338</v>
+        <v>0.9314706031295898</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.2864559368995216</v>
+        <v>0.1361132179751721</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.7088060187790575</v>
+        <v>1.079221313885782</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.004148000663683149</v>
+        <v>0.1728473725343989</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.9944414325975259</v>
+        <v>1.074683266971945</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1.181407618694905</v>
+        <v>0.996138066062656</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>1.351374162434077</v>
+        <v>1.299957152731032</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>1.858092074038922</v>
+        <v>1.622980194408761</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>1.428621642138864</v>
+        <v>1.279951490278108</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>1.205156515552929</v>
+        <v>0.9548576088735317</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>1.322230286443272</v>
+        <v>1.070106752206279</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>2.063889046260577</v>
+        <v>1.781993180435215</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>1.804149271398181</v>
+        <v>1.578507289053704</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>1.504577459315797</v>
+        <v>1.377653342322525</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>1.003420033006819</v>
+        <v>0.9791741619342176</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>1.20534227677085</v>
+        <v>1.27298502165408</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>0.992932204157583</v>
+        <v>1.058918243953734</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>1.280556178515369</v>
+        <v>1.368160027961267</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>1.260968752532314</v>
+        <v>1.472524014559212</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>1.604800433771928</v>
+        <v>1.8139923009035</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>1.925676557799612</v>
+        <v>2.243883567772123</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>1.928323532026312</v>
+        <v>2.059164234126776</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>2.281291180144152</v>
+        <v>2.510025494384351</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>2.362444798192463</v>
+        <v>2.476139804455499</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 66.33</t>
+          <t>X &gt; 66.19</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1113</v>
+        <v>1106</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0.806592239667772</v>
+        <v>0.9703312701020863</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>0.2022736623422077</v>
+        <v>0.4563279196529066</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>1.190130624092888</v>
+        <v>1.346405935723794</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.2076348256744112</v>
+        <v>0.2178107074249596</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>1.48909502698158</v>
+        <v>1.550831655797474</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>1.047130395468898</v>
+        <v>0.9034757175596297</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>0.7244180098714423</v>
+        <v>0.5552212299024362</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>1.524373681021338</v>
+        <v>1.054590330729738</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>1.386166343618882</v>
+        <v>0.9144227256685369</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>1.242181485192454</v>
+        <v>0.56519875502471</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>1.60608838701296</v>
+        <v>0.8374337696290439</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>1.686728022199276</v>
+        <v>1.060035695475115</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>1.641733071246136</v>
+        <v>1.071899855620707</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>1.151112415823796</v>
+        <v>0.6083553267617177</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>1.211747195511883</v>
+        <v>0.786737454190849</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>1.267050559503396</v>
+        <v>1.132923649307294</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>0.6838971242330132</v>
+        <v>0.6338443396226339</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>0.9384454590461573</v>
+        <v>0.9144030651021922</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>1.0644895803119</v>
+        <v>1.00299838901087</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>1.161488130621343</v>
+        <v>1.181581233709821</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>1.697109078558277</v>
+        <v>2.020809410417456</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>1.71111037680776</v>
+        <v>2.001068073189685</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>2.255126868265556</v>
+        <v>2.751895055182445</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>1.909752836066538</v>
+        <v>2.193706591055296</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 69.22</t>
+          <t>X &gt; 69.07</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>961</v>
+        <v>947</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>1.510037381885411</v>
+        <v>1.561539938556066</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>0.7590274930049006</v>
+        <v>0.6906331028521961</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.7778242608313448</v>
+        <v>0.6859390009606159</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.0648702413886042</v>
+        <v>-0.1147965311809429</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.457487677270052</v>
+        <v>0.3388119953863935</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.7485121360001088</v>
+        <v>0.4957456013844777</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.02343654789024185</v>
+        <v>-0.4035030775149124</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>1.363284369479466</v>
+        <v>0.8540764790764683</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>1.716946369292195</v>
+        <v>1.294505388760584</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>1.568380329051749</v>
+        <v>1.019287226874582</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>2.050556516479027</v>
+        <v>1.499855574812244</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>2.083981930929042</v>
+        <v>1.388810638067739</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>1.897344317767001</v>
+        <v>1.170490062389128</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>1.468148896055069</v>
+        <v>0.7757691760443137</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>1.746530052168573</v>
+        <v>1.202051636977863</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>1.924683883580862</v>
+        <v>1.408145245930939</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>1.374533656072693</v>
+        <v>0.8434879454926616</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>1.165634679618847</v>
+        <v>0.668587126038112</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>1.277467787910489</v>
+        <v>1.051028402096215</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>0.8399639620824644</v>
+        <v>0.6978798667276962</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>1.650175338341207</v>
+        <v>1.772031469171189</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>1.470271104299428</v>
+        <v>1.550565358951253</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>2.47315372521021</v>
+        <v>2.807925151348378</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>2.813554562517631</v>
+        <v>2.922476037159974</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; 72.11</t>
+          <t>X &gt; 71.95</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>825</v>
+        <v>818</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>1.147031674446815</v>
+        <v>1.638096163455671</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0.9334669973091252</v>
+        <v>1.151225472330104</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>1.192417645247829</v>
+        <v>1.221832575257814</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.1265969802555063</v>
+        <v>-0.3344250452371682</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.5073095168941819</v>
+        <v>0.3538722363502558</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>1.906396915112772</v>
+        <v>1.233697408613395</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>1.255660352434539</v>
+        <v>0.4386153963806763</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>2.916842847075408</v>
+        <v>1.940923868634712</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>2.47348154414162</v>
+        <v>1.586925067475441</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>2.791474959014231</v>
+        <v>1.995692849364545</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>3.307958843600396</v>
+        <v>2.629373647101403</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>3.15042156136451</v>
+        <v>2.425022715636487</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>2.875744342993251</v>
+        <v>2.107173773421579</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>2.048604860486051</v>
+        <v>1.206882628881488</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>2.845007017450953</v>
+        <v>2.050269088627701</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>2.590909090909093</v>
+        <v>1.837781926876524</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>2.214567711507371</v>
+        <v>1.565028317152098</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>1.746090644049829</v>
+        <v>1.262860629548804</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>1.961982024974155</v>
+        <v>1.550936394490257</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>1.663979350093705</v>
+        <v>1.473907664891307</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>2.212342273036761</v>
+        <v>2.321453805499814</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>1.894072069203411</v>
+        <v>2.077435748835342</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>3.380667993806675</v>
+        <v>3.618794514723078</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>4.3957448314925</v>
+        <v>4.556900019211128</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &gt; 75</t>
+          <t>X &gt; 74.83</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>698</v>
+        <v>687</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>1.230213058487806</v>
+        <v>1.055074421314693</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>1.181969211427386</v>
+        <v>1.240202068369442</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>1.749680821422182</v>
+        <v>1.565967736592803</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.1771279481112487</v>
+        <v>-0.3195379104912917</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>2.133601085879164</v>
+        <v>1.703754524122026</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>4.32629793100233</v>
+        <v>3.441147900235052</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>2.838016868888488</v>
+        <v>2.215031405243714</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>4.708802558805893</v>
+        <v>3.921605214708656</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>4.607023265075895</v>
+        <v>3.905855963473229</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>5.123505869841694</v>
+        <v>4.115551594690672</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>5.397565512003617</v>
+        <v>4.387786609295006</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>4.832283157266225</v>
+        <v>3.53649201114554</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>4.282186992988905</v>
+        <v>2.941115315839816</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>3.488042213963517</v>
+        <v>2.205248306010375</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>4.262563672829963</v>
+        <v>3.05425568583464</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>4.140618216549441</v>
+        <v>2.983516731570866</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>3.433635176993178</v>
+        <v>2.390481789676791</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>2.755728570593199</v>
+        <v>1.911952851360134</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>3.114886427162226</v>
+        <v>2.505456327112377</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>2.585399858906754</v>
+        <v>2.228092861616794</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>2.902452544808916</v>
+        <v>2.768430764352381</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>2.396807156465719</v>
+        <v>2.402147427258804</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>3.674147198460666</v>
+        <v>3.810265173090308</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>4.744446750394992</v>
+        <v>4.95816984692312</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &gt; 77.89</t>
+          <t>X &gt; 77.71</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>569</v>
+        <v>558</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>1.895181006075937</v>
+        <v>1.483828298344427</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>2.439138829870245</v>
+        <v>1.943388834774595</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>2.934335949556299</v>
+        <v>2.452363163218109</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>2.572875778971195</v>
+        <v>1.68359412137638</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>3.467313777425687</v>
+        <v>2.642603882511608</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>5.587496132240105</v>
+        <v>4.386839075811288</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>3.409572052919174</v>
+        <v>2.357189162343992</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>5.416070625740801</v>
+        <v>4.168670835337494</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>5.106063958797861</v>
+        <v>3.943866058954583</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>5.21188290490548</v>
+        <v>4.206015621936302</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>5.661689471496224</v>
+        <v>4.478250636540636</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>5.207193143619406</v>
+        <v>3.84893499600232</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>4.25977800119211</v>
+        <v>2.842480442819507</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>3.159964502601412</v>
+        <v>1.641120892784492</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>3.732049676022598</v>
+        <v>2.130120719146475</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>3.799195824679131</v>
+        <v>2.445780204501801</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>3.138037914415193</v>
+        <v>1.917445136417548</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>2.681703361736368</v>
+        <v>1.358593167565672</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>2.1946070449454</v>
+        <v>0.9669947886508368</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>1.502718232769318</v>
+        <v>0.9311340065184126</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>1.663159762518575</v>
+        <v>1.546036373906148</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>1.93880764996711</v>
+        <v>1.650085321484916</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>2.740523135735643</v>
+        <v>2.789777154433537</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>4.597907051229406</v>
+        <v>4.778175794552673</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &gt; 80.78</t>
+          <t>X &gt; 80.59</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>3.721790249205391</v>
+        <v>3.131333884580869</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>2.727672791514919</v>
+        <v>2.22897190664505</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>3.92701637984657</v>
+        <v>3.600098373681263</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>4.093183239524706</v>
+        <v>3.226514555617015</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>5.955194964779629</v>
+        <v>5.357958603701491</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>8.779523788239644</v>
+        <v>7.484257636395419</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>5.370212466986658</v>
+        <v>4.063355055234908</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>7.289803220035779</v>
+        <v>5.946618419266109</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>6.671949742609819</v>
+        <v>5.418092186718283</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>5.899034066573329</v>
+        <v>4.403222310754956</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>5.953313488955033</v>
+        <v>4.237820563871331</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>5.454783865726817</v>
+        <v>3.523601847912062</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>4.551402018650919</v>
+        <v>2.761890274820004</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>3.670982482863671</v>
+        <v>1.769488100797723</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>4.771080943524872</v>
+        <v>3.203323456047784</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>4.706127206127206</v>
+        <v>3.02020215565436</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>3.69308919002885</v>
+        <v>2.38984144542772</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>3.14868804664723</v>
+        <v>2.171601297646966</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>2.265678328670461</v>
+        <v>1.41143923309528</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>2.01296369907805</v>
+        <v>1.092494374021626</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>1.47041753111202</v>
+        <v>0.8819938751862253</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>1.1747913499227</v>
+        <v>1.030045638945232</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>2.328386941525629</v>
+        <v>1.943322981366471</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>4.230576666324325</v>
+        <v>4.013326844219854</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &gt; 83.67</t>
+          <t>X &gt; 83.47</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>367</v>
+        <v>356</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>3.034902205369129</v>
+        <v>2.895729436272966</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>3.245084535084708</v>
+        <v>3.197767806048546</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>4.804340690413383</v>
+        <v>4.134854526074776</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>3.818907106937942</v>
+        <v>2.720534519047376</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>6.480391838750343</v>
+        <v>5.184702406345302</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>10.48207192130549</v>
+        <v>8.629307245220097</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>7.802766289186259</v>
+        <v>6.19038961654902</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>9.704391356694771</v>
+        <v>7.803277392318478</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>8.383480718445981</v>
+        <v>6.561343288303952</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>7.338085478376797</v>
+        <v>5.217346587605171</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>7.61214512053872</v>
+        <v>5.489581602209505</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>5.69851833289453</v>
+        <v>3.29519142856013</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>4.302876702005719</v>
+        <v>1.797941942450613</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>4.626756953624522</v>
+        <v>2.267172234845489</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>5.603491040240151</v>
+        <v>3.411418473936642</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>6.197877962183142</v>
+        <v>3.870183504984468</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>4.974042569074882</v>
+        <v>2.829861111111107</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>4.3242427371883</v>
+        <v>2.312421140892255</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>4.267654554079925</v>
+        <v>2.140179146192736</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>2.819622979851765</v>
+        <v>1.125558824746236</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>2.004597247853042</v>
+        <v>0.726496282890885</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>1.928751286443941</v>
+        <v>0.9322326373400927</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>3.020664691024088</v>
+        <v>2.299462628236448</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>4.307230257964299</v>
+        <v>4.103615768778447</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &gt; 86.56</t>
+          <t>X &gt; 86.35</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>286</v>
+        <v>274</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>3.00250952992468</v>
+        <v>2.685131279006839</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>4.066334130176259</v>
+        <v>3.150968215544971</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>2.977965430795621</v>
+        <v>1.896274113653391</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>3.66361280995428</v>
+        <v>2.37148757320815</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>6.474675484260153</v>
+        <v>4.942904522076788</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>9.109194117909979</v>
+        <v>7.235069444800843</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>7.987595084369268</v>
+        <v>6.439987432568124</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>9.107985038217606</v>
+        <v>7.202682647522508</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>7.051570122230203</v>
+        <v>5.195380240480631</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>5.229703397242673</v>
+        <v>2.619969314656302</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>5.503763039404596</v>
+        <v>2.892204329260636</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>4.525712936655893</v>
+        <v>1.548006716426357</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>3.052900520149429</v>
+        <v>-0.2786291732664097</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>4.580073391954585</v>
+        <v>1.252496195905458</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>4.970881143325066</v>
+        <v>1.856564488143441</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>5.215617715617725</v>
+        <v>2.279619659036833</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>4.382399879339545</v>
+        <v>1.317071342925658</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>3.57825847621767</v>
+        <v>0.6803303954400803</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>3.794149857141996</v>
+        <v>1.11192232488272</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>2.932044618158969</v>
+        <v>0.4543085064371013</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>2.389498450192939</v>
+        <v>0.4681513308692402</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>2.313652488783838</v>
+        <v>0.7579523125635816</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>2.588127201265891</v>
+        <v>1.3665503014916</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>3.561245996993669</v>
+        <v>3.029228825450303</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &gt; 89.45</t>
+          <t>X &gt; 89.23</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>4.051460578875719</v>
+        <v>4.092841252184968</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>4.678222242064372</v>
+        <v>4.832156091357938</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>4.682510885341074</v>
+        <v>3.577461989466357</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>4.9310953274368</v>
+        <v>3.477670628096568</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>6.999151008735673</v>
+        <v>5.172555837750927</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>11.99380950252537</v>
+        <v>9.270376143256392</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>10.74109158786579</v>
+        <v>8.475294131023674</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>13.3474955277281</v>
+        <v>10.14081703736875</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>10.02359809425818</v>
+        <v>6.820470084983896</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>8.769913187452445</v>
+        <v>4.546586077449291</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>8.082434368075916</v>
+        <v>3.833599417176778</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>5.880608041550992</v>
+        <v>1.093963275513353</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>3.795907513156415</v>
+        <v>-1.006150516814259</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>4.536367098248284</v>
+        <v>-0.7617737408089482</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>5.320531492975427</v>
+        <v>1.3190821684829</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>5.434149184149192</v>
+        <v>1.188302053516054</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>4.819462816402492</v>
+        <v>1.385416666666664</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>4.71462211258131</v>
+        <v>1.556552662007576</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>5.411282724274862</v>
+        <v>2.583156404812449</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>4.155820841935189</v>
+        <v>1.587672604268199</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>4.574813135507632</v>
+        <v>2.035456529283394</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>3.537428712560057</v>
+        <v>1.960294007328109</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>4.292672655811337</v>
+        <v>3.21915691900243</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>3.255301941049602</v>
+        <v>2.549403711514998</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &gt; 92.34</t>
+          <t>X &gt; 92.11</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>7.840634368049514</v>
+        <v>6.762716783339783</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>3.061413125255257</v>
+        <v>1.936657275880194</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>3.104875557705739</v>
+        <v>-0.08139560463734341</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>3.873403019744487</v>
+        <v>0.0895609751803903</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>7.241316250900923</v>
+        <v>4.394155506836775</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>11.87272688144274</v>
+        <v>7.604524227338672</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>11.84151893829313</v>
+        <v>8.33615977235786</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>16.00775193798449</v>
+        <v>11.84803322207902</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>13.82701689767698</v>
+        <v>9.685885795885262</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>10.09113825867753</v>
+        <v>5.836399186162105</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>11.10593864158019</v>
+        <v>6.108634200766438</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>7.86422627516923</v>
+        <v>2.778617131791329</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>4.518841986090898</v>
+        <v>-0.6263513215373067</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>5.779244591125789</v>
+        <v>0.6521321742814905</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>3.639619812063749</v>
+        <v>-1.110468478889523</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>2.752525252525253</v>
+        <v>-1.646361836337007</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>2.618608115547779</v>
+        <v>-1.302083333333336</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>3.254508152467338</v>
+        <v>-0.1923493282587216</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>6.433362496354626</v>
+        <v>2.871756693412742</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>5.138726824841171</v>
+        <v>1.499041551170137</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>5.336921397615889</v>
+        <v>1.725247843440201</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>3.779593954725307</v>
+        <v>0.8564345278341179</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>4.794809407948094</v>
+        <v>1.893719806763293</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>3.237495673243338</v>
+        <v>2.52523160612462</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &gt; 95.23</t>
+          <t>X &gt; 94.99</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>4.330167379321658</v>
+        <v>6.457373271889402</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-1.801710868303523</v>
+        <v>-2.359962135243045</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>4.006646894259688</v>
+        <v>0.6710580485796669</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>1.844417512498111</v>
+        <v>-1.349915578799987</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>5.856453126907354</v>
+        <v>2.66024056681497</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>16.18834684923662</v>
+        <v>9.960031315670186</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>13.96712280302743</v>
+        <v>9.164949303437467</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>18.03673744523088</v>
+        <v>10.28860028860028</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>15.1796739025079</v>
+        <v>8.987957769712956</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>12.95748286415257</v>
+        <v>3.906191988779341</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>11.78226714399565</v>
+        <v>2.749855574812244</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>4.257140928953447</v>
+        <v>-3.241012093944768</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-1.213847224859187</v>
+        <v>-8.641618497109825</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>2.912899985650739</v>
+        <v>-3.175566844257219</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>-2.093069398886335</v>
+        <v>-8.143435511856566</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>-1.498682476943344</v>
+        <v>-8.286065240448906</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>-3.081874976239661</v>
+        <v>-9.114583333333336</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>1.161110406895688</v>
+        <v>-4.023586841480011</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>8.623378599414217</v>
+        <v>3.088206909862961</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>5.911673684744557</v>
+        <v>0.2724903246189143</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>8.267678241416213</v>
+        <v>5.765651883844242</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>0.9454554684129093</v>
+        <v>-1.885268213868621</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>1.219930180894963</v>
+        <v>1.388669301712788</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>-1.754452796966</v>
+        <v>-0.2886212077281911</v>
       </c>
     </row>
   </sheetData>
@@ -5824,247 +5824,247 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; 11.43</t>
+          <t>X &lt; 11.46</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-10.16258624386675</v>
+        <v>-10.68548387096774</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-9.048087679897726</v>
+        <v>-8.074247849528753</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-6.138280641972187</v>
+        <v>-6.471799094277479</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-3.952683936777255</v>
+        <v>-2.77848700737141</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-1.389923684686842</v>
+        <v>-1.625473718899322</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.2463178637293737</v>
+        <v>-0.03996868432980705</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-1.974906182479813</v>
+        <v>-0.8350506965625257</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.8038422649140529</v>
+        <v>0.2886002886002785</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.6869202793194944</v>
+        <v>1.845100626855825</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.08599539671699574</v>
+        <v>1.049049131636487</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.1880642454449273</v>
+        <v>1.321284146240821</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.09068515800306898</v>
+        <v>-0.3838692368019139</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>1.6847034997785</v>
+        <v>1.358381502890175</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>2.912899985650739</v>
+        <v>2.538718870028497</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-0.643794036567499</v>
+        <v>-1.000578368999413</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>4.298418972332009</v>
+        <v>3.846439935534526</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>5.613777197673386</v>
+        <v>5.171130952380956</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>8.407487218489891</v>
+        <v>7.895389704362202</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>10.07265396173305</v>
+        <v>9.538423360079406</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>13.15805049633876</v>
+        <v>12.61015266228125</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>12.61550432837273</v>
+        <v>12.04270816090052</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>12.53965836696363</v>
+        <v>11.96754563894523</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>9.915582354807995</v>
+        <v>9.354037267080749</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>14.18757618854124</v>
+        <v>13.47761255850556</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; 14.32</t>
+          <t>X &lt; 14.34</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.4875932535405099</v>
+        <v>0.5114273259434583</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>1.070247647851247</v>
+        <v>1.666011890730985</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-1.285202593840296</v>
+        <v>-0.9147872987335717</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-1.998156613283037</v>
+        <v>-1.507189497541795</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-4.168809471151413</v>
+        <v>-3.617610022962232</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.7198657111498505</v>
+        <v>0.2090483536780496</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-3.343666246892049</v>
+        <v>-2.420896043875764</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-3.621877691645125</v>
+        <v>-2.725816487284384</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-5.432242361582283</v>
+        <v>-5.350181155581922</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-2.501454333915063</v>
+        <v>-2.476507880159062</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-1.301468765827224</v>
+        <v>-1.286841672894184</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.2716336825766419</v>
+        <v>0.2714387579556217</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>2.852175319424227</v>
+        <v>2.826271411147054</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>1.705170517051712</v>
+        <v>1.660606157053401</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-2.656676484232555</v>
+        <v>-2.691272995473859</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>0.7154882154882145</v>
+        <v>0.622324601327449</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>1.507497004436672</v>
+        <v>1.435875382262999</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>4.180434078393262</v>
+        <v>4.055284855083045</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>6.248177311169449</v>
+        <v>6.104609467549921</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>10.13872682484117</v>
+        <v>9.988920683251109</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>9.596180656875141</v>
+        <v>9.421476181870375</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>9.52033469546604</v>
+        <v>9.34631365991509</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>9.794809407948094</v>
+        <v>9.589948145193468</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>12.49675493250259</v>
+        <v>12.18010272888565</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; 17.21</t>
+          <t>X &lt; 17.22</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.2666139845976048</v>
+        <v>-0.5305785353395081</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-1.828384647978105</v>
+        <v>-1.667321442602343</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-3.879900629524428</v>
+        <v>-3.823715470584098</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-1.525369986390487</v>
+        <v>-1.367337181587438</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-4.928645121514442</v>
+        <v>-4.691675809491656</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-3.806285464236275</v>
+        <v>-3.315230008371621</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-4.8734569071175</v>
+        <v>-4.720068118165315</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-3.28831431460349</v>
+        <v>-3.195720268891002</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-5.110181169955872</v>
+        <v>-5.506815749450801</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-4.019742808725276</v>
+        <v>-4.473598951987206</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-4.366801178985718</v>
+        <v>-4.811120034943855</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-4.024432570011349</v>
+        <v>-4.477945891854169</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.4424674749337711</v>
+        <v>-0.105033131256171</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.3997294139351766</v>
+        <v>-0.9630232902502556</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>-2.921226748782821</v>
+        <v>-3.47444596481823</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-1.084603801995108</v>
+        <v>-1.693629750876624</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>0.02371508587214066</v>
+        <v>-0.577997967479682</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>3.645582456585117</v>
+        <v>2.947654512724576</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>3.861473837509443</v>
+        <v>3.771872837431324</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>5.911673684744557</v>
+        <v>5.815727575173241</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>5.990245529200884</v>
+        <v>5.858039171353482</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>4.672163542947068</v>
+        <v>4.563364454276247</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>5.567756267851479</v>
+        <v>5.4167550371156</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>6.113042027050561</v>
+        <v>5.864372140387111</v>
       </c>
     </row>
     <row r="9">
@@ -6074,2211 +6074,2211 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.1727122086019293</v>
+        <v>0.3992819855823484</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-2.280708657544494</v>
+        <v>-1.705200230481132</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-2.447541265897513</v>
+        <v>-1.905152351898515</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-1.041851217543652</v>
+        <v>-0.593613057791579</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-3.270898091100662</v>
+        <v>-3.168571970858331</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-4.99336998465413</v>
+        <v>-4.277461149670373</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-5.545224027848981</v>
+        <v>-5.494484090173138</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-6.252620021958279</v>
+        <v>-6.221345461851797</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-6.211132840043575</v>
+        <v>-6.515357480437736</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-6.984048516080065</v>
+        <v>-7.311408975657073</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-7.568357972630579</v>
+        <v>-7.883055817592819</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-7.417922826722361</v>
+        <v>-7.737696843794069</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-4.249239400016243</v>
+        <v>-4.63317967854443</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-5.328687375175278</v>
+        <v>-5.725295596517626</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-8.132753419536961</v>
+        <v>-8.517154619752887</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-7.10918194823774</v>
+        <v>-7.533909672663178</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-5.526360887790318</v>
+        <v>-5.950026371308027</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-4.772832492899056</v>
+        <v>-5.239028619929542</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-3.698572013262293</v>
+        <v>-4.180684536243682</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-2.224172555225593</v>
+        <v>-2.700275306374564</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-1.47916507512295</v>
+        <v>-2.00189702294518</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-2.165489059323228</v>
+        <v>-2.920941401440544</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>-1.891014346841175</v>
+        <v>-2.25536598789212</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-0.242708669029966</v>
+        <v>-0.7297412691014173</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; 22.99</t>
+          <t>X &lt; 22.98</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>317</v>
+        <v>326</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-1.640847113431967</v>
+        <v>-1.578880504545644</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-2.123772059929934</v>
+        <v>-1.667321442602343</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-2.472466490224534</v>
+        <v>-2.155689671785076</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.2259758622430965</v>
+        <v>0.1570530623150006</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-1.633727016665723</v>
+        <v>-1.78274763764113</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-2.212921266705408</v>
+        <v>-2.073272803523494</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-2.501915405141219</v>
+        <v>-2.868354815756213</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-2.466647226069838</v>
+        <v>-2.866526792907166</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-3.365598915628482</v>
+        <v>-3.965591748253736</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-3.825034967840523</v>
+        <v>-4.454894777215401</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-4.177934573327505</v>
+        <v>-4.796156695126406</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-4.143204352951045</v>
+        <v>-4.765990183340037</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-3.385488676860454</v>
+        <v>-4.040391503244798</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-3.293087929482596</v>
+        <v>-3.981877098420227</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-3.637751603238712</v>
+        <v>-4.357283014047617</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-5.864681295715776</v>
+        <v>-6.556715191546978</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-5.058159561219902</v>
+        <v>-5.740350204498974</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-4.222561393567723</v>
+        <v>-4.952988910887576</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>-4.006670012643397</v>
+        <v>-4.738526683741803</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-3.192864955026465</v>
+        <v>-3.910443306167473</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-2.168013003870243</v>
+        <v>-2.944145476259877</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>-1.748009120047584</v>
+        <v>-2.712559531957481</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>-2.236385825139884</v>
+        <v>-3.08242197919445</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>0.2114412276305373</v>
+        <v>-0.7905732434225641</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; 25.88</t>
+          <t>X &lt; 25.86</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>402</v>
+        <v>413</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.8427935854514317</v>
+        <v>-0.6718133309814078</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-1.780501960562269</v>
+        <v>-1.27054795230368</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-2.601907019492479</v>
+        <v>-2.398996896475275</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.489342078294726</v>
+        <v>-0.2139431175263198</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-2.899733890149228</v>
+        <v>-3.012637279975927</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-3.07345082335565</v>
+        <v>-2.969750766654265</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-3.467123037015519</v>
+        <v>-3.764832778886984</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-3.36518535574487</v>
+        <v>-3.827622471690276</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-4.561321936206404</v>
+        <v>-5.152478065638121</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-4.59166335481715</v>
+        <v>-5.222137309041486</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-6.297801732457209</v>
+        <v>-6.886948299279759</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-6.329026383429962</v>
+        <v>-6.921399503145743</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-5.471990430484098</v>
+        <v>-6.099245615753887</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-4.702970297029694</v>
+        <v>-5.378956674765689</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-4.618539337184508</v>
+        <v>-5.334718804834772</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-6.251875187518749</v>
+        <v>-6.95259154146305</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-5.643218067070478</v>
+        <v>-6.330079701372078</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-5.74805877089166</v>
+        <v>-6.462963806533679</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-5.779692142442585</v>
+        <v>-6.490632329993225</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-4.35522257009832</v>
+        <v>-5.065392131907615</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-3.660144975688105</v>
+        <v>-4.422182880261715</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>-3.348427366844405</v>
+        <v>-4.255214651611674</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>-4.176998220575953</v>
+        <v>-4.980103168754603</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>-2.262780722555448</v>
+        <v>-2.963065407596119</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; 28.77</t>
+          <t>X &lt; 28.74</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>501</v>
+        <v>513</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-1.39035787664136</v>
+        <v>-1.032974218458094</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-2.799153323546491</v>
+        <v>-2.337856581222589</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-3.154310937237142</v>
+        <v>-2.911444719969609</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-1.40218753143661</v>
+        <v>-1.072523068397771</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-3.207949582980298</v>
+        <v>-2.992900066870412</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-2.520480555242955</v>
+        <v>-2.342948355730535</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-3.185983811981892</v>
+        <v>-3.332962141842387</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-2.563676633444068</v>
+        <v>-2.858155489734443</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-3.514252943592865</v>
+        <v>-3.704885449446046</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-4.088755921216652</v>
+        <v>-4.306005170786236</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-4.013108977467432</v>
+        <v>-4.22870193006105</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-4.887096476153516</v>
+        <v>-5.090079206169769</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-4.621369654120755</v>
+        <v>-4.840448906466555</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-4.44562313374194</v>
+        <v>-4.698819420141376</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-3.516464844020916</v>
+        <v>-3.821519610993292</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-5.303030303030305</v>
+        <v>-5.59939687872334</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>-4.64329664635698</v>
+        <v>-4.923550194931778</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-5.144962747003568</v>
+        <v>-5.446297847851667</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-5.127484064491938</v>
+        <v>-5.426767394585028</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-3.94857476246041</v>
+        <v>-4.23752208013034</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-3.300644739950258</v>
+        <v>-3.635375938236216</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-2.66764851637403</v>
+        <v>-3.125743138554071</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-2.87672666996248</v>
+        <v>-3.271972201033975</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-2.639638946406251</v>
+        <v>-3.044247647565157</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; 31.66</t>
+          <t>X &lt; 31.62</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>620</v>
+        <v>634</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-1.184428729913748</v>
+        <v>-1.116961626389156</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-1.594671530829395</v>
+        <v>-1.437436385131086</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-2.313483978300845</v>
+        <v>-2.295974918453297</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-1.827233922930667</v>
+        <v>-1.704812254451376</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-3.671318872260521</v>
+        <v>-3.785203752645103</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-2.761044269900296</v>
+        <v>-2.75740897274801</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-3.28736995059576</v>
+        <v>-3.710219691605332</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-2.678145497912944</v>
+        <v>-3.226496601890929</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-3.1909963001115</v>
+        <v>-3.72948251870524</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-3.642884688828573</v>
+        <v>-4.052347894050762</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-3.529338690326355</v>
+        <v>-3.937841586071038</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-3.808088093774352</v>
+        <v>-4.214423540542334</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-3.326113724033362</v>
+        <v>-3.909757298371652</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-3.547192600479953</v>
+        <v>-4.000262653180158</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-2.921226748782821</v>
+        <v>-3.420587382068376</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-3.61094897611752</v>
+        <v>-3.963384309620942</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-3.423838825775562</v>
+        <v>-3.751807308096744</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-4.812788678874433</v>
+        <v>-5.14652106625519</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-4.436383654290395</v>
+        <v>-4.774330132484813</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-3.286455982364103</v>
+        <v>-3.61337144767819</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>-3.347461219351004</v>
+        <v>-3.707629829185109</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>-2.367839652515379</v>
+        <v>-2.678691404768152</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>-2.322742926995545</v>
+        <v>-2.75051433273898</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>-2.144822128429304</v>
+        <v>-2.439467207154635</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; 34.55</t>
+          <t>X &lt; 34.5</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>738</v>
+        <v>760</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.7703531214426462</v>
+        <v>-0.7321692117707244</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-1.168137280765741</v>
+        <v>-1.03984246433803</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-3.338676428014914</v>
+        <v>-3.273896079860705</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-1.971101001703232</v>
+        <v>-2.092322777900094</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-3.442253224614866</v>
+        <v>-3.611582222747643</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-1.839937395737671</v>
+        <v>-2.201622819668145</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-1.731084620851483</v>
+        <v>-2.075652200321926</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-1.530433147370402</v>
+        <v>-1.985835801625285</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-1.413648869304573</v>
+        <v>-1.989485839309587</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-1.376847946150782</v>
+        <v>-1.86448470294998</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-1.372693837052289</v>
+        <v>-1.855407583082496</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-2.056301540095433</v>
+        <v>-2.526726379659046</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-1.155172108975833</v>
+        <v>-1.536355339215085</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-1.646156518485853</v>
+        <v>-1.916168348016612</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>-0.8198193842175527</v>
+        <v>-1.01937536148062</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>-1.170101827996568</v>
+        <v>-1.247545026871492</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>-1.708877264569175</v>
+        <v>-1.746162280701753</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-3.028292867175786</v>
+        <v>-2.931677964810731</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>-2.677448719719742</v>
+        <v>-2.585636790296526</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>-1.95079184362487</v>
+        <v>-1.844734555763857</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>-1.953526945464034</v>
+        <v>-1.885863267670921</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>-1.005190830059483</v>
+        <v>-0.9083942106788285</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>-0.9216242110565673</v>
+        <v>-1.059496567505711</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>-0.7823778588253134</v>
+        <v>-0.6953197723214899</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; 37.44</t>
+          <t>X &lt; 37.38</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>859</v>
+        <v>881</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-1.456939067454954</v>
+        <v>-1.285290384995477</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-1.271366144232871</v>
+        <v>-1.133166332176053</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-2.303043882471762</v>
+        <v>-2.215173367063514</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-1.801337464684579</v>
+        <v>-1.841745379803065</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-2.536290455112258</v>
+        <v>-2.623206145203177</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.784091786936628</v>
+        <v>-1.043698212463418</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-1.26033291355872</v>
+        <v>-1.498258090757432</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-1.010401789323346</v>
+        <v>-1.349149022247779</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.555555930371483</v>
+        <v>-0.9942053566045388</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.5164066412107644</v>
+        <v>-0.9957052059668854</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-0.4743655605337551</v>
+        <v>-0.9504849473216979</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.9851335254666793</v>
+        <v>-1.454081657752127</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.02012853895851663</v>
+        <v>-0.412333593591093</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.3572166961475673</v>
+        <v>-0.6605676550242023</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>0.02872353295400387</v>
+        <v>-0.2076482571135756</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>-0.5369823525276018</v>
+        <v>-0.6679106401100228</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>-0.4388809280201471</v>
+        <v>-0.5447762958759057</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-0.6597309125837896</v>
+        <v>-0.6776604010375067</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>-0.2118209701745499</v>
+        <v>-0.2361834179325868</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>0.09103412053593729</v>
+        <v>0.09191040510595627</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>-0.1034842052027116</v>
+        <v>-0.1350119623360655</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>0.5869239327869877</v>
+        <v>0.5843771615656337</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>0.5829231030385387</v>
+        <v>0.4874895129053058</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>0.3443813715143662</v>
+        <v>0.3253505186158421</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; 40.33</t>
+          <t>X &lt; 40.26</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>987</v>
+        <v>1010</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-1.588795061379912</v>
+        <v>-1.330237347579619</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.5688102845272667</v>
+        <v>-0.4420768709010758</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-2.555067233631227</v>
+        <v>-2.432390227282404</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-1.608524691098886</v>
+        <v>-1.592237359583308</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-2.291533181446006</v>
+        <v>-2.30802907075379</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.6416184498039925</v>
+        <v>-0.6159144776669052</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.8540164762755182</v>
+        <v>-0.9608101991766347</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.8739684921230193</v>
+        <v>-0.9136627948509144</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.5737006715572406</v>
+        <v>-0.6867239841767088</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-0.2366264384110863</v>
+        <v>-0.393666568504969</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-0.3661994904974009</v>
+        <v>-0.5174711578610314</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.4431325468212819</v>
+        <v>-0.5960333103521265</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.350960684001727</v>
+        <v>0.2692725919990835</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.0289736339930684</v>
+        <v>-0.07797137042412317</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>0.6826365927192697</v>
+        <v>0.6260128615522049</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>0.2679417790416849</v>
+        <v>0.2962277714609769</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>0.3358409891883269</v>
+        <v>0.3903671617161635</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>0.02918393824302967</v>
+        <v>0.1584731555644652</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>0.2450753191673556</v>
+        <v>0.4719452837003359</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>0.3310129555733141</v>
+        <v>0.5875218277692227</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>0.05072611142059458</v>
+        <v>0.2180971283686901</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>0.6421187646717499</v>
+        <v>0.8360039133440935</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>0.5730370282809787</v>
+        <v>0.6835987946620747</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>0.4569035309490701</v>
+        <v>0.6204697013627154</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; 43.22</t>
+          <t>X &lt; 43.14</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1125</v>
+        <v>1155</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-1.974180446765295</v>
+        <v>-1.907514852034865</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.771058503528927</v>
+        <v>-0.7308246921521118</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-2.162324858879551</v>
+        <v>-2.198400079499152</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-1.245330489490343</v>
+        <v>-1.278425377887871</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-2.060979002098563</v>
+        <v>-2.11153342775696</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.7688133371899895</v>
+        <v>-0.9573658938618479</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-1.668181238073714</v>
+        <v>-1.878056134031624</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-1.103163037008144</v>
+        <v>-1.183261183261187</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-1.012009407780418</v>
+        <v>-1.228492446737249</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-1.204666830231012</v>
+        <v>-1.418483335895992</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-1.057286530494544</v>
+        <v>-1.319408494451828</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-1.070549208278813</v>
+        <v>-1.249670102602771</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.01867810539604164</v>
+        <v>-0.1134799689712978</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.3793919214930312</v>
+        <v>-0.3617140304044071</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>0.02441168358127754</v>
+        <v>0.08167271325167036</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>-0.08916599624564014</v>
+        <v>0.03691612601072336</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>-0.04609198278063786</v>
+        <v>0.1061958874458853</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-0.2394282618230577</v>
+        <v>-0.02668821771571572</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>0.5074365704287018</v>
+        <v>0.7072545289105747</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>0.1274090411584652</v>
+        <v>0.3157803679089568</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>-0.007838255654405657</v>
+        <v>0.0946562128485624</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>0.3243374559905448</v>
+        <v>0.4523941237937166</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>0.1194591020471734</v>
+        <v>0.1765480895915772</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>0.2745327102803756</v>
+        <v>0.3607294416224534</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; 46.11</t>
+          <t>X &lt; 46.02</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1239</v>
+        <v>1269</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-1.48773706558508</v>
+        <v>-1.505009173251658</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.5837643746708494</v>
+        <v>-0.5336316030301518</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-2.059010372953345</v>
+        <v>-2.060496111545923</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.4911053735408899</v>
+        <v>-0.5688584583870124</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-1.582387452802791</v>
+        <v>-1.665904985745676</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.07045729552846325</v>
+        <v>-0.2074408659640739</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-1.278139181364985</v>
+        <v>-1.509966332108085</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-1.271050521251006</v>
+        <v>-1.377503505163084</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-1.184575754365113</v>
+        <v>-1.407179008402537</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-1.751789005936487</v>
+        <v>-1.888021677774752</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-1.512853784286186</v>
+        <v>-1.694588869632199</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-1.148516371013933</v>
+        <v>-1.261950965947463</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>0.05951127274088464</v>
+        <v>-0.01277688954481704</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-0.4831110120658266</v>
+        <v>-0.4974175703632682</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>0.06453347170408819</v>
+        <v>0.0812633511401728</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-0.1449381272532406</v>
+        <v>-0.1454546946579782</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-0.3592411163207458</v>
+        <v>-0.2493351063829863</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-0.3033101159618639</v>
+        <v>-0.06701038569746487</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>0.1537388212325652</v>
+        <v>0.3838584608336575</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>0.0667683015552214</v>
+        <v>0.283236080045512</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-0.2669433366836316</v>
+        <v>-0.1266040084116611</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>0.1887024992085387</v>
+        <v>0.3498489148655253</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>0.1084294796326759</v>
+        <v>0.1994723678349999</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-0.1613026408092111</v>
+        <v>-0.04146883291624448</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; 49</t>
+          <t>X &lt; 48.9</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1382</v>
+        <v>1414</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-1.171269447003908</v>
+        <v>-1.292275110670367</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.1790623071972561</v>
+        <v>-0.2346982365801225</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-1.148409985902383</v>
+        <v>-1.169988229086336</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.3296440527430562</v>
+        <v>0.1783236238578212</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.8270679983878537</v>
+        <v>-0.974657680213042</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.02542126670540767</v>
+        <v>-0.1438097973452273</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.9007128693592392</v>
+        <v>-0.9702403656505041</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.9946461435502698</v>
+        <v>-0.9531967835854758</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-1.200580894499645</v>
+        <v>-1.139340674417163</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-2.149228909643526</v>
+        <v>-2.14755624318672</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-2.483743325895574</v>
+        <v>-2.441092091382949</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-1.753119982407739</v>
+        <v>-1.656853678103182</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.6412423953345154</v>
+        <v>-0.5793837022017598</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-1.078615431838777</v>
+        <v>-0.9690604793350204</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-0.7273859824835043</v>
+        <v>-0.590394493469006</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-0.8539795940661108</v>
+        <v>-0.6655826952999817</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-0.987896731043584</v>
+        <v>-0.6987417491749213</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-0.8043452214545255</v>
+        <v>-0.5487404229362411</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-0.5163557871776447</v>
+        <v>-0.2635568379403921</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-0.5034088172944706</v>
+        <v>-0.1904131085815521</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-0.9312962785440249</v>
+        <v>-0.7578576099622865</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-0.7478091709437251</v>
+        <v>-0.5501347005172903</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-0.7920789988969261</v>
+        <v>-0.6601070044892623</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-0.8253225719193367</v>
+        <v>-0.6100819252285135</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; 51.89</t>
+          <t>X &lt; 51.78</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1527</v>
+        <v>1565</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-1.019487890130996</v>
+        <v>-1.031501489712625</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.1046869690472363</v>
+        <v>0.2827132555239587</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.9742392019015611</v>
+        <v>-0.8739087605501012</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.09908395359662592</v>
+        <v>0.1605484794347731</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.8491492957619116</v>
+        <v>-0.7167966725549704</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.4312654225495649</v>
+        <v>-0.2695605210645056</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-1.361859879120772</v>
+        <v>-1.22068293286484</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-1.473825868690838</v>
+        <v>-1.234844338292618</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-1.656247759302708</v>
+        <v>-1.454762449365084</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-2.197634889470621</v>
+        <v>-1.995222890271329</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-2.864383472064397</v>
+        <v>-2.681454329341108</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-2.556813657271348</v>
+        <v>-2.31905864802966</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-1.790724909795223</v>
+        <v>-1.517017858132185</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-2.076950366046368</v>
+        <v>-1.765251919565294</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-1.953334705972203</v>
+        <v>-1.616735374932787</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-1.907767373869071</v>
+        <v>-1.566613464739319</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-1.520172124927377</v>
+        <v>-1.159311767838133</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-1.652355658506067</v>
+        <v>-1.228298109421452</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-1.137472045759289</v>
+        <v>-0.7582448279625851</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-1.173777711046775</v>
+        <v>-0.8631472007949768</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-1.482250715673871</v>
+        <v>-1.17500064786261</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-1.454521782987563</v>
+        <v>-1.122367642661338</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-1.534451790423049</v>
+        <v>-1.262119738852618</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-1.441249869942283</v>
+        <v>-1.168667678828982</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; 54.77</t>
+          <t>X &lt; 54.67</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1690</v>
+        <v>1723</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.245062570106434</v>
+        <v>-0.309370377071339</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.623087277439069</v>
+        <v>0.5731071063184032</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.6656945434622514</v>
+        <v>-0.5923606136829278</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.002435277808999103</v>
+        <v>0.1191416797309586</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.7698991898919871</v>
+        <v>-0.7028546712802708</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.785110051203354</v>
+        <v>-0.6876649371216033</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-1.113174885965911</v>
+        <v>-1.045280790917772</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-1.299714258370585</v>
+        <v>-1.144111926720626</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-1.519388331081188</v>
+        <v>-1.389901030419615</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-1.494325957746078</v>
+        <v>-1.399338232595348</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-2.188132815035438</v>
+        <v>-2.055716102494777</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-2.113525328024068</v>
+        <v>-1.926029919995671</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-1.528795757659928</v>
+        <v>-1.241734573720386</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-1.749874634106519</v>
+        <v>-1.489968635153495</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-1.642411335691783</v>
+        <v>-1.417625048379236</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-1.661800682130675</v>
+        <v>-1.436704082374433</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-1.324297665896601</v>
+        <v>-1.076278051847552</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-1.335813301061663</v>
+        <v>-1.035047241164698</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-0.9674896832586128</v>
+        <v>-0.7045084034559608</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-1.218350441326997</v>
+        <v>-0.8961900953673734</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-1.313119074043016</v>
+        <v>-1.115404765059189</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-1.17706483172072</v>
+        <v>-0.9003757606070408</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-1.459215166596884</v>
+        <v>-1.179086022862037</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-1.441443621080573</v>
+        <v>-1.167110101307046</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 57.66</t>
+          <t>X &lt; 57.55</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1847</v>
+        <v>1884</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.5643356099541705</v>
+        <v>-0.5051201248353792</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.1999649533145771</v>
+        <v>0.2812338780459953</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.9412273207484958</v>
+        <v>-0.8919849369910864</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.6067684700732983</v>
+        <v>-0.5033547322391385</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-1.448982627065519</v>
+        <v>-1.279107538758659</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.9106143997526175</v>
+        <v>-0.7754408392934877</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-1.545491260311266</v>
+        <v>-1.488393114610822</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-1.686483650987938</v>
+        <v>-1.445985380237772</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-1.991240908759224</v>
+        <v>-1.766115742981242</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-1.659160427105029</v>
+        <v>-1.418345469516076</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-1.677517218798741</v>
+        <v>-1.517660348754639</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-2.171436068185415</v>
+        <v>-2.006556528279013</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-1.757520490486876</v>
+        <v>-1.635249070358235</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-1.678423092713146</v>
+        <v>-1.565011794211728</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-1.605032167502024</v>
+        <v>-1.450987832147732</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-1.572122845707753</v>
+        <v>-1.473547932224044</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-1.243312057052009</v>
+        <v>-1.046642781316351</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-1.370624265433563</v>
+        <v>-1.073369773951413</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-1.23122433669873</v>
+        <v>-1.018143215595444</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-1.60717629059193</v>
+        <v>-1.387420889432434</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-1.577993517299028</v>
+        <v>-1.424079828180467</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-1.351908559146061</v>
+        <v>-1.180771012556136</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-1.424526811388127</v>
+        <v>-1.361764977383913</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-1.522976764543657</v>
+        <v>-1.470825415410104</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 60.55</t>
+          <t>X &lt; 60.43</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2001</v>
+        <v>2038</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.6502391055229211</v>
+        <v>-0.5382300500451436</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.2664250987253993</v>
+        <v>-0.07396855892688592</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.9356617633857596</v>
+        <v>-0.7155993038478528</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.5820425248099639</v>
+        <v>-0.3518725259624063</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-1.385616774249044</v>
+        <v>-1.138794465700244</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-1.022695795942276</v>
+        <v>-0.8081231547369754</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-1.420200887630962</v>
+        <v>-1.331306033582194</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-1.819629014396448</v>
+        <v>-1.60915881504117</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-1.700967662565638</v>
+        <v>-1.503179342316741</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-1.75115090238026</v>
+        <v>-1.536118399556557</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-1.647828538416498</v>
+        <v>-1.460154238730453</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-2.373671831581341</v>
+        <v>-2.129277900758176</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-1.828996906479603</v>
+        <v>-1.526800047649566</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-1.822648699479586</v>
+        <v>-1.529695541859915</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>-1.755626180197176</v>
+        <v>-1.475834222076664</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>-1.629975715341565</v>
+        <v>-1.356139624257978</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>-1.187279445319859</v>
+        <v>-0.8221397612038004</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-1.512141905662546</v>
+        <v>-1.10222700669906</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-1.516491644925232</v>
+        <v>-1.133103346776053</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-1.84935851735888</v>
+        <v>-1.458261749607161</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-1.914132051042351</v>
+        <v>-1.633164543431462</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-1.661503658114704</v>
+        <v>-1.364853071274872</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>-1.907377294238607</v>
+        <v>-1.710031147331136</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>-1.954352846941006</v>
+        <v>-1.774034714731499</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 63.44</t>
+          <t>X &lt; 63.31</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2140</v>
+        <v>2178</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.4739492863399732</v>
+        <v>-0.5718771851489919</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>0.04842789210350418</v>
+        <v>-0.01624275448661905</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.5779187590543344</v>
+        <v>-0.6058992119091613</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.2006710543295895</v>
+        <v>-0.07498913224883097</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.7884643402506839</v>
+        <v>-0.6456202390458401</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.9000737226831603</v>
+        <v>-0.6924128960960516</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.9973004095665488</v>
+        <v>-0.9581356775760099</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-1.295896794235659</v>
+        <v>-1.145866207764428</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-1.042794909489814</v>
+        <v>-0.9006398711782566</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-0.9075205672793487</v>
+        <v>-0.753219274578683</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.9784913527429708</v>
+        <v>-0.8222289063631436</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-1.416718238117291</v>
+        <v>-1.236551907666403</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-1.258315924958232</v>
+        <v>-1.065860921352247</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-1.080359198710568</v>
+        <v>-0.9008718422894901</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>-0.7806962694901216</v>
+        <v>-0.6188388963508586</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>-0.903588962248179</v>
+        <v>-0.7462401116909803</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-0.7773448938192971</v>
+        <v>-0.5746384297520706</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-0.9479701879420332</v>
+        <v>-0.7075225349136716</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-0.9377848747927473</v>
+        <v>-0.7226287191544927</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>-1.143404186767448</v>
+        <v>-0.9212654145913746</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>-1.332164860831085</v>
+        <v>-1.121400457753566</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>-1.334007041228631</v>
+        <v>-1.104735615154205</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>-1.545945171947068</v>
+        <v>-1.366151634926339</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>-1.594626168224302</v>
+        <v>-1.436463264661157</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 66.33</t>
+          <t>X &lt; 66.19</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2301</v>
+        <v>2333</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.4566818810739619</v>
+        <v>-0.490983535622334</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.2089428958541077</v>
+        <v>-0.1591569626189155</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.7194138479790126</v>
+        <v>-0.6220401390080568</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.2885961185579689</v>
+        <v>-0.08007430895871437</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.9020426252165805</v>
+        <v>-0.7594137421082578</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.6911176875764724</v>
+        <v>-0.5361192403605983</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.5331335398968733</v>
+        <v>-0.4517754352384813</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.916431632724759</v>
+        <v>-0.6898732926130222</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.8505881685291143</v>
+        <v>-0.5807176662001581</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-0.778392178887465</v>
+        <v>-0.4529706994321927</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.9549467900917605</v>
+        <v>-0.5849065340604511</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.9929577571120802</v>
+        <v>-0.6900354238082187</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.9668686380280391</v>
+        <v>-0.6476193543751521</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-0.730042714353651</v>
+        <v>-0.3814942216376593</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>-0.7567245842806543</v>
+        <v>-0.4206996108094714</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>-0.7862842369122092</v>
+        <v>-0.5452078508839335</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-0.504827278251561</v>
+        <v>-0.2633188669809954</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-0.6273971598671011</v>
+        <v>-0.3533397059617158</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>-0.689441139892196</v>
+        <v>-0.3531938097203593</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-0.7373879015989289</v>
+        <v>-0.4386502279275604</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>-0.9940971209026372</v>
+        <v>-0.7917783984038778</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>-1.000966023403066</v>
+        <v>-0.8669409203591627</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>-1.265621135540663</v>
+        <v>-1.223392161613148</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>-1.098783239306755</v>
+        <v>-1.042625026455546</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 69.22</t>
+          <t>X &lt; 69.07</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2453</v>
+        <v>2492</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.6521556756290607</v>
+        <v>-0.6249608608044426</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.3998663360242034</v>
+        <v>-0.2099649912434955</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.4419372211199715</v>
+        <v>-0.2432276657060441</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.2026180073481214</v>
+        <v>0.06665104785066944</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.3539732133205931</v>
+        <v>-0.1465763152621236</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.4680558276119271</v>
+        <v>-0.2876945267693145</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.1647788574783533</v>
+        <v>-0.01888769289951853</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-0.7034671790669407</v>
+        <v>-0.5015514434352113</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.8416306802088442</v>
+        <v>-0.6317008395206187</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-0.7809661116027655</v>
+        <v>-0.5628928774174398</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-0.9702981791821728</v>
+        <v>-0.7493418569694583</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-0.9825921456857003</v>
+        <v>-0.704896524121331</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-0.9056409383920396</v>
+        <v>-0.5758079032093448</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-0.7376498916639491</v>
+        <v>-0.3826294445782423</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>-0.8439376690566931</v>
+        <v>-0.5029860736543057</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>-0.9162634061049317</v>
+        <v>-0.5436082185585676</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>-0.7011750822842018</v>
+        <v>-0.2863329320492269</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-0.6193942167583302</v>
+        <v>-0.1784465717212527</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>-0.664247725747046</v>
+        <v>-0.2850116318949105</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>-0.4941588080444674</v>
+        <v>-0.1506820086657825</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>-0.80917583968656</v>
+        <v>-0.5174844554718732</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>-0.7387737000985695</v>
+        <v>-0.5123901555973092</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>-1.132927620033428</v>
+        <v>-0.9910670667876289</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-1.26643753024144</v>
+        <v>-1.113077650162161</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; 72.11</t>
+          <t>X &lt; 71.95</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2589</v>
+        <v>2621</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.4249206203232347</v>
+        <v>-0.5411069712716881</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.3946204648265947</v>
+        <v>-0.3107684554906385</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.5094284014257937</v>
+        <v>-0.3664215820558638</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.128130134720827</v>
+        <v>0.1270175299322887</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.3274181276494161</v>
+        <v>-0.1273219467749485</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.7710100660916765</v>
+        <v>-0.482080816582787</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.5623354149088868</v>
+        <v>-0.3040965022419897</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-1.087577556577244</v>
+        <v>-0.7780663780663843</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.9476886834802158</v>
+        <v>-0.6287669689629922</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-1.04586889830658</v>
+        <v>-0.7934431073483239</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-1.21108245330408</v>
+        <v>-0.9953770720222295</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-1.160507801467958</v>
+        <v>-0.9287095985759137</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-1.069477102228198</v>
+        <v>-0.7850204803287468</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-0.806479262778133</v>
+        <v>-0.4611721618991496</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>-1.057155485173453</v>
+        <v>-0.6856606398940457</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>-0.979130931961123</v>
+        <v>-0.5820225249645432</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>-0.8593922268593488</v>
+        <v>-0.4570699847444715</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-0.7103815927692239</v>
+        <v>-0.3229823126368103</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>-0.7801501681989009</v>
+        <v>-0.375491862760299</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>-0.6863578047170407</v>
+        <v>-0.3515995443222195</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>-0.8590662567050984</v>
+        <v>-0.5757946177853341</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>-0.7577647084535073</v>
+        <v>-0.5746794890922544</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>-1.232646619507932</v>
+        <v>-1.055682684973299</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>-1.556290001191243</v>
+        <v>-1.4245512829944</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &lt; 75</t>
+          <t>X &lt; 74.83</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2716</v>
+        <v>2752</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.3732311952136413</v>
+        <v>-0.2888306326659134</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.3963689811754989</v>
+        <v>-0.2623129489862563</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.5725760992855484</v>
+        <v>-0.3760786063717489</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.2055443486765611</v>
+        <v>0.1008884127206215</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.7037037233695216</v>
+        <v>-0.444135144367408</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-1.264448333274537</v>
+        <v>-0.955268523932439</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.8819839279100634</v>
+        <v>-0.7160030775149053</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-1.359256358745611</v>
+        <v>-1.145666785391334</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-1.333892822002419</v>
+        <v>-1.106313441309517</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-1.463603296064029</v>
+        <v>-1.193035950492124</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-1.535240463505104</v>
+        <v>-1.263206834476584</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-1.390145398557273</v>
+        <v>-1.047597523034739</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-1.245734471554869</v>
+        <v>-0.8557745769646417</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-1.042037439253825</v>
+        <v>-0.6321393099040904</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>-1.238395818245458</v>
+        <v>-0.8061267226421407</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>-1.209785075423838</v>
+        <v>-0.752989672969484</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-1.028513115121015</v>
+        <v>-0.5664889594676339</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-0.85467082812972</v>
+        <v>-0.4089919394023767</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>-0.9479107283585151</v>
+        <v>-0.5212084781368205</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-0.8130705607797353</v>
+        <v>-0.4518125956912655</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>-0.8927654425895284</v>
+        <v>-0.5473877685783535</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>-0.7629618461086451</v>
+        <v>-0.5285639159878528</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>-1.09240279505358</v>
+        <v>-0.8810309701669254</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>-1.367588055551728</v>
+        <v>-1.239995414916351</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &lt; 77.89</t>
+          <t>X &lt; 77.71</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2845</v>
+        <v>2881</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.4330367926509311</v>
+        <v>-0.312920337782451</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.5748565591483654</v>
+        <v>-0.3331085465373462</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.7032451938902398</v>
+        <v>-0.4632069259894891</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.664118795264244</v>
+        <v>-0.3105952863676578</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.840879072914511</v>
+        <v>-0.5324263304524166</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-1.263196327830101</v>
+        <v>-0.9445658173006493</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.8279429764518014</v>
+        <v>-0.6130262689306178</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-1.226315404436562</v>
+        <v>-0.9678302614590706</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-1.165213094553017</v>
+        <v>-0.8898194582547703</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-1.183977360614371</v>
+        <v>-0.9735228909355413</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-1.274902661584413</v>
+        <v>-1.028307336799543</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-1.183855758562082</v>
+        <v>-0.9039801938060705</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.9915844066884389</v>
+        <v>-0.6665838230460253</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.7719651124481928</v>
+        <v>-0.3947069274749779</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>-0.8839857837212506</v>
+        <v>-0.45272816095504</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>-0.8997705764267252</v>
+        <v>-0.4808832267400902</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>-0.7677094783434484</v>
+        <v>-0.3420451918631571</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-0.6765361854517806</v>
+        <v>-0.1975367866225426</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>-0.5802827278169147</v>
+        <v>-0.08709675087759905</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>-0.4429587568444049</v>
+        <v>-0.08055468862028192</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>-0.4732637875693015</v>
+        <v>-0.1625622967971339</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>-0.5282544627121624</v>
+        <v>-0.2518686616345249</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>-0.6896912557514412</v>
+        <v>-0.473463476450533</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>-1.061143915378672</v>
+        <v>-0.9276038841978576</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &lt; 80.78</t>
+          <t>X &lt; 80.59</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2959</v>
+        <v>2991</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.6227384615204983</v>
+        <v>-0.497701603318589</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.503634646434584</v>
+        <v>-0.2931940165441631</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.7156563836315613</v>
+        <v>-0.5310731535515387</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.772451293783547</v>
+        <v>-0.4724053475255943</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-1.056074491083514</v>
+        <v>-0.8295485510981138</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-1.488723248566338</v>
+        <v>-1.220921065282191</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.9653807032839339</v>
+        <v>-0.7640746569302692</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-1.258354504592532</v>
+        <v>-1.050387608092755</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-1.164390111214892</v>
+        <v>-0.9372054887836327</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-1.043891826907547</v>
+        <v>-0.813434179444954</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-1.053475146366573</v>
+        <v>-0.7893764786101301</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-0.9765431377980889</v>
+        <v>-0.6796989915495004</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.8346933674444585</v>
+        <v>-0.5253860321799593</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.6993053633419919</v>
+        <v>-0.3394183568061209</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>-0.8659706840927939</v>
+        <v>-0.5205707346831687</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>-0.8583049912675733</v>
+        <v>-0.4602687198715145</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>-0.7027375051909672</v>
+        <v>-0.3303481963927908</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-0.6190787565327156</v>
+        <v>-0.26283149995119</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>-0.4844662635793995</v>
+        <v>-0.1151695400064767</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>-0.4464533604065082</v>
+        <v>-0.06758376295016433</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>-0.3614305667725404</v>
+        <v>-0.000425725920749187</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-0.3158692896741186</v>
+        <v>-0.08915809834654453</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>-0.4942296310909455</v>
+        <v>-0.2267495931178658</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>-0.7866366036770387</v>
+        <v>-0.6032013116764077</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &lt; 83.67</t>
+          <t>X &lt; 83.47</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3047</v>
+        <v>3083</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.416091413106237</v>
+        <v>-0.3621294727021436</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.4728542799798845</v>
+        <v>-0.3324612123932766</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.6874369634203319</v>
+        <v>-0.4713375203102501</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.6000237816901404</v>
+        <v>-0.302727472788348</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.9177038259273758</v>
+        <v>-0.625058033711575</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-1.397770369478657</v>
+        <v>-1.097074579728073</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-1.074785094198894</v>
+        <v>-0.8715622277359785</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-1.302075029041291</v>
+        <v>-1.061376595357181</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-1.144316290507938</v>
+        <v>-0.8830129559032827</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-1.016826942721188</v>
+        <v>-0.7542447247661812</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-1.05092410351785</v>
+        <v>-0.7875593911741561</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.820771242780225</v>
+        <v>-0.5273744677990422</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.6498715279463667</v>
+        <v>-0.3136858982763826</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.6882435054103979</v>
+        <v>-0.3350891107140299</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>-0.8036126874514764</v>
+        <v>-0.4339641666107568</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>-0.8772256112681589</v>
+        <v>-0.4559394737794236</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>-0.7300057242251938</v>
+        <v>-0.3005846295096148</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>-0.6517892356512078</v>
+        <v>-0.2066378856757538</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>-0.6459055003445684</v>
+        <v>-0.1541976935267328</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>-0.472548166964792</v>
+        <v>-0.03682446946581308</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>-0.3728539515037284</v>
+        <v>0.043819169140491</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>-0.3635981058167062</v>
+        <v>-0.0444941850881051</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>-0.4960917294097413</v>
+        <v>-0.2031241188744062</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>-0.6509677820071147</v>
+        <v>-0.4758650375279814</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &lt; 86.56</t>
+          <t>X &lt; 86.35</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3128</v>
+        <v>3165</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.3244396237461515</v>
+        <v>-0.2574962659917617</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.4518143879722487</v>
+        <v>-0.2350744443176112</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.380299042108426</v>
+        <v>-0.1517523590058261</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.4722132445502965</v>
+        <v>-0.1919545970504615</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.7267662262378067</v>
+        <v>-0.4500611553847733</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.9670932311046485</v>
+        <v>-0.7164710233006559</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.8629502367642772</v>
+        <v>-0.7068167258088707</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.9642582401325512</v>
+        <v>-0.773601529745207</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.7775717826355333</v>
+        <v>-0.5649664570215407</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.6095242115584654</v>
+        <v>-0.3660112178501009</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.6355449623675966</v>
+        <v>-0.3911094204573828</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.5457760838777119</v>
+        <v>-0.2712058749271904</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.408181246125082</v>
+        <v>-0.07424708657021739</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.546794641223201</v>
+        <v>-0.1777313464217158</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>-0.5805008505178719</v>
+        <v>-0.1970069404279897</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>-0.6049010513296196</v>
+        <v>-0.2038847397901478</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>-0.5286539790827405</v>
+        <v>-0.08680555555555713</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-0.4551044595064724</v>
+        <v>0.001269935242433462</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>-0.4756467363060537</v>
+        <v>-0.005227433571384665</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>-0.3976716425917814</v>
+        <v>0.05153072865931563</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>-0.346507160293676</v>
+        <v>0.08383370202605533</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>-0.3394452122371874</v>
+        <v>-0.004126515865543467</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>-0.3655187054001559</v>
+        <v>-0.05756818369083305</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>-0.4543675454740992</v>
+        <v>-0.2642064439769314</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &lt; 89.45</t>
+          <t>X &lt; 89.23</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3206</v>
+        <v>3242</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.3116430254790359</v>
+        <v>-0.2747531472575773</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.3820675301213114</v>
+        <v>-0.258760697025032</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.4089946806764218</v>
+        <v>-0.2074892561266779</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.4539373398339421</v>
+        <v>-0.1995119283963334</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.5864184605547251</v>
+        <v>-0.3351511382541617</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.9094163039262497</v>
+        <v>-0.6528407538705849</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.8264577569873168</v>
+        <v>-0.6624627557606289</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.9941102594084228</v>
+        <v>-0.7656959686480107</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.7799029684791492</v>
+        <v>-0.5282350500787487</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.6967614422656538</v>
+        <v>-0.414687132099786</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.653406910868803</v>
+        <v>-0.3711047206632827</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.5104255674751457</v>
+        <v>-0.1991401727624975</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.37230343349718</v>
+        <v>-0.03367270099032993</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.4196221860991969</v>
+        <v>-0.0173941481917339</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>-0.4684384795093237</v>
+        <v>-0.1142127321716728</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>-0.4777865776621155</v>
+        <v>-0.07663021674080284</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>-0.437725529021165</v>
+        <v>-0.05728203943314725</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-0.4307462177185357</v>
+        <v>-0.03613040830393288</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>-0.4766805270487211</v>
+        <v>-0.06812535922346541</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>-0.396060298730994</v>
+        <v>-0.007574650455310916</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>-0.4216511356528159</v>
+        <v>-0.002196087393556923</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>-0.3542843125694262</v>
+        <v>-0.05905291662989498</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>-0.4042343504969779</v>
+        <v>-0.1362935553499725</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>-0.3368210015100104</v>
+        <v>-0.156828262856898</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &lt; 92.34</t>
+          <t>X &lt; 92.11</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3279</v>
+        <v>3313</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.3701021104035007</v>
+        <v>-0.2853466320433498</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.2040395434085696</v>
+        <v>-0.03477981006071218</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.2318247789946</v>
+        <v>0.01835238836424224</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.2914954343325107</v>
+        <v>0.0134085970241884</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.4284274770599126</v>
+        <v>-0.1853088341897973</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.6187636992198193</v>
+        <v>-0.3724143505096862</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.6153311156443024</v>
+        <v>-0.459110846938465</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.7853689522532363</v>
+        <v>-0.5967357952917638</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.6963589371742671</v>
+        <v>-0.4819704362970967</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.5410669802692851</v>
+        <v>-0.3580206198041296</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.5836792874059071</v>
+        <v>-0.3696867317219343</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.450031464794975</v>
+        <v>-0.2375697531530321</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.3094817784030823</v>
+        <v>-0.06975950343702664</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.3606380704960088</v>
+        <v>-0.08937034033919389</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>-0.2708965437080835</v>
+        <v>0.01207985884867924</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>-0.2363534954043018</v>
+        <v>0.06102703619757932</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-0.2305161151954351</v>
+        <v>0.07770117540686527</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-0.2564000159750748</v>
+        <v>0.06537162117956541</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>-0.3878131250645964</v>
+        <v>-0.02155252901039972</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>-0.3352637664202049</v>
+        <v>0.02993818276016924</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>-0.3418652500921553</v>
+        <v>0.05321996513970362</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>-0.2776604957019586</v>
+        <v>0.02615369755329056</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>-0.3203667438134232</v>
+        <v>-0.01401170265802421</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>-0.2561168780087399</v>
+        <v>-0.09791242963638069</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &lt; 95.23</t>
+          <t>X &lt; 94.99</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3345</v>
+        <v>3373</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.1372841680638004</v>
+        <v>-0.1522965394313545</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.04036997652784891</v>
+        <v>0.08937855650402327</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.1848847908781295</v>
+        <v>0.001020121904574012</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.1682017350846365</v>
+        <v>0.04451177018622587</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.2495455978681846</v>
+        <v>-0.06703216045776372</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.4621592982248899</v>
+        <v>-0.2774312512875099</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.4144133771275875</v>
+        <v>-0.3177947687927158</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.4972564920462474</v>
+        <v>-0.3402243579496158</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.4388561181960355</v>
+        <v>-0.2842475663221578</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.3910378739898306</v>
+        <v>-0.2063877164695995</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.3678221948965543</v>
+        <v>-0.1833200609062686</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.2124294690468389</v>
+        <v>-0.0585217064854362</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.09666147923379498</v>
+        <v>0.08619215377774481</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.1809033362352608</v>
+        <v>0.003311099344017521</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>-0.07600995007764766</v>
+        <v>0.1378805669728393</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>-0.0900369637321603</v>
+        <v>0.1663249055083043</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>-0.05707472719950601</v>
+        <v>0.2104610716400259</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>-0.144145649051282</v>
+        <v>0.136783597621104</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>-0.2985335788250296</v>
+        <v>0.02560935348209625</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>-0.2433109310395167</v>
+        <v>0.08001179337816922</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>-0.2903187457532965</v>
+        <v>0.003947158869365808</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>-0.1392277651122598</v>
+        <v>0.09452976592935158</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>-0.1457498003935456</v>
+        <v>0.02979304657097259</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>-0.08421168433846304</v>
+        <v>0.003807975895774973</v>
       </c>
     </row>
   </sheetData>
